--- a/Assets/model de calcul crédit.xlsx
+++ b/Assets/model de calcul crédit.xlsx
@@ -5472,13 +5472,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="227">
-        <x:v>80000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="E3" s="226" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="F3" s="228">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="229" t="s">
         <x:v>9</x:v>
@@ -5524,7 +5524,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="228">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G4" s="229" t="s">
         <x:v>15</x:v>
@@ -5616,7 +5616,7 @@
       <x:c r="D6" s="229"/>
       <x:c r="E6" s="236"/>
       <x:c r="F6" s="248">
-        <x:v>46128</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="G6" s="229"/>
       <x:c r="H6" s="229"/>

--- a/Assets/model de calcul crédit.xlsx
+++ b/Assets/model de calcul crédit.xlsx
@@ -3,7 +3,7 @@
 <x:workbook xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <x:workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7962AE15-5F47-4EE1-9653-38CE4C6ED8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F868EB03-4A1B-4F86-B7A5-11E3A6CA9EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
@@ -2247,6 +2247,19 @@
       <x:alignment horizontal="right" wrapText="1"/>
       <x:protection hidden="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right"/>
+      <x:protection hidden="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
       <x:protection locked="0"/>
@@ -2327,12 +2340,6 @@
     <x:xf numFmtId="14" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="14" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="14" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="right"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
@@ -2416,10 +2423,6 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <x:protection locked="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right"/>
-      <x:protection hidden="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
@@ -2481,9 +2484,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -5375,55 +5375,55 @@
   <x:dimension ref="A1:W449"/>
   <x:sheetFormatPr defaultColWidth="11.425781" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.855469" style="50" customWidth="1"/>
-    <x:col min="2" max="2" width="11.425781" style="51" customWidth="1"/>
-    <x:col min="3" max="3" width="12" style="52" customWidth="1"/>
-    <x:col min="4" max="4" width="11.710938" style="50" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="6" width="11.425781" style="52" customWidth="1"/>
-    <x:col min="7" max="7" width="2.710938" style="50" customWidth="1"/>
-    <x:col min="8" max="8" width="7.710938" style="50" customWidth="1"/>
-    <x:col min="9" max="9" width="5.285156" style="50" customWidth="1"/>
-    <x:col min="10" max="10" width="6.285156" style="50" customWidth="1"/>
-    <x:col min="11" max="11" width="11.570312" style="50" bestFit="1" customWidth="1"/>
-    <x:col min="12" max="12" width="11.855469" style="50" customWidth="1"/>
-    <x:col min="13" max="13" width="11.425781" style="50" customWidth="1"/>
-    <x:col min="14" max="14" width="12.140625" style="50" customWidth="1"/>
-    <x:col min="15" max="15" width="11.425781" style="50" customWidth="1"/>
-    <x:col min="16" max="16" width="12.570312" style="50" customWidth="1"/>
-    <x:col min="17" max="17" width="4.285156" style="50" customWidth="1"/>
-    <x:col min="18" max="18" width="11.285156" style="58" hidden="1" customWidth="1"/>
-    <x:col min="19" max="19" width="15.425781" style="59" hidden="1" customWidth="1"/>
-    <x:col min="20" max="20" width="10.285156" style="50" hidden="1" customWidth="1"/>
-    <x:col min="21" max="23" width="13.710938" style="50" hidden="1" customWidth="1"/>
-    <x:col min="24" max="16384" width="11.425781" style="50" customWidth="1"/>
+    <x:col min="1" max="1" width="1.855469" style="54" customWidth="1"/>
+    <x:col min="2" max="2" width="11.425781" style="55" customWidth="1"/>
+    <x:col min="3" max="3" width="12" style="56" customWidth="1"/>
+    <x:col min="4" max="4" width="11.710938" style="54" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="6" width="11.425781" style="56" customWidth="1"/>
+    <x:col min="7" max="7" width="2.710938" style="54" customWidth="1"/>
+    <x:col min="8" max="8" width="7.710938" style="54" customWidth="1"/>
+    <x:col min="9" max="9" width="5.285156" style="54" customWidth="1"/>
+    <x:col min="10" max="10" width="6.285156" style="54" customWidth="1"/>
+    <x:col min="11" max="11" width="11.570312" style="54" bestFit="1" customWidth="1"/>
+    <x:col min="12" max="12" width="11.855469" style="54" customWidth="1"/>
+    <x:col min="13" max="13" width="11.425781" style="54" customWidth="1"/>
+    <x:col min="14" max="14" width="12.140625" style="54" customWidth="1"/>
+    <x:col min="15" max="15" width="11.425781" style="54" customWidth="1"/>
+    <x:col min="16" max="16" width="12.570312" style="54" customWidth="1"/>
+    <x:col min="17" max="17" width="4.285156" style="54" customWidth="1"/>
+    <x:col min="18" max="18" width="11.285156" style="62" hidden="1" customWidth="1"/>
+    <x:col min="19" max="19" width="15.425781" style="63" hidden="1" customWidth="1"/>
+    <x:col min="20" max="20" width="10.285156" style="54" hidden="1" customWidth="1"/>
+    <x:col min="21" max="23" width="13.710938" style="54" hidden="1" customWidth="1"/>
+    <x:col min="24" max="16384" width="11.425781" style="54" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:31" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="D1" s="53"/>
-      <x:c r="F1" s="54"/>
-      <x:c r="H1" s="55"/>
-      <x:c r="I1" s="55"/>
-      <x:c r="J1" s="55"/>
-      <x:c r="K1" s="56"/>
-      <x:c r="L1" s="57"/>
-      <x:c r="M1" s="53"/>
-      <x:c r="N1" s="53"/>
-      <x:c r="O1" s="53"/>
-      <x:c r="P1" s="53"/>
-      <x:c r="Q1" s="53"/>
-      <x:c r="S1" s="115">
+      <x:c r="D1" s="57"/>
+      <x:c r="F1" s="58"/>
+      <x:c r="H1" s="59"/>
+      <x:c r="I1" s="59"/>
+      <x:c r="J1" s="59"/>
+      <x:c r="K1" s="60"/>
+      <x:c r="L1" s="61"/>
+      <x:c r="M1" s="57"/>
+      <x:c r="N1" s="57"/>
+      <x:c r="O1" s="57"/>
+      <x:c r="P1" s="57"/>
+      <x:c r="Q1" s="57"/>
+      <x:c r="S1" s="117">
         <x:f>IF(ISERROR(Avancé!D3),2,Avancé!D3)</x:f>
       </x:c>
-      <x:c r="T1" s="79">
+      <x:c r="T1" s="81">
         <x:f>IF(Periodicite="M",12)+IF(Periodicite="T",4)+IF(Periodicite="S",2)+IF(Periodicite="A",1)+IF(Periodicite="H",52)+IF(Periodicite="Q",26)+IF(Periodicite="B",24)</x:f>
       </x:c>
-      <x:c r="U1" s="81" t="s">
+      <x:c r="U1" s="83" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="V1" s="215" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="W1" s="118" t="s">
+      <x:c r="W1" s="120" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -5449,20 +5449,20 @@
       </x:c>
       <x:c r="O2" s="223"/>
       <x:c r="P2" s="220"/>
-      <x:c r="Q2" s="53"/>
-      <x:c r="S2" s="115">
+      <x:c r="Q2" s="57"/>
+      <x:c r="S2" s="117">
         <x:f>IF(ISERROR(Avancé!I9),TRUE,IF(Avancé!I9=1,TRUE,FALSE))</x:f>
       </x:c>
-      <x:c r="T2" s="79">
+      <x:c r="T2" s="81">
         <x:f>T3*NbEchAn/12</x:f>
       </x:c>
-      <x:c r="U2" s="81" t="s">
+      <x:c r="U2" s="83" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="V2" s="224">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="W2" s="50">
+      <x:c r="W2" s="54">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -5472,7 +5472,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="227">
-        <x:v>3000</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="E3" s="226" t="s">
         <x:v>8</x:v>
@@ -5490,7 +5490,9 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L3" s="229"/>
-      <x:c r="M3" s="232"/>
+      <x:c r="M3" s="232">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="N3" s="233" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -5498,21 +5500,21 @@
       <x:c r="P3" s="235">
         <x:f>MAX(K14:K447)</x:f>
       </x:c>
-      <x:c r="Q3" s="53"/>
-      <x:c r="R3" s="85"/>
-      <x:c r="S3" s="115">
+      <x:c r="Q3" s="57"/>
+      <x:c r="R3" s="87"/>
+      <x:c r="S3" s="117">
         <x:f>IF(ISERROR(Avancé!D17),99999,Avancé!D17)</x:f>
       </x:c>
-      <x:c r="T3" s="79">
+      <x:c r="T3" s="81">
         <x:f>F3*12+F4</x:f>
       </x:c>
-      <x:c r="U3" s="81" t="s">
+      <x:c r="U3" s="83" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="V3" s="224">
         <x:f>V2=1</x:f>
       </x:c>
-      <x:c r="W3" s="50" t="s">
+      <x:c r="W3" s="54" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
@@ -5524,7 +5526,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="228">
-        <x:v>18</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G4" s="229" t="s">
         <x:v>15</x:v>
@@ -5544,20 +5546,20 @@
       <x:c r="P4" s="230">
         <x:f>MAX(H14:H447)</x:f>
       </x:c>
-      <x:c r="Q4" s="53"/>
-      <x:c r="S4" s="115">
+      <x:c r="Q4" s="57"/>
+      <x:c r="S4" s="117">
         <x:f>IF(ISERROR(Avancé!E17),99999,Avancé!E17)</x:f>
       </x:c>
-      <x:c r="T4" s="83">
+      <x:c r="T4" s="85">
         <x:f>IF(TauxActuariel,((D5+1)^(1/NbEchAn))-1,D5/NbEchAn)</x:f>
       </x:c>
-      <x:c r="U4" s="82" t="s">
+      <x:c r="U4" s="84" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="V4" s="241" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="W4" s="50" t="s">
+      <x:c r="W4" s="54" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -5591,22 +5593,22 @@
       <x:c r="P5" s="246">
         <x:f>SUM(M14:M447)</x:f>
       </x:c>
-      <x:c r="Q5" s="53"/>
-      <x:c r="S5" s="116">
+      <x:c r="Q5" s="57"/>
+      <x:c r="S5" s="118">
         <x:f>IF(1&lt;=NoEchMaxi,
 IF(ISERROR(Avancé!D37),ROUND(L15*R15,NbDeci),Avancé!D37),
 0)</x:f>
       </x:c>
-      <x:c r="T5" s="84">
+      <x:c r="T5" s="86">
         <x:f>0+IF(Periodicite="M",1)+IF(Periodicite="T",3)+IF(Periodicite="S",6)+IF(Periodicite="A",12)+IF(Periodicite="B",0.5)</x:f>
       </x:c>
-      <x:c r="U5" s="82" t="s">
+      <x:c r="U5" s="84" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="V5" s="247">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="W5" s="50" t="s">
+      <x:c r="W5" s="54" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
@@ -5616,7 +5618,7 @@
       <x:c r="D6" s="229"/>
       <x:c r="E6" s="236"/>
       <x:c r="F6" s="248">
-        <x:v>46133</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="G6" s="229"/>
       <x:c r="H6" s="229"/>
@@ -5632,24 +5634,24 @@
       <x:c r="P6" s="246">
         <x:f>SUM(N14:N447)-SUMIF(C14:C447,"&lt;0")</x:f>
       </x:c>
-      <x:c r="Q6" s="53"/>
-      <x:c r="S6" s="116">
+      <x:c r="Q6" s="57"/>
+      <x:c r="S6" s="118">
         <x:f>IF(1&gt;NoEchMaxi,
 0,
 IF(ISERROR(Avancé!E37),
    IF(1&lt;=Différé,IF(DiffTotal,-INT1E,0),IF(1&gt;=NoEchRemb,L15,IF(S15-(M15*EchFIXE)&gt;L15-2,L15,S15-(M15*EchFIXE))))+C15,
    Avancé!E37))</x:f>
       </x:c>
-      <x:c r="T6" s="79">
+      <x:c r="T6" s="81">
         <x:f>0+IF(Periodicite="H",7)+IF(Periodicite="Q",14)</x:f>
       </x:c>
-      <x:c r="U6" s="82" t="s">
+      <x:c r="U6" s="84" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="V6" s="247">
         <x:f>IF(Différé&gt;0,V5=1,FALSE)</x:f>
       </x:c>
-      <x:c r="W6" s="50" t="s">
+      <x:c r="W6" s="54" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
@@ -5677,22 +5679,22 @@
       <x:c r="P7" s="246">
         <x:f>SUM(O14:O447)</x:f>
       </x:c>
-      <x:c r="Q7" s="53"/>
-      <x:c r="S7" s="117">
+      <x:c r="Q7" s="57"/>
+      <x:c r="S7" s="119">
         <x:f>IF(ISERROR(Avancé!C37),
 IF(Ijour=0,MIN(DATE(YEAR(DebAmort),MONTH(DebAmort)-MoisD-Imois,Jour2),DATE(YEAR(DebAmort),MONTH(DebAmort)-MoisD+1-Imois,0)),DATE(YEAR(DebAmort),MONTH(DebAmort),Jour1-Ijour)),
 Avancé!C37)</x:f>
       </x:c>
-      <x:c r="T7" s="79">
+      <x:c r="T7" s="81">
         <x:f>DAY(DebAmort)</x:f>
       </x:c>
-      <x:c r="U7" s="82" t="s">
+      <x:c r="U7" s="84" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="V7" s="247">
         <x:f>IF(Différé&gt;0,V5=2,FALSE)</x:f>
       </x:c>
-      <x:c r="W7" s="50" t="s">
+      <x:c r="W7" s="54" t="s">
         <x:v>33</x:v>
       </x:c>
     </x:row>
@@ -5722,36 +5724,36 @@
       <x:c r="P8" s="258">
         <x:f>SUM(P5:P7)</x:f>
       </x:c>
-      <x:c r="Q8" s="53"/>
-      <x:c r="T8" s="79">
+      <x:c r="Q8" s="57"/>
+      <x:c r="T8" s="81">
         <x:f>IF(Periodicite="B",IF(T7&gt;15,MIN(T7-15,15),T7+15),T7)</x:f>
       </x:c>
-      <x:c r="U8" s="82" t="s">
+      <x:c r="U8" s="84" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="V8" s="259">
         <x:f>M7*NbEchAn/12</x:f>
       </x:c>
-      <x:c r="W8" s="50" t="s">
+      <x:c r="W8" s="54" t="s">
         <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:31" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <x:c r="E9" s="181"/>
-      <x:c r="F9" s="118"/>
+      <x:c r="F9" s="120"/>
       <x:c r="H9" s="182"/>
       <x:c r="I9" s="182"/>
       <x:c r="J9" s="182"/>
-      <x:c r="T9" s="79">
+      <x:c r="T9" s="81">
         <x:f>IF(Jour2&lt;Jour1,1,0)</x:f>
       </x:c>
-      <x:c r="U9" s="82" t="s">
+      <x:c r="U9" s="84" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="V9" s="260" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="W9" s="50" t="s">
+      <x:c r="W9" s="54" t="s">
         <x:v>40</x:v>
       </x:c>
     </x:row>
@@ -5852,7 +5854,7 @@
       <x:c r="F12" s="286" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G12" s="60"/>
+      <x:c r="G12" s="64"/>
       <x:c r="H12" s="287" t="s">
         <x:v>57</x:v>
       </x:c>
@@ -5866,7 +5868,7 @@
       <x:c r="N12" s="292"/>
       <x:c r="O12" s="292"/>
       <x:c r="P12" s="293"/>
-      <x:c r="Q12" s="45"/>
+      <x:c r="Q12" s="49"/>
       <x:c r="R12" s="294"/>
       <x:c r="S12" s="295"/>
       <x:c r="V12" s="296">
@@ -5874,13 +5876,13 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <x:c r="A13" s="60"/>
+      <x:c r="A13" s="64"/>
       <x:c r="B13" s="297"/>
       <x:c r="C13" s="298"/>
       <x:c r="D13" s="299"/>
       <x:c r="E13" s="298"/>
       <x:c r="F13" s="300"/>
-      <x:c r="G13" s="60"/>
+      <x:c r="G13" s="64"/>
       <x:c r="H13" s="301" t="s">
         <x:v>59</x:v>
       </x:c>
@@ -5892,11 +5894,11 @@
       <x:c r="N13" s="307"/>
       <x:c r="O13" s="307"/>
       <x:c r="P13" s="308"/>
-      <x:c r="Q13" s="45"/>
+      <x:c r="Q13" s="49"/>
       <x:c r="R13" s="309"/>
       <x:c r="S13" s="310"/>
     </x:row>
-    <x:row r="14" spans="1:31" ht="13.5" customHeight="1" s="60" customFormat="1" x14ac:dyDescent="0.2">
+    <x:row r="14" spans="1:31" ht="13.5" customHeight="1" s="64" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="B14" s="311"/>
       <x:c r="C14" s="312">
         <x:f>IF(M8&gt;0,-M8,-D3)</x:f>
@@ -5906,7 +5908,7 @@
       </x:c>
       <x:c r="E14" s="313"/>
       <x:c r="F14" s="314"/>
-      <x:c r="G14" s="50"/>
+      <x:c r="G14" s="54"/>
       <x:c r="H14" s="315">
         <x:v>0</x:v>
       </x:c>
@@ -5930,17 +5932,17 @@
       <x:c r="P14" s="321">
         <x:f>SUM(M14:O14)</x:f>
       </x:c>
-      <x:c r="Q14" s="45"/>
+      <x:c r="Q14" s="49"/>
       <x:c r="R14" s="294"/>
       <x:c r="S14" s="295"/>
     </x:row>
-    <x:row r="15" spans="1:31" ht="12.75" customHeight="1" s="60" customFormat="1" x14ac:dyDescent="0.2">
+    <x:row r="15" spans="1:31" ht="12.75" customHeight="1" s="64" customFormat="1" x14ac:dyDescent="0.2">
       <x:c r="B15" s="322"/>
       <x:c r="C15" s="323"/>
       <x:c r="D15" s="324"/>
       <x:c r="E15" s="325"/>
       <x:c r="F15" s="326"/>
-      <x:c r="G15" s="50"/>
+      <x:c r="G15" s="54"/>
       <x:c r="H15" s="327">
         <x:f>IF(L15=0,"",H14+1)</x:f>
       </x:c>
@@ -5969,21 +5971,21 @@
         <x:f>SUM(M15:O15)</x:f>
       </x:c>
       <x:c r="Q15" s="0"/>
-      <x:c r="R15" s="71">
+      <x:c r="R15" s="75">
         <x:f>IF(B15&gt;0,IF(TauxActuariel,((B15+1)^(1/NbEchAn))-1,B15/NbEchAn),TxPer)</x:f>
       </x:c>
-      <x:c r="S15" s="70">
+      <x:c r="S15" s="74">
         <x:f>IF(E15&gt;0,E15,IF(D15&gt;0,IF(AND(EchFIXE,R15&gt;0),ROUND((L15-C15)*R15/(1-((1+R15)^-D15)),NbDeci),ROUND(L15/D15,NbDeci)),MtEch))</x:f>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:31" ht="13.5" customHeight="1" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <x:c r="A16" s="50"/>
+    <x:row r="16" spans="1:31" ht="13.5" customHeight="1" s="64" customFormat="1" x14ac:dyDescent="0.2">
+      <x:c r="A16" s="54"/>
       <x:c r="B16" s="334"/>
       <x:c r="C16" s="335"/>
       <x:c r="D16" s="336"/>
       <x:c r="E16" s="337"/>
       <x:c r="F16" s="338"/>
-      <x:c r="G16" s="50"/>
+      <x:c r="G16" s="54"/>
       <x:c r="H16" s="327">
         <x:f>IF(L16=0,"",H15+1)</x:f>
       </x:c>
@@ -6012,10 +6014,10 @@
         <x:f>SUM(M16:O16)</x:f>
       </x:c>
       <x:c r="Q16" s="0"/>
-      <x:c r="R16" s="71">
+      <x:c r="R16" s="75">
         <x:f>IF(B16&gt;0,IF(TauxActuariel,((B16+1)^(1/NbEchAn))-1,B16/NbEchAn),R15)</x:f>
       </x:c>
-      <x:c r="S16" s="70">
+      <x:c r="S16" s="74">
         <x:f>IF(E16&gt;0,E16,IF(D16&gt;0,IF(AND(EchFIXE,R16&gt;0),ROUND((L16-C16)*R16/(1-((1+R16)^-D16)),NbDeci),ROUND(L16/D16,NbDeci)),S15))</x:f>
       </x:c>
     </x:row>
@@ -6053,10 +6055,10 @@
         <x:f>SUM(M17:O17)</x:f>
       </x:c>
       <x:c r="Q17" s="0"/>
-      <x:c r="R17" s="71">
+      <x:c r="R17" s="75">
         <x:f>IF(B17&gt;0,IF(TauxActuariel,((B17+1)^(1/NbEchAn))-1,B17/NbEchAn),R16)</x:f>
       </x:c>
-      <x:c r="S17" s="70">
+      <x:c r="S17" s="74">
         <x:f>IF(E17&gt;0,E17,IF(D17&gt;0,IF(AND(EchFIXE,R17&gt;0),ROUND((L17-C17)*R17/(1-((1+R17)^-D17)),NbDeci),ROUND(L17/D17,NbDeci)),S16))</x:f>
       </x:c>
     </x:row>
@@ -6094,10 +6096,10 @@
         <x:f>SUM(M18:O18)</x:f>
       </x:c>
       <x:c r="Q18" s="0"/>
-      <x:c r="R18" s="71">
+      <x:c r="R18" s="75">
         <x:f>IF(B18&gt;0,IF(TauxActuariel,((B18+1)^(1/NbEchAn))-1,B18/NbEchAn),R17)</x:f>
       </x:c>
-      <x:c r="S18" s="70">
+      <x:c r="S18" s="74">
         <x:f>IF(E18&gt;0,E18,IF(D18&gt;0,IF(AND(EchFIXE,R18&gt;0),ROUND((L18-C18)*R18/(1-((1+R18)^-D18)),NbDeci),ROUND(L18/D18,NbDeci)),S17))</x:f>
       </x:c>
     </x:row>
@@ -6135,10 +6137,10 @@
         <x:f>SUM(M19:O19)</x:f>
       </x:c>
       <x:c r="Q19" s="0"/>
-      <x:c r="R19" s="71">
+      <x:c r="R19" s="75">
         <x:f>IF(B19&gt;0,IF(TauxActuariel,((B19+1)^(1/NbEchAn))-1,B19/NbEchAn),R18)</x:f>
       </x:c>
-      <x:c r="S19" s="70">
+      <x:c r="S19" s="74">
         <x:f>IF(E19&gt;0,E19,IF(D19&gt;0,IF(AND(EchFIXE,R19&gt;0),ROUND((L19-C19)*R19/(1-((1+R19)^-D19)),NbDeci),ROUND(L19/D19,NbDeci)),S18))</x:f>
       </x:c>
     </x:row>
@@ -6176,10 +6178,10 @@
         <x:f>SUM(M20:O20)</x:f>
       </x:c>
       <x:c r="Q20" s="0"/>
-      <x:c r="R20" s="71">
+      <x:c r="R20" s="75">
         <x:f>IF(B20&gt;0,IF(TauxActuariel,((B20+1)^(1/NbEchAn))-1,B20/NbEchAn),R19)</x:f>
       </x:c>
-      <x:c r="S20" s="70">
+      <x:c r="S20" s="74">
         <x:f>IF(E20&gt;0,E20,IF(D20&gt;0,IF(AND(EchFIXE,R20&gt;0),ROUND((L20-C20)*R20/(1-((1+R20)^-D20)),NbDeci),ROUND(L20/D20,NbDeci)),S19))</x:f>
       </x:c>
     </x:row>
@@ -6217,10 +6219,10 @@
         <x:f>SUM(M21:O21)</x:f>
       </x:c>
       <x:c r="Q21" s="0"/>
-      <x:c r="R21" s="71">
+      <x:c r="R21" s="75">
         <x:f>IF(B21&gt;0,IF(TauxActuariel,((B21+1)^(1/NbEchAn))-1,B21/NbEchAn),R20)</x:f>
       </x:c>
-      <x:c r="S21" s="70">
+      <x:c r="S21" s="74">
         <x:f>IF(E21&gt;0,E21,IF(D21&gt;0,IF(AND(EchFIXE,R21&gt;0),ROUND((L21-C21)*R21/(1-((1+R21)^-D21)),NbDeci),ROUND(L21/D21,NbDeci)),S20))</x:f>
       </x:c>
     </x:row>
@@ -6258,10 +6260,10 @@
         <x:f>SUM(M22:O22)</x:f>
       </x:c>
       <x:c r="Q22" s="0"/>
-      <x:c r="R22" s="71">
+      <x:c r="R22" s="75">
         <x:f>IF(B22&gt;0,IF(TauxActuariel,((B22+1)^(1/NbEchAn))-1,B22/NbEchAn),R21)</x:f>
       </x:c>
-      <x:c r="S22" s="70">
+      <x:c r="S22" s="74">
         <x:f>IF(E22&gt;0,E22,IF(D22&gt;0,IF(AND(EchFIXE,R22&gt;0),ROUND((L22-C22)*R22/(1-((1+R22)^-D22)),NbDeci),ROUND(L22/D22,NbDeci)),S21))</x:f>
       </x:c>
     </x:row>
@@ -6299,10 +6301,10 @@
         <x:f>SUM(M23:O23)</x:f>
       </x:c>
       <x:c r="Q23" s="0"/>
-      <x:c r="R23" s="71">
+      <x:c r="R23" s="75">
         <x:f>IF(B23&gt;0,IF(TauxActuariel,((B23+1)^(1/NbEchAn))-1,B23/NbEchAn),R22)</x:f>
       </x:c>
-      <x:c r="S23" s="70">
+      <x:c r="S23" s="74">
         <x:f>IF(E23&gt;0,E23,IF(D23&gt;0,IF(AND(EchFIXE,R23&gt;0),ROUND((L23-C23)*R23/(1-((1+R23)^-D23)),NbDeci),ROUND(L23/D23,NbDeci)),S22))</x:f>
       </x:c>
     </x:row>
@@ -6340,10 +6342,10 @@
         <x:f>SUM(M24:O24)</x:f>
       </x:c>
       <x:c r="Q24" s="0"/>
-      <x:c r="R24" s="71">
+      <x:c r="R24" s="75">
         <x:f>IF(B24&gt;0,IF(TauxActuariel,((B24+1)^(1/NbEchAn))-1,B24/NbEchAn),R23)</x:f>
       </x:c>
-      <x:c r="S24" s="70">
+      <x:c r="S24" s="74">
         <x:f>IF(E24&gt;0,E24,IF(D24&gt;0,IF(AND(EchFIXE,R24&gt;0),ROUND((L24-C24)*R24/(1-((1+R24)^-D24)),NbDeci),ROUND(L24/D24,NbDeci)),S23))</x:f>
       </x:c>
     </x:row>
@@ -6381,10 +6383,10 @@
         <x:f>SUM(M25:O25)</x:f>
       </x:c>
       <x:c r="Q25" s="0"/>
-      <x:c r="R25" s="71">
+      <x:c r="R25" s="75">
         <x:f>IF(B25&gt;0,IF(TauxActuariel,((B25+1)^(1/NbEchAn))-1,B25/NbEchAn),R24)</x:f>
       </x:c>
-      <x:c r="S25" s="70">
+      <x:c r="S25" s="74">
         <x:f>IF(E25&gt;0,E25,IF(D25&gt;0,IF(AND(EchFIXE,R25&gt;0),ROUND((L25-C25)*R25/(1-((1+R25)^-D25)),NbDeci),ROUND(L25/D25,NbDeci)),S24))</x:f>
       </x:c>
     </x:row>
@@ -6422,10 +6424,10 @@
         <x:f>SUM(M26:O26)</x:f>
       </x:c>
       <x:c r="Q26" s="0"/>
-      <x:c r="R26" s="71">
+      <x:c r="R26" s="75">
         <x:f>IF(B26&gt;0,IF(TauxActuariel,((B26+1)^(1/NbEchAn))-1,B26/NbEchAn),R25)</x:f>
       </x:c>
-      <x:c r="S26" s="70">
+      <x:c r="S26" s="74">
         <x:f>IF(E26&gt;0,E26,IF(D26&gt;0,IF(AND(EchFIXE,R26&gt;0),ROUND((L26-C26)*R26/(1-((1+R26)^-D26)),NbDeci),ROUND(L26/D26,NbDeci)),S25))</x:f>
       </x:c>
     </x:row>
@@ -6463,10 +6465,10 @@
         <x:f>SUM(M27:O27)</x:f>
       </x:c>
       <x:c r="Q27" s="0"/>
-      <x:c r="R27" s="71">
+      <x:c r="R27" s="75">
         <x:f>IF(B27&gt;0,IF(TauxActuariel,((B27+1)^(1/NbEchAn))-1,B27/NbEchAn),R26)</x:f>
       </x:c>
-      <x:c r="S27" s="70">
+      <x:c r="S27" s="74">
         <x:f>IF(E27&gt;0,E27,IF(D27&gt;0,IF(AND(EchFIXE,R27&gt;0),ROUND((L27-C27)*R27/(1-((1+R27)^-D27)),NbDeci),ROUND(L27/D27,NbDeci)),S26))</x:f>
       </x:c>
     </x:row>
@@ -6504,10 +6506,10 @@
         <x:f>SUM(M28:O28)</x:f>
       </x:c>
       <x:c r="Q28" s="0"/>
-      <x:c r="R28" s="71">
+      <x:c r="R28" s="75">
         <x:f>IF(B28&gt;0,IF(TauxActuariel,((B28+1)^(1/NbEchAn))-1,B28/NbEchAn),R27)</x:f>
       </x:c>
-      <x:c r="S28" s="70">
+      <x:c r="S28" s="74">
         <x:f>IF(E28&gt;0,E28,IF(D28&gt;0,IF(AND(EchFIXE,R28&gt;0),ROUND((L28-C28)*R28/(1-((1+R28)^-D28)),NbDeci),ROUND(L28/D28,NbDeci)),S27))</x:f>
       </x:c>
     </x:row>
@@ -6545,10 +6547,10 @@
         <x:f>SUM(M29:O29)</x:f>
       </x:c>
       <x:c r="Q29" s="0"/>
-      <x:c r="R29" s="71">
+      <x:c r="R29" s="75">
         <x:f>IF(B29&gt;0,IF(TauxActuariel,((B29+1)^(1/NbEchAn))-1,B29/NbEchAn),R28)</x:f>
       </x:c>
-      <x:c r="S29" s="70">
+      <x:c r="S29" s="74">
         <x:f>IF(E29&gt;0,E29,IF(D29&gt;0,IF(AND(EchFIXE,R29&gt;0),ROUND((L29-C29)*R29/(1-((1+R29)^-D29)),NbDeci),ROUND(L29/D29,NbDeci)),S28))</x:f>
       </x:c>
     </x:row>
@@ -6586,10 +6588,10 @@
         <x:f>SUM(M30:O30)</x:f>
       </x:c>
       <x:c r="Q30" s="0"/>
-      <x:c r="R30" s="71">
+      <x:c r="R30" s="75">
         <x:f>IF(B30&gt;0,IF(TauxActuariel,((B30+1)^(1/NbEchAn))-1,B30/NbEchAn),R29)</x:f>
       </x:c>
-      <x:c r="S30" s="70">
+      <x:c r="S30" s="74">
         <x:f>IF(E30&gt;0,E30,IF(D30&gt;0,IF(AND(EchFIXE,R30&gt;0),ROUND((L30-C30)*R30/(1-((1+R30)^-D30)),NbDeci),ROUND(L30/D30,NbDeci)),S29))</x:f>
       </x:c>
     </x:row>
@@ -6627,10 +6629,10 @@
         <x:f>SUM(M31:O31)</x:f>
       </x:c>
       <x:c r="Q31" s="0"/>
-      <x:c r="R31" s="71">
+      <x:c r="R31" s="75">
         <x:f>IF(B31&gt;0,IF(TauxActuariel,((B31+1)^(1/NbEchAn))-1,B31/NbEchAn),R30)</x:f>
       </x:c>
-      <x:c r="S31" s="70">
+      <x:c r="S31" s="74">
         <x:f>IF(E31&gt;0,E31,IF(D31&gt;0,IF(AND(EchFIXE,R31&gt;0),ROUND((L31-C31)*R31/(1-((1+R31)^-D31)),NbDeci),ROUND(L31/D31,NbDeci)),S30))</x:f>
       </x:c>
     </x:row>
@@ -6668,10 +6670,10 @@
         <x:f>SUM(M32:O32)</x:f>
       </x:c>
       <x:c r="Q32" s="0"/>
-      <x:c r="R32" s="71">
+      <x:c r="R32" s="75">
         <x:f>IF(B32&gt;0,IF(TauxActuariel,((B32+1)^(1/NbEchAn))-1,B32/NbEchAn),R31)</x:f>
       </x:c>
-      <x:c r="S32" s="70">
+      <x:c r="S32" s="74">
         <x:f>IF(E32&gt;0,E32,IF(D32&gt;0,IF(AND(EchFIXE,R32&gt;0),ROUND((L32-C32)*R32/(1-((1+R32)^-D32)),NbDeci),ROUND(L32/D32,NbDeci)),S31))</x:f>
       </x:c>
     </x:row>
@@ -6709,10 +6711,10 @@
         <x:f>SUM(M33:O33)</x:f>
       </x:c>
       <x:c r="Q33" s="0"/>
-      <x:c r="R33" s="71">
+      <x:c r="R33" s="75">
         <x:f>IF(B33&gt;0,IF(TauxActuariel,((B33+1)^(1/NbEchAn))-1,B33/NbEchAn),R32)</x:f>
       </x:c>
-      <x:c r="S33" s="70">
+      <x:c r="S33" s="74">
         <x:f>IF(E33&gt;0,E33,IF(D33&gt;0,IF(AND(EchFIXE,R33&gt;0),ROUND((L33-C33)*R33/(1-((1+R33)^-D33)),NbDeci),ROUND(L33/D33,NbDeci)),S32))</x:f>
       </x:c>
     </x:row>
@@ -6750,10 +6752,10 @@
         <x:f>SUM(M34:O34)</x:f>
       </x:c>
       <x:c r="Q34" s="0"/>
-      <x:c r="R34" s="71">
+      <x:c r="R34" s="75">
         <x:f>IF(B34&gt;0,IF(TauxActuariel,((B34+1)^(1/NbEchAn))-1,B34/NbEchAn),R33)</x:f>
       </x:c>
-      <x:c r="S34" s="70">
+      <x:c r="S34" s="74">
         <x:f>IF(E34&gt;0,E34,IF(D34&gt;0,IF(AND(EchFIXE,R34&gt;0),ROUND((L34-C34)*R34/(1-((1+R34)^-D34)),NbDeci),ROUND(L34/D34,NbDeci)),S33))</x:f>
       </x:c>
     </x:row>
@@ -6791,10 +6793,10 @@
         <x:f>SUM(M35:O35)</x:f>
       </x:c>
       <x:c r="Q35" s="0"/>
-      <x:c r="R35" s="71">
+      <x:c r="R35" s="75">
         <x:f>IF(B35&gt;0,IF(TauxActuariel,((B35+1)^(1/NbEchAn))-1,B35/NbEchAn),R34)</x:f>
       </x:c>
-      <x:c r="S35" s="70">
+      <x:c r="S35" s="74">
         <x:f>IF(E35&gt;0,E35,IF(D35&gt;0,IF(AND(EchFIXE,R35&gt;0),ROUND((L35-C35)*R35/(1-((1+R35)^-D35)),NbDeci),ROUND(L35/D35,NbDeci)),S34))</x:f>
       </x:c>
     </x:row>
@@ -6832,10 +6834,10 @@
         <x:f>SUM(M36:O36)</x:f>
       </x:c>
       <x:c r="Q36" s="0"/>
-      <x:c r="R36" s="71">
+      <x:c r="R36" s="75">
         <x:f>IF(B36&gt;0,IF(TauxActuariel,((B36+1)^(1/NbEchAn))-1,B36/NbEchAn),R35)</x:f>
       </x:c>
-      <x:c r="S36" s="70">
+      <x:c r="S36" s="74">
         <x:f>IF(E36&gt;0,E36,IF(D36&gt;0,IF(AND(EchFIXE,R36&gt;0),ROUND((L36-C36)*R36/(1-((1+R36)^-D36)),NbDeci),ROUND(L36/D36,NbDeci)),S35))</x:f>
       </x:c>
     </x:row>
@@ -6873,10 +6875,10 @@
         <x:f>SUM(M37:O37)</x:f>
       </x:c>
       <x:c r="Q37" s="0"/>
-      <x:c r="R37" s="71">
+      <x:c r="R37" s="75">
         <x:f>IF(B37&gt;0,IF(TauxActuariel,((B37+1)^(1/NbEchAn))-1,B37/NbEchAn),R36)</x:f>
       </x:c>
-      <x:c r="S37" s="70">
+      <x:c r="S37" s="74">
         <x:f>IF(E37&gt;0,E37,IF(D37&gt;0,IF(AND(EchFIXE,R37&gt;0),ROUND((L37-C37)*R37/(1-((1+R37)^-D37)),NbDeci),ROUND(L37/D37,NbDeci)),S36))</x:f>
       </x:c>
     </x:row>
@@ -6914,10 +6916,10 @@
         <x:f>SUM(M38:O38)</x:f>
       </x:c>
       <x:c r="Q38" s="0"/>
-      <x:c r="R38" s="71">
+      <x:c r="R38" s="75">
         <x:f>IF(B38&gt;0,IF(TauxActuariel,((B38+1)^(1/NbEchAn))-1,B38/NbEchAn),R37)</x:f>
       </x:c>
-      <x:c r="S38" s="70">
+      <x:c r="S38" s="74">
         <x:f>IF(E38&gt;0,E38,IF(D38&gt;0,IF(AND(EchFIXE,R38&gt;0),ROUND((L38-C38)*R38/(1-((1+R38)^-D38)),NbDeci),ROUND(L38/D38,NbDeci)),S37))</x:f>
       </x:c>
     </x:row>
@@ -6955,10 +6957,10 @@
         <x:f>SUM(M39:O39)</x:f>
       </x:c>
       <x:c r="Q39" s="0"/>
-      <x:c r="R39" s="71">
+      <x:c r="R39" s="75">
         <x:f>IF(B39&gt;0,IF(TauxActuariel,((B39+1)^(1/NbEchAn))-1,B39/NbEchAn),R38)</x:f>
       </x:c>
-      <x:c r="S39" s="70">
+      <x:c r="S39" s="74">
         <x:f>IF(E39&gt;0,E39,IF(D39&gt;0,IF(AND(EchFIXE,R39&gt;0),ROUND((L39-C39)*R39/(1-((1+R39)^-D39)),NbDeci),ROUND(L39/D39,NbDeci)),S38))</x:f>
       </x:c>
     </x:row>
@@ -6996,10 +6998,10 @@
         <x:f>SUM(M40:O40)</x:f>
       </x:c>
       <x:c r="Q40" s="0"/>
-      <x:c r="R40" s="71">
+      <x:c r="R40" s="75">
         <x:f>IF(B40&gt;0,IF(TauxActuariel,((B40+1)^(1/NbEchAn))-1,B40/NbEchAn),R39)</x:f>
       </x:c>
-      <x:c r="S40" s="70">
+      <x:c r="S40" s="74">
         <x:f>IF(E40&gt;0,E40,IF(D40&gt;0,IF(AND(EchFIXE,R40&gt;0),ROUND((L40-C40)*R40/(1-((1+R40)^-D40)),NbDeci),ROUND(L40/D40,NbDeci)),S39))</x:f>
       </x:c>
     </x:row>
@@ -7037,10 +7039,10 @@
         <x:f>SUM(M41:O41)</x:f>
       </x:c>
       <x:c r="Q41" s="0"/>
-      <x:c r="R41" s="71">
+      <x:c r="R41" s="75">
         <x:f>IF(B41&gt;0,IF(TauxActuariel,((B41+1)^(1/NbEchAn))-1,B41/NbEchAn),R40)</x:f>
       </x:c>
-      <x:c r="S41" s="70">
+      <x:c r="S41" s="74">
         <x:f>IF(E41&gt;0,E41,IF(D41&gt;0,IF(AND(EchFIXE,R41&gt;0),ROUND((L41-C41)*R41/(1-((1+R41)^-D41)),NbDeci),ROUND(L41/D41,NbDeci)),S40))</x:f>
       </x:c>
     </x:row>
@@ -7078,10 +7080,10 @@
         <x:f>SUM(M42:O42)</x:f>
       </x:c>
       <x:c r="Q42" s="0"/>
-      <x:c r="R42" s="71">
+      <x:c r="R42" s="75">
         <x:f>IF(B42&gt;0,IF(TauxActuariel,((B42+1)^(1/NbEchAn))-1,B42/NbEchAn),R41)</x:f>
       </x:c>
-      <x:c r="S42" s="70">
+      <x:c r="S42" s="74">
         <x:f>IF(E42&gt;0,E42,IF(D42&gt;0,IF(AND(EchFIXE,R42&gt;0),ROUND((L42-C42)*R42/(1-((1+R42)^-D42)),NbDeci),ROUND(L42/D42,NbDeci)),S41))</x:f>
       </x:c>
     </x:row>
@@ -7119,10 +7121,10 @@
         <x:f>SUM(M43:O43)</x:f>
       </x:c>
       <x:c r="Q43" s="0"/>
-      <x:c r="R43" s="71">
+      <x:c r="R43" s="75">
         <x:f>IF(B43&gt;0,IF(TauxActuariel,((B43+1)^(1/NbEchAn))-1,B43/NbEchAn),R42)</x:f>
       </x:c>
-      <x:c r="S43" s="70">
+      <x:c r="S43" s="74">
         <x:f>IF(E43&gt;0,E43,IF(D43&gt;0,IF(AND(EchFIXE,R43&gt;0),ROUND((L43-C43)*R43/(1-((1+R43)^-D43)),NbDeci),ROUND(L43/D43,NbDeci)),S42))</x:f>
       </x:c>
     </x:row>
@@ -7160,10 +7162,10 @@
         <x:f>SUM(M44:O44)</x:f>
       </x:c>
       <x:c r="Q44" s="0"/>
-      <x:c r="R44" s="71">
+      <x:c r="R44" s="75">
         <x:f>IF(B44&gt;0,IF(TauxActuariel,((B44+1)^(1/NbEchAn))-1,B44/NbEchAn),R43)</x:f>
       </x:c>
-      <x:c r="S44" s="70">
+      <x:c r="S44" s="74">
         <x:f>IF(E44&gt;0,E44,IF(D44&gt;0,IF(AND(EchFIXE,R44&gt;0),ROUND((L44-C44)*R44/(1-((1+R44)^-D44)),NbDeci),ROUND(L44/D44,NbDeci)),S43))</x:f>
       </x:c>
     </x:row>
@@ -7201,10 +7203,10 @@
         <x:f>SUM(M45:O45)</x:f>
       </x:c>
       <x:c r="Q45" s="0"/>
-      <x:c r="R45" s="71">
+      <x:c r="R45" s="75">
         <x:f>IF(B45&gt;0,IF(TauxActuariel,((B45+1)^(1/NbEchAn))-1,B45/NbEchAn),R44)</x:f>
       </x:c>
-      <x:c r="S45" s="70">
+      <x:c r="S45" s="74">
         <x:f>IF(E45&gt;0,E45,IF(D45&gt;0,IF(AND(EchFIXE,R45&gt;0),ROUND((L45-C45)*R45/(1-((1+R45)^-D45)),NbDeci),ROUND(L45/D45,NbDeci)),S44))</x:f>
       </x:c>
     </x:row>
@@ -7242,10 +7244,10 @@
         <x:f>SUM(M46:O46)</x:f>
       </x:c>
       <x:c r="Q46" s="0"/>
-      <x:c r="R46" s="71">
+      <x:c r="R46" s="75">
         <x:f>IF(B46&gt;0,IF(TauxActuariel,((B46+1)^(1/NbEchAn))-1,B46/NbEchAn),R45)</x:f>
       </x:c>
-      <x:c r="S46" s="70">
+      <x:c r="S46" s="74">
         <x:f>IF(E46&gt;0,E46,IF(D46&gt;0,IF(AND(EchFIXE,R46&gt;0),ROUND((L46-C46)*R46/(1-((1+R46)^-D46)),NbDeci),ROUND(L46/D46,NbDeci)),S45))</x:f>
       </x:c>
     </x:row>
@@ -7283,10 +7285,10 @@
         <x:f>SUM(M47:O47)</x:f>
       </x:c>
       <x:c r="Q47" s="0"/>
-      <x:c r="R47" s="71">
+      <x:c r="R47" s="75">
         <x:f>IF(B47&gt;0,IF(TauxActuariel,((B47+1)^(1/NbEchAn))-1,B47/NbEchAn),R46)</x:f>
       </x:c>
-      <x:c r="S47" s="70">
+      <x:c r="S47" s="74">
         <x:f>IF(E47&gt;0,E47,IF(D47&gt;0,IF(AND(EchFIXE,R47&gt;0),ROUND((L47-C47)*R47/(1-((1+R47)^-D47)),NbDeci),ROUND(L47/D47,NbDeci)),S46))</x:f>
       </x:c>
     </x:row>
@@ -7324,10 +7326,10 @@
         <x:f>SUM(M48:O48)</x:f>
       </x:c>
       <x:c r="Q48" s="0"/>
-      <x:c r="R48" s="71">
+      <x:c r="R48" s="75">
         <x:f>IF(B48&gt;0,IF(TauxActuariel,((B48+1)^(1/NbEchAn))-1,B48/NbEchAn),R47)</x:f>
       </x:c>
-      <x:c r="S48" s="70">
+      <x:c r="S48" s="74">
         <x:f>IF(E48&gt;0,E48,IF(D48&gt;0,IF(AND(EchFIXE,R48&gt;0),ROUND((L48-C48)*R48/(1-((1+R48)^-D48)),NbDeci),ROUND(L48/D48,NbDeci)),S47))</x:f>
       </x:c>
     </x:row>
@@ -7365,10 +7367,10 @@
         <x:f>SUM(M49:O49)</x:f>
       </x:c>
       <x:c r="Q49" s="0"/>
-      <x:c r="R49" s="71">
+      <x:c r="R49" s="75">
         <x:f>IF(B49&gt;0,IF(TauxActuariel,((B49+1)^(1/NbEchAn))-1,B49/NbEchAn),R48)</x:f>
       </x:c>
-      <x:c r="S49" s="70">
+      <x:c r="S49" s="74">
         <x:f>IF(E49&gt;0,E49,IF(D49&gt;0,IF(AND(EchFIXE,R49&gt;0),ROUND((L49-C49)*R49/(1-((1+R49)^-D49)),NbDeci),ROUND(L49/D49,NbDeci)),S48))</x:f>
       </x:c>
     </x:row>
@@ -7406,10 +7408,10 @@
         <x:f>SUM(M50:O50)</x:f>
       </x:c>
       <x:c r="Q50" s="0"/>
-      <x:c r="R50" s="71">
+      <x:c r="R50" s="75">
         <x:f>IF(B50&gt;0,IF(TauxActuariel,((B50+1)^(1/NbEchAn))-1,B50/NbEchAn),R49)</x:f>
       </x:c>
-      <x:c r="S50" s="70">
+      <x:c r="S50" s="74">
         <x:f>IF(E50&gt;0,E50,IF(D50&gt;0,IF(AND(EchFIXE,R50&gt;0),ROUND((L50-C50)*R50/(1-((1+R50)^-D50)),NbDeci),ROUND(L50/D50,NbDeci)),S49))</x:f>
       </x:c>
     </x:row>
@@ -7447,10 +7449,10 @@
         <x:f>SUM(M51:O51)</x:f>
       </x:c>
       <x:c r="Q51" s="0"/>
-      <x:c r="R51" s="71">
+      <x:c r="R51" s="75">
         <x:f>IF(B51&gt;0,IF(TauxActuariel,((B51+1)^(1/NbEchAn))-1,B51/NbEchAn),R50)</x:f>
       </x:c>
-      <x:c r="S51" s="70">
+      <x:c r="S51" s="74">
         <x:f>IF(E51&gt;0,E51,IF(D51&gt;0,IF(AND(EchFIXE,R51&gt;0),ROUND((L51-C51)*R51/(1-((1+R51)^-D51)),NbDeci),ROUND(L51/D51,NbDeci)),S50))</x:f>
       </x:c>
     </x:row>
@@ -7488,10 +7490,10 @@
         <x:f>SUM(M52:O52)</x:f>
       </x:c>
       <x:c r="Q52" s="0"/>
-      <x:c r="R52" s="71">
+      <x:c r="R52" s="75">
         <x:f>IF(B52&gt;0,IF(TauxActuariel,((B52+1)^(1/NbEchAn))-1,B52/NbEchAn),R51)</x:f>
       </x:c>
-      <x:c r="S52" s="70">
+      <x:c r="S52" s="74">
         <x:f>IF(E52&gt;0,E52,IF(D52&gt;0,IF(AND(EchFIXE,R52&gt;0),ROUND((L52-C52)*R52/(1-((1+R52)^-D52)),NbDeci),ROUND(L52/D52,NbDeci)),S51))</x:f>
       </x:c>
     </x:row>
@@ -7529,10 +7531,10 @@
         <x:f>SUM(M53:O53)</x:f>
       </x:c>
       <x:c r="Q53" s="0"/>
-      <x:c r="R53" s="71">
+      <x:c r="R53" s="75">
         <x:f>IF(B53&gt;0,IF(TauxActuariel,((B53+1)^(1/NbEchAn))-1,B53/NbEchAn),R52)</x:f>
       </x:c>
-      <x:c r="S53" s="70">
+      <x:c r="S53" s="74">
         <x:f>IF(E53&gt;0,E53,IF(D53&gt;0,IF(AND(EchFIXE,R53&gt;0),ROUND((L53-C53)*R53/(1-((1+R53)^-D53)),NbDeci),ROUND(L53/D53,NbDeci)),S52))</x:f>
       </x:c>
     </x:row>
@@ -7570,10 +7572,10 @@
         <x:f>SUM(M54:O54)</x:f>
       </x:c>
       <x:c r="Q54" s="0"/>
-      <x:c r="R54" s="71">
+      <x:c r="R54" s="75">
         <x:f>IF(B54&gt;0,IF(TauxActuariel,((B54+1)^(1/NbEchAn))-1,B54/NbEchAn),R53)</x:f>
       </x:c>
-      <x:c r="S54" s="70">
+      <x:c r="S54" s="74">
         <x:f>IF(E54&gt;0,E54,IF(D54&gt;0,IF(AND(EchFIXE,R54&gt;0),ROUND((L54-C54)*R54/(1-((1+R54)^-D54)),NbDeci),ROUND(L54/D54,NbDeci)),S53))</x:f>
       </x:c>
     </x:row>
@@ -7611,10 +7613,10 @@
         <x:f>SUM(M55:O55)</x:f>
       </x:c>
       <x:c r="Q55" s="0"/>
-      <x:c r="R55" s="71">
+      <x:c r="R55" s="75">
         <x:f>IF(B55&gt;0,IF(TauxActuariel,((B55+1)^(1/NbEchAn))-1,B55/NbEchAn),R54)</x:f>
       </x:c>
-      <x:c r="S55" s="70">
+      <x:c r="S55" s="74">
         <x:f>IF(E55&gt;0,E55,IF(D55&gt;0,IF(AND(EchFIXE,R55&gt;0),ROUND((L55-C55)*R55/(1-((1+R55)^-D55)),NbDeci),ROUND(L55/D55,NbDeci)),S54))</x:f>
       </x:c>
     </x:row>
@@ -7652,10 +7654,10 @@
         <x:f>SUM(M56:O56)</x:f>
       </x:c>
       <x:c r="Q56" s="0"/>
-      <x:c r="R56" s="71">
+      <x:c r="R56" s="75">
         <x:f>IF(B56&gt;0,IF(TauxActuariel,((B56+1)^(1/NbEchAn))-1,B56/NbEchAn),R55)</x:f>
       </x:c>
-      <x:c r="S56" s="70">
+      <x:c r="S56" s="74">
         <x:f>IF(E56&gt;0,E56,IF(D56&gt;0,IF(AND(EchFIXE,R56&gt;0),ROUND((L56-C56)*R56/(1-((1+R56)^-D56)),NbDeci),ROUND(L56/D56,NbDeci)),S55))</x:f>
       </x:c>
     </x:row>
@@ -7693,10 +7695,10 @@
         <x:f>SUM(M57:O57)</x:f>
       </x:c>
       <x:c r="Q57" s="0"/>
-      <x:c r="R57" s="71">
+      <x:c r="R57" s="75">
         <x:f>IF(B57&gt;0,IF(TauxActuariel,((B57+1)^(1/NbEchAn))-1,B57/NbEchAn),R56)</x:f>
       </x:c>
-      <x:c r="S57" s="70">
+      <x:c r="S57" s="74">
         <x:f>IF(E57&gt;0,E57,IF(D57&gt;0,IF(AND(EchFIXE,R57&gt;0),ROUND((L57-C57)*R57/(1-((1+R57)^-D57)),NbDeci),ROUND(L57/D57,NbDeci)),S56))</x:f>
       </x:c>
     </x:row>
@@ -7734,10 +7736,10 @@
         <x:f>SUM(M58:O58)</x:f>
       </x:c>
       <x:c r="Q58" s="0"/>
-      <x:c r="R58" s="71">
+      <x:c r="R58" s="75">
         <x:f>IF(B58&gt;0,IF(TauxActuariel,((B58+1)^(1/NbEchAn))-1,B58/NbEchAn),R57)</x:f>
       </x:c>
-      <x:c r="S58" s="70">
+      <x:c r="S58" s="74">
         <x:f>IF(E58&gt;0,E58,IF(D58&gt;0,IF(AND(EchFIXE,R58&gt;0),ROUND((L58-C58)*R58/(1-((1+R58)^-D58)),NbDeci),ROUND(L58/D58,NbDeci)),S57))</x:f>
       </x:c>
     </x:row>
@@ -7775,10 +7777,10 @@
         <x:f>SUM(M59:O59)</x:f>
       </x:c>
       <x:c r="Q59" s="0"/>
-      <x:c r="R59" s="71">
+      <x:c r="R59" s="75">
         <x:f>IF(B59&gt;0,IF(TauxActuariel,((B59+1)^(1/NbEchAn))-1,B59/NbEchAn),R58)</x:f>
       </x:c>
-      <x:c r="S59" s="70">
+      <x:c r="S59" s="74">
         <x:f>IF(E59&gt;0,E59,IF(D59&gt;0,IF(AND(EchFIXE,R59&gt;0),ROUND((L59-C59)*R59/(1-((1+R59)^-D59)),NbDeci),ROUND(L59/D59,NbDeci)),S58))</x:f>
       </x:c>
     </x:row>
@@ -7816,10 +7818,10 @@
         <x:f>SUM(M60:O60)</x:f>
       </x:c>
       <x:c r="Q60" s="0"/>
-      <x:c r="R60" s="71">
+      <x:c r="R60" s="75">
         <x:f>IF(B60&gt;0,IF(TauxActuariel,((B60+1)^(1/NbEchAn))-1,B60/NbEchAn),R59)</x:f>
       </x:c>
-      <x:c r="S60" s="70">
+      <x:c r="S60" s="74">
         <x:f>IF(E60&gt;0,E60,IF(D60&gt;0,IF(AND(EchFIXE,R60&gt;0),ROUND((L60-C60)*R60/(1-((1+R60)^-D60)),NbDeci),ROUND(L60/D60,NbDeci)),S59))</x:f>
       </x:c>
     </x:row>
@@ -7857,10 +7859,10 @@
         <x:f>SUM(M61:O61)</x:f>
       </x:c>
       <x:c r="Q61" s="0"/>
-      <x:c r="R61" s="71">
+      <x:c r="R61" s="75">
         <x:f>IF(B61&gt;0,IF(TauxActuariel,((B61+1)^(1/NbEchAn))-1,B61/NbEchAn),R60)</x:f>
       </x:c>
-      <x:c r="S61" s="70">
+      <x:c r="S61" s="74">
         <x:f>IF(E61&gt;0,E61,IF(D61&gt;0,IF(AND(EchFIXE,R61&gt;0),ROUND((L61-C61)*R61/(1-((1+R61)^-D61)),NbDeci),ROUND(L61/D61,NbDeci)),S60))</x:f>
       </x:c>
     </x:row>
@@ -7898,10 +7900,10 @@
         <x:f>SUM(M62:O62)</x:f>
       </x:c>
       <x:c r="Q62" s="0"/>
-      <x:c r="R62" s="71">
+      <x:c r="R62" s="75">
         <x:f>IF(B62&gt;0,IF(TauxActuariel,((B62+1)^(1/NbEchAn))-1,B62/NbEchAn),R61)</x:f>
       </x:c>
-      <x:c r="S62" s="70">
+      <x:c r="S62" s="74">
         <x:f>IF(E62&gt;0,E62,IF(D62&gt;0,IF(AND(EchFIXE,R62&gt;0),ROUND((L62-C62)*R62/(1-((1+R62)^-D62)),NbDeci),ROUND(L62/D62,NbDeci)),S61))</x:f>
       </x:c>
     </x:row>
@@ -7939,10 +7941,10 @@
         <x:f>SUM(M63:O63)</x:f>
       </x:c>
       <x:c r="Q63" s="0"/>
-      <x:c r="R63" s="71">
+      <x:c r="R63" s="75">
         <x:f>IF(B63&gt;0,IF(TauxActuariel,((B63+1)^(1/NbEchAn))-1,B63/NbEchAn),R62)</x:f>
       </x:c>
-      <x:c r="S63" s="70">
+      <x:c r="S63" s="74">
         <x:f>IF(E63&gt;0,E63,IF(D63&gt;0,IF(AND(EchFIXE,R63&gt;0),ROUND((L63-C63)*R63/(1-((1+R63)^-D63)),NbDeci),ROUND(L63/D63,NbDeci)),S62))</x:f>
       </x:c>
     </x:row>
@@ -7980,10 +7982,10 @@
         <x:f>SUM(M64:O64)</x:f>
       </x:c>
       <x:c r="Q64" s="0"/>
-      <x:c r="R64" s="71">
+      <x:c r="R64" s="75">
         <x:f>IF(B64&gt;0,IF(TauxActuariel,((B64+1)^(1/NbEchAn))-1,B64/NbEchAn),R63)</x:f>
       </x:c>
-      <x:c r="S64" s="70">
+      <x:c r="S64" s="74">
         <x:f>IF(E64&gt;0,E64,IF(D64&gt;0,IF(AND(EchFIXE,R64&gt;0),ROUND((L64-C64)*R64/(1-((1+R64)^-D64)),NbDeci),ROUND(L64/D64,NbDeci)),S63))</x:f>
       </x:c>
     </x:row>
@@ -8021,10 +8023,10 @@
         <x:f>SUM(M65:O65)</x:f>
       </x:c>
       <x:c r="Q65" s="0"/>
-      <x:c r="R65" s="71">
+      <x:c r="R65" s="75">
         <x:f>IF(B65&gt;0,IF(TauxActuariel,((B65+1)^(1/NbEchAn))-1,B65/NbEchAn),R64)</x:f>
       </x:c>
-      <x:c r="S65" s="70">
+      <x:c r="S65" s="74">
         <x:f>IF(E65&gt;0,E65,IF(D65&gt;0,IF(AND(EchFIXE,R65&gt;0),ROUND((L65-C65)*R65/(1-((1+R65)^-D65)),NbDeci),ROUND(L65/D65,NbDeci)),S64))</x:f>
       </x:c>
     </x:row>
@@ -8062,10 +8064,10 @@
         <x:f>SUM(M66:O66)</x:f>
       </x:c>
       <x:c r="Q66" s="0"/>
-      <x:c r="R66" s="71">
+      <x:c r="R66" s="75">
         <x:f>IF(B66&gt;0,IF(TauxActuariel,((B66+1)^(1/NbEchAn))-1,B66/NbEchAn),R65)</x:f>
       </x:c>
-      <x:c r="S66" s="70">
+      <x:c r="S66" s="74">
         <x:f>IF(E66&gt;0,E66,IF(D66&gt;0,IF(AND(EchFIXE,R66&gt;0),ROUND((L66-C66)*R66/(1-((1+R66)^-D66)),NbDeci),ROUND(L66/D66,NbDeci)),S65))</x:f>
       </x:c>
     </x:row>
@@ -8103,10 +8105,10 @@
         <x:f>SUM(M67:O67)</x:f>
       </x:c>
       <x:c r="Q67" s="0"/>
-      <x:c r="R67" s="71">
+      <x:c r="R67" s="75">
         <x:f>IF(B67&gt;0,IF(TauxActuariel,((B67+1)^(1/NbEchAn))-1,B67/NbEchAn),R66)</x:f>
       </x:c>
-      <x:c r="S67" s="70">
+      <x:c r="S67" s="74">
         <x:f>IF(E67&gt;0,E67,IF(D67&gt;0,IF(AND(EchFIXE,R67&gt;0),ROUND((L67-C67)*R67/(1-((1+R67)^-D67)),NbDeci),ROUND(L67/D67,NbDeci)),S66))</x:f>
       </x:c>
     </x:row>
@@ -8144,10 +8146,10 @@
         <x:f>SUM(M68:O68)</x:f>
       </x:c>
       <x:c r="Q68" s="0"/>
-      <x:c r="R68" s="71">
+      <x:c r="R68" s="75">
         <x:f>IF(B68&gt;0,IF(TauxActuariel,((B68+1)^(1/NbEchAn))-1,B68/NbEchAn),R67)</x:f>
       </x:c>
-      <x:c r="S68" s="70">
+      <x:c r="S68" s="74">
         <x:f>IF(E68&gt;0,E68,IF(D68&gt;0,IF(AND(EchFIXE,R68&gt;0),ROUND((L68-C68)*R68/(1-((1+R68)^-D68)),NbDeci),ROUND(L68/D68,NbDeci)),S67))</x:f>
       </x:c>
     </x:row>
@@ -8185,10 +8187,10 @@
         <x:f>SUM(M69:O69)</x:f>
       </x:c>
       <x:c r="Q69" s="0"/>
-      <x:c r="R69" s="71">
+      <x:c r="R69" s="75">
         <x:f>IF(B69&gt;0,IF(TauxActuariel,((B69+1)^(1/NbEchAn))-1,B69/NbEchAn),R68)</x:f>
       </x:c>
-      <x:c r="S69" s="70">
+      <x:c r="S69" s="74">
         <x:f>IF(E69&gt;0,E69,IF(D69&gt;0,IF(AND(EchFIXE,R69&gt;0),ROUND((L69-C69)*R69/(1-((1+R69)^-D69)),NbDeci),ROUND(L69/D69,NbDeci)),S68))</x:f>
       </x:c>
     </x:row>
@@ -8226,10 +8228,10 @@
         <x:f>SUM(M70:O70)</x:f>
       </x:c>
       <x:c r="Q70" s="0"/>
-      <x:c r="R70" s="71">
+      <x:c r="R70" s="75">
         <x:f>IF(B70&gt;0,IF(TauxActuariel,((B70+1)^(1/NbEchAn))-1,B70/NbEchAn),R69)</x:f>
       </x:c>
-      <x:c r="S70" s="70">
+      <x:c r="S70" s="74">
         <x:f>IF(E70&gt;0,E70,IF(D70&gt;0,IF(AND(EchFIXE,R70&gt;0),ROUND((L70-C70)*R70/(1-((1+R70)^-D70)),NbDeci),ROUND(L70/D70,NbDeci)),S69))</x:f>
       </x:c>
     </x:row>
@@ -8267,10 +8269,10 @@
         <x:f>SUM(M71:O71)</x:f>
       </x:c>
       <x:c r="Q71" s="0"/>
-      <x:c r="R71" s="71">
+      <x:c r="R71" s="75">
         <x:f>IF(B71&gt;0,IF(TauxActuariel,((B71+1)^(1/NbEchAn))-1,B71/NbEchAn),R70)</x:f>
       </x:c>
-      <x:c r="S71" s="70">
+      <x:c r="S71" s="74">
         <x:f>IF(E71&gt;0,E71,IF(D71&gt;0,IF(AND(EchFIXE,R71&gt;0),ROUND((L71-C71)*R71/(1-((1+R71)^-D71)),NbDeci),ROUND(L71/D71,NbDeci)),S70))</x:f>
       </x:c>
     </x:row>
@@ -8308,10 +8310,10 @@
         <x:f>SUM(M72:O72)</x:f>
       </x:c>
       <x:c r="Q72" s="0"/>
-      <x:c r="R72" s="71">
+      <x:c r="R72" s="75">
         <x:f>IF(B72&gt;0,IF(TauxActuariel,((B72+1)^(1/NbEchAn))-1,B72/NbEchAn),R71)</x:f>
       </x:c>
-      <x:c r="S72" s="70">
+      <x:c r="S72" s="74">
         <x:f>IF(E72&gt;0,E72,IF(D72&gt;0,IF(AND(EchFIXE,R72&gt;0),ROUND((L72-C72)*R72/(1-((1+R72)^-D72)),NbDeci),ROUND(L72/D72,NbDeci)),S71))</x:f>
       </x:c>
     </x:row>
@@ -8349,10 +8351,10 @@
         <x:f>SUM(M73:O73)</x:f>
       </x:c>
       <x:c r="Q73" s="0"/>
-      <x:c r="R73" s="71">
+      <x:c r="R73" s="75">
         <x:f>IF(B73&gt;0,IF(TauxActuariel,((B73+1)^(1/NbEchAn))-1,B73/NbEchAn),R72)</x:f>
       </x:c>
-      <x:c r="S73" s="70">
+      <x:c r="S73" s="74">
         <x:f>IF(E73&gt;0,E73,IF(D73&gt;0,IF(AND(EchFIXE,R73&gt;0),ROUND((L73-C73)*R73/(1-((1+R73)^-D73)),NbDeci),ROUND(L73/D73,NbDeci)),S72))</x:f>
       </x:c>
     </x:row>
@@ -8390,10 +8392,10 @@
         <x:f>SUM(M74:O74)</x:f>
       </x:c>
       <x:c r="Q74" s="0"/>
-      <x:c r="R74" s="71">
+      <x:c r="R74" s="75">
         <x:f>IF(B74&gt;0,IF(TauxActuariel,((B74+1)^(1/NbEchAn))-1,B74/NbEchAn),R73)</x:f>
       </x:c>
-      <x:c r="S74" s="70">
+      <x:c r="S74" s="74">
         <x:f>IF(E74&gt;0,E74,IF(D74&gt;0,IF(AND(EchFIXE,R74&gt;0),ROUND((L74-C74)*R74/(1-((1+R74)^-D74)),NbDeci),ROUND(L74/D74,NbDeci)),S73))</x:f>
       </x:c>
     </x:row>
@@ -8431,10 +8433,10 @@
         <x:f>SUM(M75:O75)</x:f>
       </x:c>
       <x:c r="Q75" s="0"/>
-      <x:c r="R75" s="71">
+      <x:c r="R75" s="75">
         <x:f>IF(B75&gt;0,IF(TauxActuariel,((B75+1)^(1/NbEchAn))-1,B75/NbEchAn),R74)</x:f>
       </x:c>
-      <x:c r="S75" s="70">
+      <x:c r="S75" s="74">
         <x:f>IF(E75&gt;0,E75,IF(D75&gt;0,IF(AND(EchFIXE,R75&gt;0),ROUND((L75-C75)*R75/(1-((1+R75)^-D75)),NbDeci),ROUND(L75/D75,NbDeci)),S74))</x:f>
       </x:c>
     </x:row>
@@ -8472,10 +8474,10 @@
         <x:f>SUM(M76:O76)</x:f>
       </x:c>
       <x:c r="Q76" s="0"/>
-      <x:c r="R76" s="71">
+      <x:c r="R76" s="75">
         <x:f>IF(B76&gt;0,IF(TauxActuariel,((B76+1)^(1/NbEchAn))-1,B76/NbEchAn),R75)</x:f>
       </x:c>
-      <x:c r="S76" s="70">
+      <x:c r="S76" s="74">
         <x:f>IF(E76&gt;0,E76,IF(D76&gt;0,IF(AND(EchFIXE,R76&gt;0),ROUND((L76-C76)*R76/(1-((1+R76)^-D76)),NbDeci),ROUND(L76/D76,NbDeci)),S75))</x:f>
       </x:c>
     </x:row>
@@ -8513,10 +8515,10 @@
         <x:f>SUM(M77:O77)</x:f>
       </x:c>
       <x:c r="Q77" s="0"/>
-      <x:c r="R77" s="71">
+      <x:c r="R77" s="75">
         <x:f>IF(B77&gt;0,IF(TauxActuariel,((B77+1)^(1/NbEchAn))-1,B77/NbEchAn),R76)</x:f>
       </x:c>
-      <x:c r="S77" s="70">
+      <x:c r="S77" s="74">
         <x:f>IF(E77&gt;0,E77,IF(D77&gt;0,IF(AND(EchFIXE,R77&gt;0),ROUND((L77-C77)*R77/(1-((1+R77)^-D77)),NbDeci),ROUND(L77/D77,NbDeci)),S76))</x:f>
       </x:c>
     </x:row>
@@ -8554,10 +8556,10 @@
         <x:f>SUM(M78:O78)</x:f>
       </x:c>
       <x:c r="Q78" s="0"/>
-      <x:c r="R78" s="71">
+      <x:c r="R78" s="75">
         <x:f>IF(B78&gt;0,IF(TauxActuariel,((B78+1)^(1/NbEchAn))-1,B78/NbEchAn),R77)</x:f>
       </x:c>
-      <x:c r="S78" s="70">
+      <x:c r="S78" s="74">
         <x:f>IF(E78&gt;0,E78,IF(D78&gt;0,IF(AND(EchFIXE,R78&gt;0),ROUND((L78-C78)*R78/(1-((1+R78)^-D78)),NbDeci),ROUND(L78/D78,NbDeci)),S77))</x:f>
       </x:c>
     </x:row>
@@ -8595,10 +8597,10 @@
         <x:f>SUM(M79:O79)</x:f>
       </x:c>
       <x:c r="Q79" s="0"/>
-      <x:c r="R79" s="71">
+      <x:c r="R79" s="75">
         <x:f>IF(B79&gt;0,IF(TauxActuariel,((B79+1)^(1/NbEchAn))-1,B79/NbEchAn),R78)</x:f>
       </x:c>
-      <x:c r="S79" s="70">
+      <x:c r="S79" s="74">
         <x:f>IF(E79&gt;0,E79,IF(D79&gt;0,IF(AND(EchFIXE,R79&gt;0),ROUND((L79-C79)*R79/(1-((1+R79)^-D79)),NbDeci),ROUND(L79/D79,NbDeci)),S78))</x:f>
       </x:c>
     </x:row>
@@ -8636,10 +8638,10 @@
         <x:f>SUM(M80:O80)</x:f>
       </x:c>
       <x:c r="Q80" s="0"/>
-      <x:c r="R80" s="71">
+      <x:c r="R80" s="75">
         <x:f>IF(B80&gt;0,IF(TauxActuariel,((B80+1)^(1/NbEchAn))-1,B80/NbEchAn),R79)</x:f>
       </x:c>
-      <x:c r="S80" s="70">
+      <x:c r="S80" s="74">
         <x:f>IF(E80&gt;0,E80,IF(D80&gt;0,IF(AND(EchFIXE,R80&gt;0),ROUND((L80-C80)*R80/(1-((1+R80)^-D80)),NbDeci),ROUND(L80/D80,NbDeci)),S79))</x:f>
       </x:c>
     </x:row>
@@ -8677,10 +8679,10 @@
         <x:f>SUM(M81:O81)</x:f>
       </x:c>
       <x:c r="Q81" s="0"/>
-      <x:c r="R81" s="71">
+      <x:c r="R81" s="75">
         <x:f>IF(B81&gt;0,IF(TauxActuariel,((B81+1)^(1/NbEchAn))-1,B81/NbEchAn),R80)</x:f>
       </x:c>
-      <x:c r="S81" s="70">
+      <x:c r="S81" s="74">
         <x:f>IF(E81&gt;0,E81,IF(D81&gt;0,IF(AND(EchFIXE,R81&gt;0),ROUND((L81-C81)*R81/(1-((1+R81)^-D81)),NbDeci),ROUND(L81/D81,NbDeci)),S80))</x:f>
       </x:c>
     </x:row>
@@ -8718,10 +8720,10 @@
         <x:f>SUM(M82:O82)</x:f>
       </x:c>
       <x:c r="Q82" s="0"/>
-      <x:c r="R82" s="71">
+      <x:c r="R82" s="75">
         <x:f>IF(B82&gt;0,IF(TauxActuariel,((B82+1)^(1/NbEchAn))-1,B82/NbEchAn),R81)</x:f>
       </x:c>
-      <x:c r="S82" s="70">
+      <x:c r="S82" s="74">
         <x:f>IF(E82&gt;0,E82,IF(D82&gt;0,IF(AND(EchFIXE,R82&gt;0),ROUND((L82-C82)*R82/(1-((1+R82)^-D82)),NbDeci),ROUND(L82/D82,NbDeci)),S81))</x:f>
       </x:c>
     </x:row>
@@ -8759,10 +8761,10 @@
         <x:f>SUM(M83:O83)</x:f>
       </x:c>
       <x:c r="Q83" s="0"/>
-      <x:c r="R83" s="71">
+      <x:c r="R83" s="75">
         <x:f>IF(B83&gt;0,IF(TauxActuariel,((B83+1)^(1/NbEchAn))-1,B83/NbEchAn),R82)</x:f>
       </x:c>
-      <x:c r="S83" s="70">
+      <x:c r="S83" s="74">
         <x:f>IF(E83&gt;0,E83,IF(D83&gt;0,IF(AND(EchFIXE,R83&gt;0),ROUND((L83-C83)*R83/(1-((1+R83)^-D83)),NbDeci),ROUND(L83/D83,NbDeci)),S82))</x:f>
       </x:c>
     </x:row>
@@ -8800,10 +8802,10 @@
         <x:f>SUM(M84:O84)</x:f>
       </x:c>
       <x:c r="Q84" s="0"/>
-      <x:c r="R84" s="71">
+      <x:c r="R84" s="75">
         <x:f>IF(B84&gt;0,IF(TauxActuariel,((B84+1)^(1/NbEchAn))-1,B84/NbEchAn),R83)</x:f>
       </x:c>
-      <x:c r="S84" s="70">
+      <x:c r="S84" s="74">
         <x:f>IF(E84&gt;0,E84,IF(D84&gt;0,IF(AND(EchFIXE,R84&gt;0),ROUND((L84-C84)*R84/(1-((1+R84)^-D84)),NbDeci),ROUND(L84/D84,NbDeci)),S83))</x:f>
       </x:c>
     </x:row>
@@ -8841,10 +8843,10 @@
         <x:f>SUM(M85:O85)</x:f>
       </x:c>
       <x:c r="Q85" s="0"/>
-      <x:c r="R85" s="71">
+      <x:c r="R85" s="75">
         <x:f>IF(B85&gt;0,IF(TauxActuariel,((B85+1)^(1/NbEchAn))-1,B85/NbEchAn),R84)</x:f>
       </x:c>
-      <x:c r="S85" s="70">
+      <x:c r="S85" s="74">
         <x:f>IF(E85&gt;0,E85,IF(D85&gt;0,IF(AND(EchFIXE,R85&gt;0),ROUND((L85-C85)*R85/(1-((1+R85)^-D85)),NbDeci),ROUND(L85/D85,NbDeci)),S84))</x:f>
       </x:c>
     </x:row>
@@ -8882,10 +8884,10 @@
         <x:f>SUM(M86:O86)</x:f>
       </x:c>
       <x:c r="Q86" s="0"/>
-      <x:c r="R86" s="71">
+      <x:c r="R86" s="75">
         <x:f>IF(B86&gt;0,IF(TauxActuariel,((B86+1)^(1/NbEchAn))-1,B86/NbEchAn),R85)</x:f>
       </x:c>
-      <x:c r="S86" s="70">
+      <x:c r="S86" s="74">
         <x:f>IF(E86&gt;0,E86,IF(D86&gt;0,IF(AND(EchFIXE,R86&gt;0),ROUND((L86-C86)*R86/(1-((1+R86)^-D86)),NbDeci),ROUND(L86/D86,NbDeci)),S85))</x:f>
       </x:c>
     </x:row>
@@ -8923,10 +8925,10 @@
         <x:f>SUM(M87:O87)</x:f>
       </x:c>
       <x:c r="Q87" s="0"/>
-      <x:c r="R87" s="71">
+      <x:c r="R87" s="75">
         <x:f>IF(B87&gt;0,IF(TauxActuariel,((B87+1)^(1/NbEchAn))-1,B87/NbEchAn),R86)</x:f>
       </x:c>
-      <x:c r="S87" s="70">
+      <x:c r="S87" s="74">
         <x:f>IF(E87&gt;0,E87,IF(D87&gt;0,IF(AND(EchFIXE,R87&gt;0),ROUND((L87-C87)*R87/(1-((1+R87)^-D87)),NbDeci),ROUND(L87/D87,NbDeci)),S86))</x:f>
       </x:c>
     </x:row>
@@ -8964,10 +8966,10 @@
         <x:f>SUM(M88:O88)</x:f>
       </x:c>
       <x:c r="Q88" s="0"/>
-      <x:c r="R88" s="71">
+      <x:c r="R88" s="75">
         <x:f>IF(B88&gt;0,IF(TauxActuariel,((B88+1)^(1/NbEchAn))-1,B88/NbEchAn),R87)</x:f>
       </x:c>
-      <x:c r="S88" s="70">
+      <x:c r="S88" s="74">
         <x:f>IF(E88&gt;0,E88,IF(D88&gt;0,IF(AND(EchFIXE,R88&gt;0),ROUND((L88-C88)*R88/(1-((1+R88)^-D88)),NbDeci),ROUND(L88/D88,NbDeci)),S87))</x:f>
       </x:c>
     </x:row>
@@ -9005,10 +9007,10 @@
         <x:f>SUM(M89:O89)</x:f>
       </x:c>
       <x:c r="Q89" s="0"/>
-      <x:c r="R89" s="71">
+      <x:c r="R89" s="75">
         <x:f>IF(B89&gt;0,IF(TauxActuariel,((B89+1)^(1/NbEchAn))-1,B89/NbEchAn),R88)</x:f>
       </x:c>
-      <x:c r="S89" s="70">
+      <x:c r="S89" s="74">
         <x:f>IF(E89&gt;0,E89,IF(D89&gt;0,IF(AND(EchFIXE,R89&gt;0),ROUND((L89-C89)*R89/(1-((1+R89)^-D89)),NbDeci),ROUND(L89/D89,NbDeci)),S88))</x:f>
       </x:c>
     </x:row>
@@ -9046,10 +9048,10 @@
         <x:f>SUM(M90:O90)</x:f>
       </x:c>
       <x:c r="Q90" s="0"/>
-      <x:c r="R90" s="71">
+      <x:c r="R90" s="75">
         <x:f>IF(B90&gt;0,IF(TauxActuariel,((B90+1)^(1/NbEchAn))-1,B90/NbEchAn),R89)</x:f>
       </x:c>
-      <x:c r="S90" s="70">
+      <x:c r="S90" s="74">
         <x:f>IF(E90&gt;0,E90,IF(D90&gt;0,IF(AND(EchFIXE,R90&gt;0),ROUND((L90-C90)*R90/(1-((1+R90)^-D90)),NbDeci),ROUND(L90/D90,NbDeci)),S89))</x:f>
       </x:c>
     </x:row>
@@ -9087,10 +9089,10 @@
         <x:f>SUM(M91:O91)</x:f>
       </x:c>
       <x:c r="Q91" s="0"/>
-      <x:c r="R91" s="71">
+      <x:c r="R91" s="75">
         <x:f>IF(B91&gt;0,IF(TauxActuariel,((B91+1)^(1/NbEchAn))-1,B91/NbEchAn),R90)</x:f>
       </x:c>
-      <x:c r="S91" s="70">
+      <x:c r="S91" s="74">
         <x:f>IF(E91&gt;0,E91,IF(D91&gt;0,IF(AND(EchFIXE,R91&gt;0),ROUND((L91-C91)*R91/(1-((1+R91)^-D91)),NbDeci),ROUND(L91/D91,NbDeci)),S90))</x:f>
       </x:c>
     </x:row>
@@ -9128,10 +9130,10 @@
         <x:f>SUM(M92:O92)</x:f>
       </x:c>
       <x:c r="Q92" s="0"/>
-      <x:c r="R92" s="71">
+      <x:c r="R92" s="75">
         <x:f>IF(B92&gt;0,IF(TauxActuariel,((B92+1)^(1/NbEchAn))-1,B92/NbEchAn),R91)</x:f>
       </x:c>
-      <x:c r="S92" s="70">
+      <x:c r="S92" s="74">
         <x:f>IF(E92&gt;0,E92,IF(D92&gt;0,IF(AND(EchFIXE,R92&gt;0),ROUND((L92-C92)*R92/(1-((1+R92)^-D92)),NbDeci),ROUND(L92/D92,NbDeci)),S91))</x:f>
       </x:c>
     </x:row>
@@ -9169,10 +9171,10 @@
         <x:f>SUM(M93:O93)</x:f>
       </x:c>
       <x:c r="Q93" s="0"/>
-      <x:c r="R93" s="71">
+      <x:c r="R93" s="75">
         <x:f>IF(B93&gt;0,IF(TauxActuariel,((B93+1)^(1/NbEchAn))-1,B93/NbEchAn),R92)</x:f>
       </x:c>
-      <x:c r="S93" s="70">
+      <x:c r="S93" s="74">
         <x:f>IF(E93&gt;0,E93,IF(D93&gt;0,IF(AND(EchFIXE,R93&gt;0),ROUND((L93-C93)*R93/(1-((1+R93)^-D93)),NbDeci),ROUND(L93/D93,NbDeci)),S92))</x:f>
       </x:c>
     </x:row>
@@ -9210,10 +9212,10 @@
         <x:f>SUM(M94:O94)</x:f>
       </x:c>
       <x:c r="Q94" s="0"/>
-      <x:c r="R94" s="71">
+      <x:c r="R94" s="75">
         <x:f>IF(B94&gt;0,IF(TauxActuariel,((B94+1)^(1/NbEchAn))-1,B94/NbEchAn),R93)</x:f>
       </x:c>
-      <x:c r="S94" s="70">
+      <x:c r="S94" s="74">
         <x:f>IF(E94&gt;0,E94,IF(D94&gt;0,IF(AND(EchFIXE,R94&gt;0),ROUND((L94-C94)*R94/(1-((1+R94)^-D94)),NbDeci),ROUND(L94/D94,NbDeci)),S93))</x:f>
       </x:c>
     </x:row>
@@ -9251,10 +9253,10 @@
         <x:f>SUM(M95:O95)</x:f>
       </x:c>
       <x:c r="Q95" s="0"/>
-      <x:c r="R95" s="71">
+      <x:c r="R95" s="75">
         <x:f>IF(B95&gt;0,IF(TauxActuariel,((B95+1)^(1/NbEchAn))-1,B95/NbEchAn),R94)</x:f>
       </x:c>
-      <x:c r="S95" s="70">
+      <x:c r="S95" s="74">
         <x:f>IF(E95&gt;0,E95,IF(D95&gt;0,IF(AND(EchFIXE,R95&gt;0),ROUND((L95-C95)*R95/(1-((1+R95)^-D95)),NbDeci),ROUND(L95/D95,NbDeci)),S94))</x:f>
       </x:c>
     </x:row>
@@ -9292,10 +9294,10 @@
         <x:f>SUM(M96:O96)</x:f>
       </x:c>
       <x:c r="Q96" s="0"/>
-      <x:c r="R96" s="71">
+      <x:c r="R96" s="75">
         <x:f>IF(B96&gt;0,IF(TauxActuariel,((B96+1)^(1/NbEchAn))-1,B96/NbEchAn),R95)</x:f>
       </x:c>
-      <x:c r="S96" s="70">
+      <x:c r="S96" s="74">
         <x:f>IF(E96&gt;0,E96,IF(D96&gt;0,IF(AND(EchFIXE,R96&gt;0),ROUND((L96-C96)*R96/(1-((1+R96)^-D96)),NbDeci),ROUND(L96/D96,NbDeci)),S95))</x:f>
       </x:c>
     </x:row>
@@ -9333,10 +9335,10 @@
         <x:f>SUM(M97:O97)</x:f>
       </x:c>
       <x:c r="Q97" s="0"/>
-      <x:c r="R97" s="71">
+      <x:c r="R97" s="75">
         <x:f>IF(B97&gt;0,IF(TauxActuariel,((B97+1)^(1/NbEchAn))-1,B97/NbEchAn),R96)</x:f>
       </x:c>
-      <x:c r="S97" s="70">
+      <x:c r="S97" s="74">
         <x:f>IF(E97&gt;0,E97,IF(D97&gt;0,IF(AND(EchFIXE,R97&gt;0),ROUND((L97-C97)*R97/(1-((1+R97)^-D97)),NbDeci),ROUND(L97/D97,NbDeci)),S96))</x:f>
       </x:c>
     </x:row>
@@ -9374,10 +9376,10 @@
         <x:f>SUM(M98:O98)</x:f>
       </x:c>
       <x:c r="Q98" s="0"/>
-      <x:c r="R98" s="71">
+      <x:c r="R98" s="75">
         <x:f>IF(B98&gt;0,IF(TauxActuariel,((B98+1)^(1/NbEchAn))-1,B98/NbEchAn),R97)</x:f>
       </x:c>
-      <x:c r="S98" s="70">
+      <x:c r="S98" s="74">
         <x:f>IF(E98&gt;0,E98,IF(D98&gt;0,IF(AND(EchFIXE,R98&gt;0),ROUND((L98-C98)*R98/(1-((1+R98)^-D98)),NbDeci),ROUND(L98/D98,NbDeci)),S97))</x:f>
       </x:c>
     </x:row>
@@ -9415,10 +9417,10 @@
         <x:f>SUM(M99:O99)</x:f>
       </x:c>
       <x:c r="Q99" s="0"/>
-      <x:c r="R99" s="71">
+      <x:c r="R99" s="75">
         <x:f>IF(B99&gt;0,IF(TauxActuariel,((B99+1)^(1/NbEchAn))-1,B99/NbEchAn),R98)</x:f>
       </x:c>
-      <x:c r="S99" s="70">
+      <x:c r="S99" s="74">
         <x:f>IF(E99&gt;0,E99,IF(D99&gt;0,IF(AND(EchFIXE,R99&gt;0),ROUND((L99-C99)*R99/(1-((1+R99)^-D99)),NbDeci),ROUND(L99/D99,NbDeci)),S98))</x:f>
       </x:c>
     </x:row>
@@ -9456,10 +9458,10 @@
         <x:f>SUM(M100:O100)</x:f>
       </x:c>
       <x:c r="Q100" s="0"/>
-      <x:c r="R100" s="71">
+      <x:c r="R100" s="75">
         <x:f>IF(B100&gt;0,IF(TauxActuariel,((B100+1)^(1/NbEchAn))-1,B100/NbEchAn),R99)</x:f>
       </x:c>
-      <x:c r="S100" s="70">
+      <x:c r="S100" s="74">
         <x:f>IF(E100&gt;0,E100,IF(D100&gt;0,IF(AND(EchFIXE,R100&gt;0),ROUND((L100-C100)*R100/(1-((1+R100)^-D100)),NbDeci),ROUND(L100/D100,NbDeci)),S99))</x:f>
       </x:c>
     </x:row>
@@ -9497,10 +9499,10 @@
         <x:f>SUM(M101:O101)</x:f>
       </x:c>
       <x:c r="Q101" s="0"/>
-      <x:c r="R101" s="71">
+      <x:c r="R101" s="75">
         <x:f>IF(B101&gt;0,IF(TauxActuariel,((B101+1)^(1/NbEchAn))-1,B101/NbEchAn),R100)</x:f>
       </x:c>
-      <x:c r="S101" s="70">
+      <x:c r="S101" s="74">
         <x:f>IF(E101&gt;0,E101,IF(D101&gt;0,IF(AND(EchFIXE,R101&gt;0),ROUND((L101-C101)*R101/(1-((1+R101)^-D101)),NbDeci),ROUND(L101/D101,NbDeci)),S100))</x:f>
       </x:c>
     </x:row>
@@ -9538,10 +9540,10 @@
         <x:f>SUM(M102:O102)</x:f>
       </x:c>
       <x:c r="Q102" s="0"/>
-      <x:c r="R102" s="71">
+      <x:c r="R102" s="75">
         <x:f>IF(B102&gt;0,IF(TauxActuariel,((B102+1)^(1/NbEchAn))-1,B102/NbEchAn),R101)</x:f>
       </x:c>
-      <x:c r="S102" s="70">
+      <x:c r="S102" s="74">
         <x:f>IF(E102&gt;0,E102,IF(D102&gt;0,IF(AND(EchFIXE,R102&gt;0),ROUND((L102-C102)*R102/(1-((1+R102)^-D102)),NbDeci),ROUND(L102/D102,NbDeci)),S101))</x:f>
       </x:c>
     </x:row>
@@ -9579,10 +9581,10 @@
         <x:f>SUM(M103:O103)</x:f>
       </x:c>
       <x:c r="Q103" s="0"/>
-      <x:c r="R103" s="71">
+      <x:c r="R103" s="75">
         <x:f>IF(B103&gt;0,IF(TauxActuariel,((B103+1)^(1/NbEchAn))-1,B103/NbEchAn),R102)</x:f>
       </x:c>
-      <x:c r="S103" s="70">
+      <x:c r="S103" s="74">
         <x:f>IF(E103&gt;0,E103,IF(D103&gt;0,IF(AND(EchFIXE,R103&gt;0),ROUND((L103-C103)*R103/(1-((1+R103)^-D103)),NbDeci),ROUND(L103/D103,NbDeci)),S102))</x:f>
       </x:c>
     </x:row>
@@ -9620,10 +9622,10 @@
         <x:f>SUM(M104:O104)</x:f>
       </x:c>
       <x:c r="Q104" s="0"/>
-      <x:c r="R104" s="71">
+      <x:c r="R104" s="75">
         <x:f>IF(B104&gt;0,IF(TauxActuariel,((B104+1)^(1/NbEchAn))-1,B104/NbEchAn),R103)</x:f>
       </x:c>
-      <x:c r="S104" s="70">
+      <x:c r="S104" s="74">
         <x:f>IF(E104&gt;0,E104,IF(D104&gt;0,IF(AND(EchFIXE,R104&gt;0),ROUND((L104-C104)*R104/(1-((1+R104)^-D104)),NbDeci),ROUND(L104/D104,NbDeci)),S103))</x:f>
       </x:c>
     </x:row>
@@ -9661,10 +9663,10 @@
         <x:f>SUM(M105:O105)</x:f>
       </x:c>
       <x:c r="Q105" s="0"/>
-      <x:c r="R105" s="71">
+      <x:c r="R105" s="75">
         <x:f>IF(B105&gt;0,IF(TauxActuariel,((B105+1)^(1/NbEchAn))-1,B105/NbEchAn),R104)</x:f>
       </x:c>
-      <x:c r="S105" s="70">
+      <x:c r="S105" s="74">
         <x:f>IF(E105&gt;0,E105,IF(D105&gt;0,IF(AND(EchFIXE,R105&gt;0),ROUND((L105-C105)*R105/(1-((1+R105)^-D105)),NbDeci),ROUND(L105/D105,NbDeci)),S104))</x:f>
       </x:c>
     </x:row>
@@ -9702,10 +9704,10 @@
         <x:f>SUM(M106:O106)</x:f>
       </x:c>
       <x:c r="Q106" s="0"/>
-      <x:c r="R106" s="71">
+      <x:c r="R106" s="75">
         <x:f>IF(B106&gt;0,IF(TauxActuariel,((B106+1)^(1/NbEchAn))-1,B106/NbEchAn),R105)</x:f>
       </x:c>
-      <x:c r="S106" s="70">
+      <x:c r="S106" s="74">
         <x:f>IF(E106&gt;0,E106,IF(D106&gt;0,IF(AND(EchFIXE,R106&gt;0),ROUND((L106-C106)*R106/(1-((1+R106)^-D106)),NbDeci),ROUND(L106/D106,NbDeci)),S105))</x:f>
       </x:c>
     </x:row>
@@ -9743,10 +9745,10 @@
         <x:f>SUM(M107:O107)</x:f>
       </x:c>
       <x:c r="Q107" s="0"/>
-      <x:c r="R107" s="71">
+      <x:c r="R107" s="75">
         <x:f>IF(B107&gt;0,IF(TauxActuariel,((B107+1)^(1/NbEchAn))-1,B107/NbEchAn),R106)</x:f>
       </x:c>
-      <x:c r="S107" s="70">
+      <x:c r="S107" s="74">
         <x:f>IF(E107&gt;0,E107,IF(D107&gt;0,IF(AND(EchFIXE,R107&gt;0),ROUND((L107-C107)*R107/(1-((1+R107)^-D107)),NbDeci),ROUND(L107/D107,NbDeci)),S106))</x:f>
       </x:c>
     </x:row>
@@ -9784,10 +9786,10 @@
         <x:f>SUM(M108:O108)</x:f>
       </x:c>
       <x:c r="Q108" s="0"/>
-      <x:c r="R108" s="71">
+      <x:c r="R108" s="75">
         <x:f>IF(B108&gt;0,IF(TauxActuariel,((B108+1)^(1/NbEchAn))-1,B108/NbEchAn),R107)</x:f>
       </x:c>
-      <x:c r="S108" s="70">
+      <x:c r="S108" s="74">
         <x:f>IF(E108&gt;0,E108,IF(D108&gt;0,IF(AND(EchFIXE,R108&gt;0),ROUND((L108-C108)*R108/(1-((1+R108)^-D108)),NbDeci),ROUND(L108/D108,NbDeci)),S107))</x:f>
       </x:c>
     </x:row>
@@ -9825,10 +9827,10 @@
         <x:f>SUM(M109:O109)</x:f>
       </x:c>
       <x:c r="Q109" s="0"/>
-      <x:c r="R109" s="71">
+      <x:c r="R109" s="75">
         <x:f>IF(B109&gt;0,IF(TauxActuariel,((B109+1)^(1/NbEchAn))-1,B109/NbEchAn),R108)</x:f>
       </x:c>
-      <x:c r="S109" s="70">
+      <x:c r="S109" s="74">
         <x:f>IF(E109&gt;0,E109,IF(D109&gt;0,IF(AND(EchFIXE,R109&gt;0),ROUND((L109-C109)*R109/(1-((1+R109)^-D109)),NbDeci),ROUND(L109/D109,NbDeci)),S108))</x:f>
       </x:c>
     </x:row>
@@ -9866,10 +9868,10 @@
         <x:f>SUM(M110:O110)</x:f>
       </x:c>
       <x:c r="Q110" s="0"/>
-      <x:c r="R110" s="71">
+      <x:c r="R110" s="75">
         <x:f>IF(B110&gt;0,IF(TauxActuariel,((B110+1)^(1/NbEchAn))-1,B110/NbEchAn),R109)</x:f>
       </x:c>
-      <x:c r="S110" s="70">
+      <x:c r="S110" s="74">
         <x:f>IF(E110&gt;0,E110,IF(D110&gt;0,IF(AND(EchFIXE,R110&gt;0),ROUND((L110-C110)*R110/(1-((1+R110)^-D110)),NbDeci),ROUND(L110/D110,NbDeci)),S109))</x:f>
       </x:c>
     </x:row>
@@ -9907,10 +9909,10 @@
         <x:f>SUM(M111:O111)</x:f>
       </x:c>
       <x:c r="Q111" s="0"/>
-      <x:c r="R111" s="71">
+      <x:c r="R111" s="75">
         <x:f>IF(B111&gt;0,IF(TauxActuariel,((B111+1)^(1/NbEchAn))-1,B111/NbEchAn),R110)</x:f>
       </x:c>
-      <x:c r="S111" s="70">
+      <x:c r="S111" s="74">
         <x:f>IF(E111&gt;0,E111,IF(D111&gt;0,IF(AND(EchFIXE,R111&gt;0),ROUND((L111-C111)*R111/(1-((1+R111)^-D111)),NbDeci),ROUND(L111/D111,NbDeci)),S110))</x:f>
       </x:c>
     </x:row>
@@ -9948,10 +9950,10 @@
         <x:f>SUM(M112:O112)</x:f>
       </x:c>
       <x:c r="Q112" s="0"/>
-      <x:c r="R112" s="71">
+      <x:c r="R112" s="75">
         <x:f>IF(B112&gt;0,IF(TauxActuariel,((B112+1)^(1/NbEchAn))-1,B112/NbEchAn),R111)</x:f>
       </x:c>
-      <x:c r="S112" s="70">
+      <x:c r="S112" s="74">
         <x:f>IF(E112&gt;0,E112,IF(D112&gt;0,IF(AND(EchFIXE,R112&gt;0),ROUND((L112-C112)*R112/(1-((1+R112)^-D112)),NbDeci),ROUND(L112/D112,NbDeci)),S111))</x:f>
       </x:c>
     </x:row>
@@ -9989,10 +9991,10 @@
         <x:f>SUM(M113:O113)</x:f>
       </x:c>
       <x:c r="Q113" s="0"/>
-      <x:c r="R113" s="71">
+      <x:c r="R113" s="75">
         <x:f>IF(B113&gt;0,IF(TauxActuariel,((B113+1)^(1/NbEchAn))-1,B113/NbEchAn),R112)</x:f>
       </x:c>
-      <x:c r="S113" s="70">
+      <x:c r="S113" s="74">
         <x:f>IF(E113&gt;0,E113,IF(D113&gt;0,IF(AND(EchFIXE,R113&gt;0),ROUND((L113-C113)*R113/(1-((1+R113)^-D113)),NbDeci),ROUND(L113/D113,NbDeci)),S112))</x:f>
       </x:c>
     </x:row>
@@ -10030,10 +10032,10 @@
         <x:f>SUM(M114:O114)</x:f>
       </x:c>
       <x:c r="Q114" s="0"/>
-      <x:c r="R114" s="71">
+      <x:c r="R114" s="75">
         <x:f>IF(B114&gt;0,IF(TauxActuariel,((B114+1)^(1/NbEchAn))-1,B114/NbEchAn),R113)</x:f>
       </x:c>
-      <x:c r="S114" s="70">
+      <x:c r="S114" s="74">
         <x:f>IF(E114&gt;0,E114,IF(D114&gt;0,IF(AND(EchFIXE,R114&gt;0),ROUND((L114-C114)*R114/(1-((1+R114)^-D114)),NbDeci),ROUND(L114/D114,NbDeci)),S113))</x:f>
       </x:c>
     </x:row>
@@ -10071,10 +10073,10 @@
         <x:f>SUM(M115:O115)</x:f>
       </x:c>
       <x:c r="Q115" s="0"/>
-      <x:c r="R115" s="71">
+      <x:c r="R115" s="75">
         <x:f>IF(B115&gt;0,IF(TauxActuariel,((B115+1)^(1/NbEchAn))-1,B115/NbEchAn),R114)</x:f>
       </x:c>
-      <x:c r="S115" s="70">
+      <x:c r="S115" s="74">
         <x:f>IF(E115&gt;0,E115,IF(D115&gt;0,IF(AND(EchFIXE,R115&gt;0),ROUND((L115-C115)*R115/(1-((1+R115)^-D115)),NbDeci),ROUND(L115/D115,NbDeci)),S114))</x:f>
       </x:c>
     </x:row>
@@ -10112,10 +10114,10 @@
         <x:f>SUM(M116:O116)</x:f>
       </x:c>
       <x:c r="Q116" s="0"/>
-      <x:c r="R116" s="71">
+      <x:c r="R116" s="75">
         <x:f>IF(B116&gt;0,IF(TauxActuariel,((B116+1)^(1/NbEchAn))-1,B116/NbEchAn),R115)</x:f>
       </x:c>
-      <x:c r="S116" s="70">
+      <x:c r="S116" s="74">
         <x:f>IF(E116&gt;0,E116,IF(D116&gt;0,IF(AND(EchFIXE,R116&gt;0),ROUND((L116-C116)*R116/(1-((1+R116)^-D116)),NbDeci),ROUND(L116/D116,NbDeci)),S115))</x:f>
       </x:c>
     </x:row>
@@ -10153,10 +10155,10 @@
         <x:f>SUM(M117:O117)</x:f>
       </x:c>
       <x:c r="Q117" s="0"/>
-      <x:c r="R117" s="71">
+      <x:c r="R117" s="75">
         <x:f>IF(B117&gt;0,IF(TauxActuariel,((B117+1)^(1/NbEchAn))-1,B117/NbEchAn),R116)</x:f>
       </x:c>
-      <x:c r="S117" s="70">
+      <x:c r="S117" s="74">
         <x:f>IF(E117&gt;0,E117,IF(D117&gt;0,IF(AND(EchFIXE,R117&gt;0),ROUND((L117-C117)*R117/(1-((1+R117)^-D117)),NbDeci),ROUND(L117/D117,NbDeci)),S116))</x:f>
       </x:c>
     </x:row>
@@ -10194,10 +10196,10 @@
         <x:f>SUM(M118:O118)</x:f>
       </x:c>
       <x:c r="Q118" s="0"/>
-      <x:c r="R118" s="71">
+      <x:c r="R118" s="75">
         <x:f>IF(B118&gt;0,IF(TauxActuariel,((B118+1)^(1/NbEchAn))-1,B118/NbEchAn),R117)</x:f>
       </x:c>
-      <x:c r="S118" s="70">
+      <x:c r="S118" s="74">
         <x:f>IF(E118&gt;0,E118,IF(D118&gt;0,IF(AND(EchFIXE,R118&gt;0),ROUND((L118-C118)*R118/(1-((1+R118)^-D118)),NbDeci),ROUND(L118/D118,NbDeci)),S117))</x:f>
       </x:c>
     </x:row>
@@ -10235,10 +10237,10 @@
         <x:f>SUM(M119:O119)</x:f>
       </x:c>
       <x:c r="Q119" s="0"/>
-      <x:c r="R119" s="71">
+      <x:c r="R119" s="75">
         <x:f>IF(B119&gt;0,IF(TauxActuariel,((B119+1)^(1/NbEchAn))-1,B119/NbEchAn),R118)</x:f>
       </x:c>
-      <x:c r="S119" s="70">
+      <x:c r="S119" s="74">
         <x:f>IF(E119&gt;0,E119,IF(D119&gt;0,IF(AND(EchFIXE,R119&gt;0),ROUND((L119-C119)*R119/(1-((1+R119)^-D119)),NbDeci),ROUND(L119/D119,NbDeci)),S118))</x:f>
       </x:c>
     </x:row>
@@ -10276,10 +10278,10 @@
         <x:f>SUM(M120:O120)</x:f>
       </x:c>
       <x:c r="Q120" s="0"/>
-      <x:c r="R120" s="71">
+      <x:c r="R120" s="75">
         <x:f>IF(B120&gt;0,IF(TauxActuariel,((B120+1)^(1/NbEchAn))-1,B120/NbEchAn),R119)</x:f>
       </x:c>
-      <x:c r="S120" s="70">
+      <x:c r="S120" s="74">
         <x:f>IF(E120&gt;0,E120,IF(D120&gt;0,IF(AND(EchFIXE,R120&gt;0),ROUND((L120-C120)*R120/(1-((1+R120)^-D120)),NbDeci),ROUND(L120/D120,NbDeci)),S119))</x:f>
       </x:c>
     </x:row>
@@ -10317,10 +10319,10 @@
         <x:f>SUM(M121:O121)</x:f>
       </x:c>
       <x:c r="Q121" s="0"/>
-      <x:c r="R121" s="71">
+      <x:c r="R121" s="75">
         <x:f>IF(B121&gt;0,IF(TauxActuariel,((B121+1)^(1/NbEchAn))-1,B121/NbEchAn),R120)</x:f>
       </x:c>
-      <x:c r="S121" s="70">
+      <x:c r="S121" s="74">
         <x:f>IF(E121&gt;0,E121,IF(D121&gt;0,IF(AND(EchFIXE,R121&gt;0),ROUND((L121-C121)*R121/(1-((1+R121)^-D121)),NbDeci),ROUND(L121/D121,NbDeci)),S120))</x:f>
       </x:c>
     </x:row>
@@ -10358,10 +10360,10 @@
         <x:f>SUM(M122:O122)</x:f>
       </x:c>
       <x:c r="Q122" s="0"/>
-      <x:c r="R122" s="71">
+      <x:c r="R122" s="75">
         <x:f>IF(B122&gt;0,IF(TauxActuariel,((B122+1)^(1/NbEchAn))-1,B122/NbEchAn),R121)</x:f>
       </x:c>
-      <x:c r="S122" s="70">
+      <x:c r="S122" s="74">
         <x:f>IF(E122&gt;0,E122,IF(D122&gt;0,IF(AND(EchFIXE,R122&gt;0),ROUND((L122-C122)*R122/(1-((1+R122)^-D122)),NbDeci),ROUND(L122/D122,NbDeci)),S121))</x:f>
       </x:c>
     </x:row>
@@ -10399,10 +10401,10 @@
         <x:f>SUM(M123:O123)</x:f>
       </x:c>
       <x:c r="Q123" s="0"/>
-      <x:c r="R123" s="71">
+      <x:c r="R123" s="75">
         <x:f>IF(B123&gt;0,IF(TauxActuariel,((B123+1)^(1/NbEchAn))-1,B123/NbEchAn),R122)</x:f>
       </x:c>
-      <x:c r="S123" s="70">
+      <x:c r="S123" s="74">
         <x:f>IF(E123&gt;0,E123,IF(D123&gt;0,IF(AND(EchFIXE,R123&gt;0),ROUND((L123-C123)*R123/(1-((1+R123)^-D123)),NbDeci),ROUND(L123/D123,NbDeci)),S122))</x:f>
       </x:c>
     </x:row>
@@ -10440,10 +10442,10 @@
         <x:f>SUM(M124:O124)</x:f>
       </x:c>
       <x:c r="Q124" s="0"/>
-      <x:c r="R124" s="71">
+      <x:c r="R124" s="75">
         <x:f>IF(B124&gt;0,IF(TauxActuariel,((B124+1)^(1/NbEchAn))-1,B124/NbEchAn),R123)</x:f>
       </x:c>
-      <x:c r="S124" s="70">
+      <x:c r="S124" s="74">
         <x:f>IF(E124&gt;0,E124,IF(D124&gt;0,IF(AND(EchFIXE,R124&gt;0),ROUND((L124-C124)*R124/(1-((1+R124)^-D124)),NbDeci),ROUND(L124/D124,NbDeci)),S123))</x:f>
       </x:c>
     </x:row>
@@ -10481,10 +10483,10 @@
         <x:f>SUM(M125:O125)</x:f>
       </x:c>
       <x:c r="Q125" s="0"/>
-      <x:c r="R125" s="71">
+      <x:c r="R125" s="75">
         <x:f>IF(B125&gt;0,IF(TauxActuariel,((B125+1)^(1/NbEchAn))-1,B125/NbEchAn),R124)</x:f>
       </x:c>
-      <x:c r="S125" s="70">
+      <x:c r="S125" s="74">
         <x:f>IF(E125&gt;0,E125,IF(D125&gt;0,IF(AND(EchFIXE,R125&gt;0),ROUND((L125-C125)*R125/(1-((1+R125)^-D125)),NbDeci),ROUND(L125/D125,NbDeci)),S124))</x:f>
       </x:c>
     </x:row>
@@ -10522,10 +10524,10 @@
         <x:f>SUM(M126:O126)</x:f>
       </x:c>
       <x:c r="Q126" s="0"/>
-      <x:c r="R126" s="71">
+      <x:c r="R126" s="75">
         <x:f>IF(B126&gt;0,IF(TauxActuariel,((B126+1)^(1/NbEchAn))-1,B126/NbEchAn),R125)</x:f>
       </x:c>
-      <x:c r="S126" s="70">
+      <x:c r="S126" s="74">
         <x:f>IF(E126&gt;0,E126,IF(D126&gt;0,IF(AND(EchFIXE,R126&gt;0),ROUND((L126-C126)*R126/(1-((1+R126)^-D126)),NbDeci),ROUND(L126/D126,NbDeci)),S125))</x:f>
       </x:c>
     </x:row>
@@ -10563,10 +10565,10 @@
         <x:f>SUM(M127:O127)</x:f>
       </x:c>
       <x:c r="Q127" s="0"/>
-      <x:c r="R127" s="71">
+      <x:c r="R127" s="75">
         <x:f>IF(B127&gt;0,IF(TauxActuariel,((B127+1)^(1/NbEchAn))-1,B127/NbEchAn),R126)</x:f>
       </x:c>
-      <x:c r="S127" s="70">
+      <x:c r="S127" s="74">
         <x:f>IF(E127&gt;0,E127,IF(D127&gt;0,IF(AND(EchFIXE,R127&gt;0),ROUND((L127-C127)*R127/(1-((1+R127)^-D127)),NbDeci),ROUND(L127/D127,NbDeci)),S126))</x:f>
       </x:c>
     </x:row>
@@ -10604,10 +10606,10 @@
         <x:f>SUM(M128:O128)</x:f>
       </x:c>
       <x:c r="Q128" s="0"/>
-      <x:c r="R128" s="71">
+      <x:c r="R128" s="75">
         <x:f>IF(B128&gt;0,IF(TauxActuariel,((B128+1)^(1/NbEchAn))-1,B128/NbEchAn),R127)</x:f>
       </x:c>
-      <x:c r="S128" s="70">
+      <x:c r="S128" s="74">
         <x:f>IF(E128&gt;0,E128,IF(D128&gt;0,IF(AND(EchFIXE,R128&gt;0),ROUND((L128-C128)*R128/(1-((1+R128)^-D128)),NbDeci),ROUND(L128/D128,NbDeci)),S127))</x:f>
       </x:c>
     </x:row>
@@ -10645,10 +10647,10 @@
         <x:f>SUM(M129:O129)</x:f>
       </x:c>
       <x:c r="Q129" s="0"/>
-      <x:c r="R129" s="71">
+      <x:c r="R129" s="75">
         <x:f>IF(B129&gt;0,IF(TauxActuariel,((B129+1)^(1/NbEchAn))-1,B129/NbEchAn),R128)</x:f>
       </x:c>
-      <x:c r="S129" s="70">
+      <x:c r="S129" s="74">
         <x:f>IF(E129&gt;0,E129,IF(D129&gt;0,IF(AND(EchFIXE,R129&gt;0),ROUND((L129-C129)*R129/(1-((1+R129)^-D129)),NbDeci),ROUND(L129/D129,NbDeci)),S128))</x:f>
       </x:c>
     </x:row>
@@ -10686,10 +10688,10 @@
         <x:f>SUM(M130:O130)</x:f>
       </x:c>
       <x:c r="Q130" s="0"/>
-      <x:c r="R130" s="71">
+      <x:c r="R130" s="75">
         <x:f>IF(B130&gt;0,IF(TauxActuariel,((B130+1)^(1/NbEchAn))-1,B130/NbEchAn),R129)</x:f>
       </x:c>
-      <x:c r="S130" s="70">
+      <x:c r="S130" s="74">
         <x:f>IF(E130&gt;0,E130,IF(D130&gt;0,IF(AND(EchFIXE,R130&gt;0),ROUND((L130-C130)*R130/(1-((1+R130)^-D130)),NbDeci),ROUND(L130/D130,NbDeci)),S129))</x:f>
       </x:c>
     </x:row>
@@ -10727,10 +10729,10 @@
         <x:f>SUM(M131:O131)</x:f>
       </x:c>
       <x:c r="Q131" s="0"/>
-      <x:c r="R131" s="71">
+      <x:c r="R131" s="75">
         <x:f>IF(B131&gt;0,IF(TauxActuariel,((B131+1)^(1/NbEchAn))-1,B131/NbEchAn),R130)</x:f>
       </x:c>
-      <x:c r="S131" s="70">
+      <x:c r="S131" s="74">
         <x:f>IF(E131&gt;0,E131,IF(D131&gt;0,IF(AND(EchFIXE,R131&gt;0),ROUND((L131-C131)*R131/(1-((1+R131)^-D131)),NbDeci),ROUND(L131/D131,NbDeci)),S130))</x:f>
       </x:c>
     </x:row>
@@ -10768,10 +10770,10 @@
         <x:f>SUM(M132:O132)</x:f>
       </x:c>
       <x:c r="Q132" s="0"/>
-      <x:c r="R132" s="71">
+      <x:c r="R132" s="75">
         <x:f>IF(B132&gt;0,IF(TauxActuariel,((B132+1)^(1/NbEchAn))-1,B132/NbEchAn),R131)</x:f>
       </x:c>
-      <x:c r="S132" s="70">
+      <x:c r="S132" s="74">
         <x:f>IF(E132&gt;0,E132,IF(D132&gt;0,IF(AND(EchFIXE,R132&gt;0),ROUND((L132-C132)*R132/(1-((1+R132)^-D132)),NbDeci),ROUND(L132/D132,NbDeci)),S131))</x:f>
       </x:c>
     </x:row>
@@ -10809,10 +10811,10 @@
         <x:f>SUM(M133:O133)</x:f>
       </x:c>
       <x:c r="Q133" s="0"/>
-      <x:c r="R133" s="71">
+      <x:c r="R133" s="75">
         <x:f>IF(B133&gt;0,IF(TauxActuariel,((B133+1)^(1/NbEchAn))-1,B133/NbEchAn),R132)</x:f>
       </x:c>
-      <x:c r="S133" s="70">
+      <x:c r="S133" s="74">
         <x:f>IF(E133&gt;0,E133,IF(D133&gt;0,IF(AND(EchFIXE,R133&gt;0),ROUND((L133-C133)*R133/(1-((1+R133)^-D133)),NbDeci),ROUND(L133/D133,NbDeci)),S132))</x:f>
       </x:c>
     </x:row>
@@ -10850,10 +10852,10 @@
         <x:f>SUM(M134:O134)</x:f>
       </x:c>
       <x:c r="Q134" s="0"/>
-      <x:c r="R134" s="71">
+      <x:c r="R134" s="75">
         <x:f>IF(B134&gt;0,IF(TauxActuariel,((B134+1)^(1/NbEchAn))-1,B134/NbEchAn),R133)</x:f>
       </x:c>
-      <x:c r="S134" s="70">
+      <x:c r="S134" s="74">
         <x:f>IF(E134&gt;0,E134,IF(D134&gt;0,IF(AND(EchFIXE,R134&gt;0),ROUND((L134-C134)*R134/(1-((1+R134)^-D134)),NbDeci),ROUND(L134/D134,NbDeci)),S133))</x:f>
       </x:c>
     </x:row>
@@ -10891,10 +10893,10 @@
         <x:f>SUM(M135:O135)</x:f>
       </x:c>
       <x:c r="Q135" s="0"/>
-      <x:c r="R135" s="71">
+      <x:c r="R135" s="75">
         <x:f>IF(B135&gt;0,IF(TauxActuariel,((B135+1)^(1/NbEchAn))-1,B135/NbEchAn),R134)</x:f>
       </x:c>
-      <x:c r="S135" s="70">
+      <x:c r="S135" s="74">
         <x:f>IF(E135&gt;0,E135,IF(D135&gt;0,IF(AND(EchFIXE,R135&gt;0),ROUND((L135-C135)*R135/(1-((1+R135)^-D135)),NbDeci),ROUND(L135/D135,NbDeci)),S134))</x:f>
       </x:c>
     </x:row>
@@ -10932,10 +10934,10 @@
         <x:f>SUM(M136:O136)</x:f>
       </x:c>
       <x:c r="Q136" s="0"/>
-      <x:c r="R136" s="71">
+      <x:c r="R136" s="75">
         <x:f>IF(B136&gt;0,IF(TauxActuariel,((B136+1)^(1/NbEchAn))-1,B136/NbEchAn),R135)</x:f>
       </x:c>
-      <x:c r="S136" s="70">
+      <x:c r="S136" s="74">
         <x:f>IF(E136&gt;0,E136,IF(D136&gt;0,IF(AND(EchFIXE,R136&gt;0),ROUND((L136-C136)*R136/(1-((1+R136)^-D136)),NbDeci),ROUND(L136/D136,NbDeci)),S135))</x:f>
       </x:c>
     </x:row>
@@ -10973,10 +10975,10 @@
         <x:f>SUM(M137:O137)</x:f>
       </x:c>
       <x:c r="Q137" s="0"/>
-      <x:c r="R137" s="71">
+      <x:c r="R137" s="75">
         <x:f>IF(B137&gt;0,IF(TauxActuariel,((B137+1)^(1/NbEchAn))-1,B137/NbEchAn),R136)</x:f>
       </x:c>
-      <x:c r="S137" s="70">
+      <x:c r="S137" s="74">
         <x:f>IF(E137&gt;0,E137,IF(D137&gt;0,IF(AND(EchFIXE,R137&gt;0),ROUND((L137-C137)*R137/(1-((1+R137)^-D137)),NbDeci),ROUND(L137/D137,NbDeci)),S136))</x:f>
       </x:c>
     </x:row>
@@ -11014,10 +11016,10 @@
         <x:f>SUM(M138:O138)</x:f>
       </x:c>
       <x:c r="Q138" s="0"/>
-      <x:c r="R138" s="71">
+      <x:c r="R138" s="75">
         <x:f>IF(B138&gt;0,IF(TauxActuariel,((B138+1)^(1/NbEchAn))-1,B138/NbEchAn),R137)</x:f>
       </x:c>
-      <x:c r="S138" s="70">
+      <x:c r="S138" s="74">
         <x:f>IF(E138&gt;0,E138,IF(D138&gt;0,IF(AND(EchFIXE,R138&gt;0),ROUND((L138-C138)*R138/(1-((1+R138)^-D138)),NbDeci),ROUND(L138/D138,NbDeci)),S137))</x:f>
       </x:c>
     </x:row>
@@ -11055,10 +11057,10 @@
         <x:f>SUM(M139:O139)</x:f>
       </x:c>
       <x:c r="Q139" s="0"/>
-      <x:c r="R139" s="71">
+      <x:c r="R139" s="75">
         <x:f>IF(B139&gt;0,IF(TauxActuariel,((B139+1)^(1/NbEchAn))-1,B139/NbEchAn),R138)</x:f>
       </x:c>
-      <x:c r="S139" s="70">
+      <x:c r="S139" s="74">
         <x:f>IF(E139&gt;0,E139,IF(D139&gt;0,IF(AND(EchFIXE,R139&gt;0),ROUND((L139-C139)*R139/(1-((1+R139)^-D139)),NbDeci),ROUND(L139/D139,NbDeci)),S138))</x:f>
       </x:c>
     </x:row>
@@ -11096,10 +11098,10 @@
         <x:f>SUM(M140:O140)</x:f>
       </x:c>
       <x:c r="Q140" s="0"/>
-      <x:c r="R140" s="71">
+      <x:c r="R140" s="75">
         <x:f>IF(B140&gt;0,IF(TauxActuariel,((B140+1)^(1/NbEchAn))-1,B140/NbEchAn),R139)</x:f>
       </x:c>
-      <x:c r="S140" s="70">
+      <x:c r="S140" s="74">
         <x:f>IF(E140&gt;0,E140,IF(D140&gt;0,IF(AND(EchFIXE,R140&gt;0),ROUND((L140-C140)*R140/(1-((1+R140)^-D140)),NbDeci),ROUND(L140/D140,NbDeci)),S139))</x:f>
       </x:c>
     </x:row>
@@ -11137,10 +11139,10 @@
         <x:f>SUM(M141:O141)</x:f>
       </x:c>
       <x:c r="Q141" s="0"/>
-      <x:c r="R141" s="71">
+      <x:c r="R141" s="75">
         <x:f>IF(B141&gt;0,IF(TauxActuariel,((B141+1)^(1/NbEchAn))-1,B141/NbEchAn),R140)</x:f>
       </x:c>
-      <x:c r="S141" s="70">
+      <x:c r="S141" s="74">
         <x:f>IF(E141&gt;0,E141,IF(D141&gt;0,IF(AND(EchFIXE,R141&gt;0),ROUND((L141-C141)*R141/(1-((1+R141)^-D141)),NbDeci),ROUND(L141/D141,NbDeci)),S140))</x:f>
       </x:c>
     </x:row>
@@ -11178,10 +11180,10 @@
         <x:f>SUM(M142:O142)</x:f>
       </x:c>
       <x:c r="Q142" s="0"/>
-      <x:c r="R142" s="71">
+      <x:c r="R142" s="75">
         <x:f>IF(B142&gt;0,IF(TauxActuariel,((B142+1)^(1/NbEchAn))-1,B142/NbEchAn),R141)</x:f>
       </x:c>
-      <x:c r="S142" s="70">
+      <x:c r="S142" s="74">
         <x:f>IF(E142&gt;0,E142,IF(D142&gt;0,IF(AND(EchFIXE,R142&gt;0),ROUND((L142-C142)*R142/(1-((1+R142)^-D142)),NbDeci),ROUND(L142/D142,NbDeci)),S141))</x:f>
       </x:c>
     </x:row>
@@ -11219,10 +11221,10 @@
         <x:f>SUM(M143:O143)</x:f>
       </x:c>
       <x:c r="Q143" s="0"/>
-      <x:c r="R143" s="71">
+      <x:c r="R143" s="75">
         <x:f>IF(B143&gt;0,IF(TauxActuariel,((B143+1)^(1/NbEchAn))-1,B143/NbEchAn),R142)</x:f>
       </x:c>
-      <x:c r="S143" s="70">
+      <x:c r="S143" s="74">
         <x:f>IF(E143&gt;0,E143,IF(D143&gt;0,IF(AND(EchFIXE,R143&gt;0),ROUND((L143-C143)*R143/(1-((1+R143)^-D143)),NbDeci),ROUND(L143/D143,NbDeci)),S142))</x:f>
       </x:c>
     </x:row>
@@ -11260,10 +11262,10 @@
         <x:f>SUM(M144:O144)</x:f>
       </x:c>
       <x:c r="Q144" s="0"/>
-      <x:c r="R144" s="71">
+      <x:c r="R144" s="75">
         <x:f>IF(B144&gt;0,IF(TauxActuariel,((B144+1)^(1/NbEchAn))-1,B144/NbEchAn),R143)</x:f>
       </x:c>
-      <x:c r="S144" s="70">
+      <x:c r="S144" s="74">
         <x:f>IF(E144&gt;0,E144,IF(D144&gt;0,IF(AND(EchFIXE,R144&gt;0),ROUND((L144-C144)*R144/(1-((1+R144)^-D144)),NbDeci),ROUND(L144/D144,NbDeci)),S143))</x:f>
       </x:c>
     </x:row>
@@ -11301,10 +11303,10 @@
         <x:f>SUM(M145:O145)</x:f>
       </x:c>
       <x:c r="Q145" s="0"/>
-      <x:c r="R145" s="71">
+      <x:c r="R145" s="75">
         <x:f>IF(B145&gt;0,IF(TauxActuariel,((B145+1)^(1/NbEchAn))-1,B145/NbEchAn),R144)</x:f>
       </x:c>
-      <x:c r="S145" s="70">
+      <x:c r="S145" s="74">
         <x:f>IF(E145&gt;0,E145,IF(D145&gt;0,IF(AND(EchFIXE,R145&gt;0),ROUND((L145-C145)*R145/(1-((1+R145)^-D145)),NbDeci),ROUND(L145/D145,NbDeci)),S144))</x:f>
       </x:c>
     </x:row>
@@ -11342,10 +11344,10 @@
         <x:f>SUM(M146:O146)</x:f>
       </x:c>
       <x:c r="Q146" s="0"/>
-      <x:c r="R146" s="71">
+      <x:c r="R146" s="75">
         <x:f>IF(B146&gt;0,IF(TauxActuariel,((B146+1)^(1/NbEchAn))-1,B146/NbEchAn),R145)</x:f>
       </x:c>
-      <x:c r="S146" s="70">
+      <x:c r="S146" s="74">
         <x:f>IF(E146&gt;0,E146,IF(D146&gt;0,IF(AND(EchFIXE,R146&gt;0),ROUND((L146-C146)*R146/(1-((1+R146)^-D146)),NbDeci),ROUND(L146/D146,NbDeci)),S145))</x:f>
       </x:c>
     </x:row>
@@ -11383,10 +11385,10 @@
         <x:f>SUM(M147:O147)</x:f>
       </x:c>
       <x:c r="Q147" s="0"/>
-      <x:c r="R147" s="71">
+      <x:c r="R147" s="75">
         <x:f>IF(B147&gt;0,IF(TauxActuariel,((B147+1)^(1/NbEchAn))-1,B147/NbEchAn),R146)</x:f>
       </x:c>
-      <x:c r="S147" s="70">
+      <x:c r="S147" s="74">
         <x:f>IF(E147&gt;0,E147,IF(D147&gt;0,IF(AND(EchFIXE,R147&gt;0),ROUND((L147-C147)*R147/(1-((1+R147)^-D147)),NbDeci),ROUND(L147/D147,NbDeci)),S146))</x:f>
       </x:c>
     </x:row>
@@ -11424,10 +11426,10 @@
         <x:f>SUM(M148:O148)</x:f>
       </x:c>
       <x:c r="Q148" s="0"/>
-      <x:c r="R148" s="71">
+      <x:c r="R148" s="75">
         <x:f>IF(B148&gt;0,IF(TauxActuariel,((B148+1)^(1/NbEchAn))-1,B148/NbEchAn),R147)</x:f>
       </x:c>
-      <x:c r="S148" s="70">
+      <x:c r="S148" s="74">
         <x:f>IF(E148&gt;0,E148,IF(D148&gt;0,IF(AND(EchFIXE,R148&gt;0),ROUND((L148-C148)*R148/(1-((1+R148)^-D148)),NbDeci),ROUND(L148/D148,NbDeci)),S147))</x:f>
       </x:c>
     </x:row>
@@ -11465,10 +11467,10 @@
         <x:f>SUM(M149:O149)</x:f>
       </x:c>
       <x:c r="Q149" s="0"/>
-      <x:c r="R149" s="71">
+      <x:c r="R149" s="75">
         <x:f>IF(B149&gt;0,IF(TauxActuariel,((B149+1)^(1/NbEchAn))-1,B149/NbEchAn),R148)</x:f>
       </x:c>
-      <x:c r="S149" s="70">
+      <x:c r="S149" s="74">
         <x:f>IF(E149&gt;0,E149,IF(D149&gt;0,IF(AND(EchFIXE,R149&gt;0),ROUND((L149-C149)*R149/(1-((1+R149)^-D149)),NbDeci),ROUND(L149/D149,NbDeci)),S148))</x:f>
       </x:c>
     </x:row>
@@ -11506,10 +11508,10 @@
         <x:f>SUM(M150:O150)</x:f>
       </x:c>
       <x:c r="Q150" s="0"/>
-      <x:c r="R150" s="71">
+      <x:c r="R150" s="75">
         <x:f>IF(B150&gt;0,IF(TauxActuariel,((B150+1)^(1/NbEchAn))-1,B150/NbEchAn),R149)</x:f>
       </x:c>
-      <x:c r="S150" s="70">
+      <x:c r="S150" s="74">
         <x:f>IF(E150&gt;0,E150,IF(D150&gt;0,IF(AND(EchFIXE,R150&gt;0),ROUND((L150-C150)*R150/(1-((1+R150)^-D150)),NbDeci),ROUND(L150/D150,NbDeci)),S149))</x:f>
       </x:c>
     </x:row>
@@ -11547,10 +11549,10 @@
         <x:f>SUM(M151:O151)</x:f>
       </x:c>
       <x:c r="Q151" s="0"/>
-      <x:c r="R151" s="71">
+      <x:c r="R151" s="75">
         <x:f>IF(B151&gt;0,IF(TauxActuariel,((B151+1)^(1/NbEchAn))-1,B151/NbEchAn),R150)</x:f>
       </x:c>
-      <x:c r="S151" s="70">
+      <x:c r="S151" s="74">
         <x:f>IF(E151&gt;0,E151,IF(D151&gt;0,IF(AND(EchFIXE,R151&gt;0),ROUND((L151-C151)*R151/(1-((1+R151)^-D151)),NbDeci),ROUND(L151/D151,NbDeci)),S150))</x:f>
       </x:c>
     </x:row>
@@ -11588,10 +11590,10 @@
         <x:f>SUM(M152:O152)</x:f>
       </x:c>
       <x:c r="Q152" s="0"/>
-      <x:c r="R152" s="71">
+      <x:c r="R152" s="75">
         <x:f>IF(B152&gt;0,IF(TauxActuariel,((B152+1)^(1/NbEchAn))-1,B152/NbEchAn),R151)</x:f>
       </x:c>
-      <x:c r="S152" s="70">
+      <x:c r="S152" s="74">
         <x:f>IF(E152&gt;0,E152,IF(D152&gt;0,IF(AND(EchFIXE,R152&gt;0),ROUND((L152-C152)*R152/(1-((1+R152)^-D152)),NbDeci),ROUND(L152/D152,NbDeci)),S151))</x:f>
       </x:c>
     </x:row>
@@ -11629,10 +11631,10 @@
         <x:f>SUM(M153:O153)</x:f>
       </x:c>
       <x:c r="Q153" s="0"/>
-      <x:c r="R153" s="71">
+      <x:c r="R153" s="75">
         <x:f>IF(B153&gt;0,IF(TauxActuariel,((B153+1)^(1/NbEchAn))-1,B153/NbEchAn),R152)</x:f>
       </x:c>
-      <x:c r="S153" s="70">
+      <x:c r="S153" s="74">
         <x:f>IF(E153&gt;0,E153,IF(D153&gt;0,IF(AND(EchFIXE,R153&gt;0),ROUND((L153-C153)*R153/(1-((1+R153)^-D153)),NbDeci),ROUND(L153/D153,NbDeci)),S152))</x:f>
       </x:c>
     </x:row>
@@ -11670,10 +11672,10 @@
         <x:f>SUM(M154:O154)</x:f>
       </x:c>
       <x:c r="Q154" s="0"/>
-      <x:c r="R154" s="71">
+      <x:c r="R154" s="75">
         <x:f>IF(B154&gt;0,IF(TauxActuariel,((B154+1)^(1/NbEchAn))-1,B154/NbEchAn),R153)</x:f>
       </x:c>
-      <x:c r="S154" s="70">
+      <x:c r="S154" s="74">
         <x:f>IF(E154&gt;0,E154,IF(D154&gt;0,IF(AND(EchFIXE,R154&gt;0),ROUND((L154-C154)*R154/(1-((1+R154)^-D154)),NbDeci),ROUND(L154/D154,NbDeci)),S153))</x:f>
       </x:c>
     </x:row>
@@ -11711,10 +11713,10 @@
         <x:f>SUM(M155:O155)</x:f>
       </x:c>
       <x:c r="Q155" s="0"/>
-      <x:c r="R155" s="71">
+      <x:c r="R155" s="75">
         <x:f>IF(B155&gt;0,IF(TauxActuariel,((B155+1)^(1/NbEchAn))-1,B155/NbEchAn),R154)</x:f>
       </x:c>
-      <x:c r="S155" s="70">
+      <x:c r="S155" s="74">
         <x:f>IF(E155&gt;0,E155,IF(D155&gt;0,IF(AND(EchFIXE,R155&gt;0),ROUND((L155-C155)*R155/(1-((1+R155)^-D155)),NbDeci),ROUND(L155/D155,NbDeci)),S154))</x:f>
       </x:c>
     </x:row>
@@ -11752,10 +11754,10 @@
         <x:f>SUM(M156:O156)</x:f>
       </x:c>
       <x:c r="Q156" s="0"/>
-      <x:c r="R156" s="71">
+      <x:c r="R156" s="75">
         <x:f>IF(B156&gt;0,IF(TauxActuariel,((B156+1)^(1/NbEchAn))-1,B156/NbEchAn),R155)</x:f>
       </x:c>
-      <x:c r="S156" s="70">
+      <x:c r="S156" s="74">
         <x:f>IF(E156&gt;0,E156,IF(D156&gt;0,IF(AND(EchFIXE,R156&gt;0),ROUND((L156-C156)*R156/(1-((1+R156)^-D156)),NbDeci),ROUND(L156/D156,NbDeci)),S155))</x:f>
       </x:c>
     </x:row>
@@ -11793,10 +11795,10 @@
         <x:f>SUM(M157:O157)</x:f>
       </x:c>
       <x:c r="Q157" s="0"/>
-      <x:c r="R157" s="71">
+      <x:c r="R157" s="75">
         <x:f>IF(B157&gt;0,IF(TauxActuariel,((B157+1)^(1/NbEchAn))-1,B157/NbEchAn),R156)</x:f>
       </x:c>
-      <x:c r="S157" s="70">
+      <x:c r="S157" s="74">
         <x:f>IF(E157&gt;0,E157,IF(D157&gt;0,IF(AND(EchFIXE,R157&gt;0),ROUND((L157-C157)*R157/(1-((1+R157)^-D157)),NbDeci),ROUND(L157/D157,NbDeci)),S156))</x:f>
       </x:c>
     </x:row>
@@ -11834,10 +11836,10 @@
         <x:f>SUM(M158:O158)</x:f>
       </x:c>
       <x:c r="Q158" s="0"/>
-      <x:c r="R158" s="71">
+      <x:c r="R158" s="75">
         <x:f>IF(B158&gt;0,IF(TauxActuariel,((B158+1)^(1/NbEchAn))-1,B158/NbEchAn),R157)</x:f>
       </x:c>
-      <x:c r="S158" s="70">
+      <x:c r="S158" s="74">
         <x:f>IF(E158&gt;0,E158,IF(D158&gt;0,IF(AND(EchFIXE,R158&gt;0),ROUND((L158-C158)*R158/(1-((1+R158)^-D158)),NbDeci),ROUND(L158/D158,NbDeci)),S157))</x:f>
       </x:c>
     </x:row>
@@ -11875,10 +11877,10 @@
         <x:f>SUM(M159:O159)</x:f>
       </x:c>
       <x:c r="Q159" s="0"/>
-      <x:c r="R159" s="71">
+      <x:c r="R159" s="75">
         <x:f>IF(B159&gt;0,IF(TauxActuariel,((B159+1)^(1/NbEchAn))-1,B159/NbEchAn),R158)</x:f>
       </x:c>
-      <x:c r="S159" s="70">
+      <x:c r="S159" s="74">
         <x:f>IF(E159&gt;0,E159,IF(D159&gt;0,IF(AND(EchFIXE,R159&gt;0),ROUND((L159-C159)*R159/(1-((1+R159)^-D159)),NbDeci),ROUND(L159/D159,NbDeci)),S158))</x:f>
       </x:c>
     </x:row>
@@ -11916,10 +11918,10 @@
         <x:f>SUM(M160:O160)</x:f>
       </x:c>
       <x:c r="Q160" s="0"/>
-      <x:c r="R160" s="71">
+      <x:c r="R160" s="75">
         <x:f>IF(B160&gt;0,IF(TauxActuariel,((B160+1)^(1/NbEchAn))-1,B160/NbEchAn),R159)</x:f>
       </x:c>
-      <x:c r="S160" s="70">
+      <x:c r="S160" s="74">
         <x:f>IF(E160&gt;0,E160,IF(D160&gt;0,IF(AND(EchFIXE,R160&gt;0),ROUND((L160-C160)*R160/(1-((1+R160)^-D160)),NbDeci),ROUND(L160/D160,NbDeci)),S159))</x:f>
       </x:c>
     </x:row>
@@ -11957,10 +11959,10 @@
         <x:f>SUM(M161:O161)</x:f>
       </x:c>
       <x:c r="Q161" s="0"/>
-      <x:c r="R161" s="71">
+      <x:c r="R161" s="75">
         <x:f>IF(B161&gt;0,IF(TauxActuariel,((B161+1)^(1/NbEchAn))-1,B161/NbEchAn),R160)</x:f>
       </x:c>
-      <x:c r="S161" s="70">
+      <x:c r="S161" s="74">
         <x:f>IF(E161&gt;0,E161,IF(D161&gt;0,IF(AND(EchFIXE,R161&gt;0),ROUND((L161-C161)*R161/(1-((1+R161)^-D161)),NbDeci),ROUND(L161/D161,NbDeci)),S160))</x:f>
       </x:c>
     </x:row>
@@ -11998,10 +12000,10 @@
         <x:f>SUM(M162:O162)</x:f>
       </x:c>
       <x:c r="Q162" s="0"/>
-      <x:c r="R162" s="71">
+      <x:c r="R162" s="75">
         <x:f>IF(B162&gt;0,IF(TauxActuariel,((B162+1)^(1/NbEchAn))-1,B162/NbEchAn),R161)</x:f>
       </x:c>
-      <x:c r="S162" s="70">
+      <x:c r="S162" s="74">
         <x:f>IF(E162&gt;0,E162,IF(D162&gt;0,IF(AND(EchFIXE,R162&gt;0),ROUND((L162-C162)*R162/(1-((1+R162)^-D162)),NbDeci),ROUND(L162/D162,NbDeci)),S161))</x:f>
       </x:c>
     </x:row>
@@ -12039,10 +12041,10 @@
         <x:f>SUM(M163:O163)</x:f>
       </x:c>
       <x:c r="Q163" s="0"/>
-      <x:c r="R163" s="71">
+      <x:c r="R163" s="75">
         <x:f>IF(B163&gt;0,IF(TauxActuariel,((B163+1)^(1/NbEchAn))-1,B163/NbEchAn),R162)</x:f>
       </x:c>
-      <x:c r="S163" s="70">
+      <x:c r="S163" s="74">
         <x:f>IF(E163&gt;0,E163,IF(D163&gt;0,IF(AND(EchFIXE,R163&gt;0),ROUND((L163-C163)*R163/(1-((1+R163)^-D163)),NbDeci),ROUND(L163/D163,NbDeci)),S162))</x:f>
       </x:c>
     </x:row>
@@ -12080,10 +12082,10 @@
         <x:f>SUM(M164:O164)</x:f>
       </x:c>
       <x:c r="Q164" s="0"/>
-      <x:c r="R164" s="71">
+      <x:c r="R164" s="75">
         <x:f>IF(B164&gt;0,IF(TauxActuariel,((B164+1)^(1/NbEchAn))-1,B164/NbEchAn),R163)</x:f>
       </x:c>
-      <x:c r="S164" s="70">
+      <x:c r="S164" s="74">
         <x:f>IF(E164&gt;0,E164,IF(D164&gt;0,IF(AND(EchFIXE,R164&gt;0),ROUND((L164-C164)*R164/(1-((1+R164)^-D164)),NbDeci),ROUND(L164/D164,NbDeci)),S163))</x:f>
       </x:c>
     </x:row>
@@ -12121,10 +12123,10 @@
         <x:f>SUM(M165:O165)</x:f>
       </x:c>
       <x:c r="Q165" s="0"/>
-      <x:c r="R165" s="71">
+      <x:c r="R165" s="75">
         <x:f>IF(B165&gt;0,IF(TauxActuariel,((B165+1)^(1/NbEchAn))-1,B165/NbEchAn),R164)</x:f>
       </x:c>
-      <x:c r="S165" s="70">
+      <x:c r="S165" s="74">
         <x:f>IF(E165&gt;0,E165,IF(D165&gt;0,IF(AND(EchFIXE,R165&gt;0),ROUND((L165-C165)*R165/(1-((1+R165)^-D165)),NbDeci),ROUND(L165/D165,NbDeci)),S164))</x:f>
       </x:c>
     </x:row>
@@ -12162,10 +12164,10 @@
         <x:f>SUM(M166:O166)</x:f>
       </x:c>
       <x:c r="Q166" s="0"/>
-      <x:c r="R166" s="71">
+      <x:c r="R166" s="75">
         <x:f>IF(B166&gt;0,IF(TauxActuariel,((B166+1)^(1/NbEchAn))-1,B166/NbEchAn),R165)</x:f>
       </x:c>
-      <x:c r="S166" s="70">
+      <x:c r="S166" s="74">
         <x:f>IF(E166&gt;0,E166,IF(D166&gt;0,IF(AND(EchFIXE,R166&gt;0),ROUND((L166-C166)*R166/(1-((1+R166)^-D166)),NbDeci),ROUND(L166/D166,NbDeci)),S165))</x:f>
       </x:c>
     </x:row>
@@ -12203,10 +12205,10 @@
         <x:f>SUM(M167:O167)</x:f>
       </x:c>
       <x:c r="Q167" s="0"/>
-      <x:c r="R167" s="71">
+      <x:c r="R167" s="75">
         <x:f>IF(B167&gt;0,IF(TauxActuariel,((B167+1)^(1/NbEchAn))-1,B167/NbEchAn),R166)</x:f>
       </x:c>
-      <x:c r="S167" s="70">
+      <x:c r="S167" s="74">
         <x:f>IF(E167&gt;0,E167,IF(D167&gt;0,IF(AND(EchFIXE,R167&gt;0),ROUND((L167-C167)*R167/(1-((1+R167)^-D167)),NbDeci),ROUND(L167/D167,NbDeci)),S166))</x:f>
       </x:c>
     </x:row>
@@ -12244,10 +12246,10 @@
         <x:f>SUM(M168:O168)</x:f>
       </x:c>
       <x:c r="Q168" s="0"/>
-      <x:c r="R168" s="71">
+      <x:c r="R168" s="75">
         <x:f>IF(B168&gt;0,IF(TauxActuariel,((B168+1)^(1/NbEchAn))-1,B168/NbEchAn),R167)</x:f>
       </x:c>
-      <x:c r="S168" s="70">
+      <x:c r="S168" s="74">
         <x:f>IF(E168&gt;0,E168,IF(D168&gt;0,IF(AND(EchFIXE,R168&gt;0),ROUND((L168-C168)*R168/(1-((1+R168)^-D168)),NbDeci),ROUND(L168/D168,NbDeci)),S167))</x:f>
       </x:c>
     </x:row>
@@ -12285,10 +12287,10 @@
         <x:f>SUM(M169:O169)</x:f>
       </x:c>
       <x:c r="Q169" s="0"/>
-      <x:c r="R169" s="71">
+      <x:c r="R169" s="75">
         <x:f>IF(B169&gt;0,IF(TauxActuariel,((B169+1)^(1/NbEchAn))-1,B169/NbEchAn),R168)</x:f>
       </x:c>
-      <x:c r="S169" s="70">
+      <x:c r="S169" s="74">
         <x:f>IF(E169&gt;0,E169,IF(D169&gt;0,IF(AND(EchFIXE,R169&gt;0),ROUND((L169-C169)*R169/(1-((1+R169)^-D169)),NbDeci),ROUND(L169/D169,NbDeci)),S168))</x:f>
       </x:c>
     </x:row>
@@ -12326,10 +12328,10 @@
         <x:f>SUM(M170:O170)</x:f>
       </x:c>
       <x:c r="Q170" s="0"/>
-      <x:c r="R170" s="71">
+      <x:c r="R170" s="75">
         <x:f>IF(B170&gt;0,IF(TauxActuariel,((B170+1)^(1/NbEchAn))-1,B170/NbEchAn),R169)</x:f>
       </x:c>
-      <x:c r="S170" s="70">
+      <x:c r="S170" s="74">
         <x:f>IF(E170&gt;0,E170,IF(D170&gt;0,IF(AND(EchFIXE,R170&gt;0),ROUND((L170-C170)*R170/(1-((1+R170)^-D170)),NbDeci),ROUND(L170/D170,NbDeci)),S169))</x:f>
       </x:c>
     </x:row>
@@ -12367,10 +12369,10 @@
         <x:f>SUM(M171:O171)</x:f>
       </x:c>
       <x:c r="Q171" s="0"/>
-      <x:c r="R171" s="71">
+      <x:c r="R171" s="75">
         <x:f>IF(B171&gt;0,IF(TauxActuariel,((B171+1)^(1/NbEchAn))-1,B171/NbEchAn),R170)</x:f>
       </x:c>
-      <x:c r="S171" s="70">
+      <x:c r="S171" s="74">
         <x:f>IF(E171&gt;0,E171,IF(D171&gt;0,IF(AND(EchFIXE,R171&gt;0),ROUND((L171-C171)*R171/(1-((1+R171)^-D171)),NbDeci),ROUND(L171/D171,NbDeci)),S170))</x:f>
       </x:c>
     </x:row>
@@ -12408,10 +12410,10 @@
         <x:f>SUM(M172:O172)</x:f>
       </x:c>
       <x:c r="Q172" s="0"/>
-      <x:c r="R172" s="71">
+      <x:c r="R172" s="75">
         <x:f>IF(B172&gt;0,IF(TauxActuariel,((B172+1)^(1/NbEchAn))-1,B172/NbEchAn),R171)</x:f>
       </x:c>
-      <x:c r="S172" s="70">
+      <x:c r="S172" s="74">
         <x:f>IF(E172&gt;0,E172,IF(D172&gt;0,IF(AND(EchFIXE,R172&gt;0),ROUND((L172-C172)*R172/(1-((1+R172)^-D172)),NbDeci),ROUND(L172/D172,NbDeci)),S171))</x:f>
       </x:c>
     </x:row>
@@ -12449,10 +12451,10 @@
         <x:f>SUM(M173:O173)</x:f>
       </x:c>
       <x:c r="Q173" s="0"/>
-      <x:c r="R173" s="71">
+      <x:c r="R173" s="75">
         <x:f>IF(B173&gt;0,IF(TauxActuariel,((B173+1)^(1/NbEchAn))-1,B173/NbEchAn),R172)</x:f>
       </x:c>
-      <x:c r="S173" s="70">
+      <x:c r="S173" s="74">
         <x:f>IF(E173&gt;0,E173,IF(D173&gt;0,IF(AND(EchFIXE,R173&gt;0),ROUND((L173-C173)*R173/(1-((1+R173)^-D173)),NbDeci),ROUND(L173/D173,NbDeci)),S172))</x:f>
       </x:c>
     </x:row>
@@ -12490,10 +12492,10 @@
         <x:f>SUM(M174:O174)</x:f>
       </x:c>
       <x:c r="Q174" s="0"/>
-      <x:c r="R174" s="71">
+      <x:c r="R174" s="75">
         <x:f>IF(B174&gt;0,IF(TauxActuariel,((B174+1)^(1/NbEchAn))-1,B174/NbEchAn),R173)</x:f>
       </x:c>
-      <x:c r="S174" s="70">
+      <x:c r="S174" s="74">
         <x:f>IF(E174&gt;0,E174,IF(D174&gt;0,IF(AND(EchFIXE,R174&gt;0),ROUND((L174-C174)*R174/(1-((1+R174)^-D174)),NbDeci),ROUND(L174/D174,NbDeci)),S173))</x:f>
       </x:c>
     </x:row>
@@ -12531,10 +12533,10 @@
         <x:f>SUM(M175:O175)</x:f>
       </x:c>
       <x:c r="Q175" s="0"/>
-      <x:c r="R175" s="71">
+      <x:c r="R175" s="75">
         <x:f>IF(B175&gt;0,IF(TauxActuariel,((B175+1)^(1/NbEchAn))-1,B175/NbEchAn),R174)</x:f>
       </x:c>
-      <x:c r="S175" s="70">
+      <x:c r="S175" s="74">
         <x:f>IF(E175&gt;0,E175,IF(D175&gt;0,IF(AND(EchFIXE,R175&gt;0),ROUND((L175-C175)*R175/(1-((1+R175)^-D175)),NbDeci),ROUND(L175/D175,NbDeci)),S174))</x:f>
       </x:c>
     </x:row>
@@ -12572,10 +12574,10 @@
         <x:f>SUM(M176:O176)</x:f>
       </x:c>
       <x:c r="Q176" s="0"/>
-      <x:c r="R176" s="71">
+      <x:c r="R176" s="75">
         <x:f>IF(B176&gt;0,IF(TauxActuariel,((B176+1)^(1/NbEchAn))-1,B176/NbEchAn),R175)</x:f>
       </x:c>
-      <x:c r="S176" s="70">
+      <x:c r="S176" s="74">
         <x:f>IF(E176&gt;0,E176,IF(D176&gt;0,IF(AND(EchFIXE,R176&gt;0),ROUND((L176-C176)*R176/(1-((1+R176)^-D176)),NbDeci),ROUND(L176/D176,NbDeci)),S175))</x:f>
       </x:c>
     </x:row>
@@ -12613,10 +12615,10 @@
         <x:f>SUM(M177:O177)</x:f>
       </x:c>
       <x:c r="Q177" s="0"/>
-      <x:c r="R177" s="71">
+      <x:c r="R177" s="75">
         <x:f>IF(B177&gt;0,IF(TauxActuariel,((B177+1)^(1/NbEchAn))-1,B177/NbEchAn),R176)</x:f>
       </x:c>
-      <x:c r="S177" s="70">
+      <x:c r="S177" s="74">
         <x:f>IF(E177&gt;0,E177,IF(D177&gt;0,IF(AND(EchFIXE,R177&gt;0),ROUND((L177-C177)*R177/(1-((1+R177)^-D177)),NbDeci),ROUND(L177/D177,NbDeci)),S176))</x:f>
       </x:c>
     </x:row>
@@ -12654,10 +12656,10 @@
         <x:f>SUM(M178:O178)</x:f>
       </x:c>
       <x:c r="Q178" s="0"/>
-      <x:c r="R178" s="71">
+      <x:c r="R178" s="75">
         <x:f>IF(B178&gt;0,IF(TauxActuariel,((B178+1)^(1/NbEchAn))-1,B178/NbEchAn),R177)</x:f>
       </x:c>
-      <x:c r="S178" s="70">
+      <x:c r="S178" s="74">
         <x:f>IF(E178&gt;0,E178,IF(D178&gt;0,IF(AND(EchFIXE,R178&gt;0),ROUND((L178-C178)*R178/(1-((1+R178)^-D178)),NbDeci),ROUND(L178/D178,NbDeci)),S177))</x:f>
       </x:c>
     </x:row>
@@ -12695,10 +12697,10 @@
         <x:f>SUM(M179:O179)</x:f>
       </x:c>
       <x:c r="Q179" s="0"/>
-      <x:c r="R179" s="71">
+      <x:c r="R179" s="75">
         <x:f>IF(B179&gt;0,IF(TauxActuariel,((B179+1)^(1/NbEchAn))-1,B179/NbEchAn),R178)</x:f>
       </x:c>
-      <x:c r="S179" s="70">
+      <x:c r="S179" s="74">
         <x:f>IF(E179&gt;0,E179,IF(D179&gt;0,IF(AND(EchFIXE,R179&gt;0),ROUND((L179-C179)*R179/(1-((1+R179)^-D179)),NbDeci),ROUND(L179/D179,NbDeci)),S178))</x:f>
       </x:c>
     </x:row>
@@ -12736,10 +12738,10 @@
         <x:f>SUM(M180:O180)</x:f>
       </x:c>
       <x:c r="Q180" s="0"/>
-      <x:c r="R180" s="71">
+      <x:c r="R180" s="75">
         <x:f>IF(B180&gt;0,IF(TauxActuariel,((B180+1)^(1/NbEchAn))-1,B180/NbEchAn),R179)</x:f>
       </x:c>
-      <x:c r="S180" s="70">
+      <x:c r="S180" s="74">
         <x:f>IF(E180&gt;0,E180,IF(D180&gt;0,IF(AND(EchFIXE,R180&gt;0),ROUND((L180-C180)*R180/(1-((1+R180)^-D180)),NbDeci),ROUND(L180/D180,NbDeci)),S179))</x:f>
       </x:c>
     </x:row>
@@ -12777,10 +12779,10 @@
         <x:f>SUM(M181:O181)</x:f>
       </x:c>
       <x:c r="Q181" s="0"/>
-      <x:c r="R181" s="71">
+      <x:c r="R181" s="75">
         <x:f>IF(B181&gt;0,IF(TauxActuariel,((B181+1)^(1/NbEchAn))-1,B181/NbEchAn),R180)</x:f>
       </x:c>
-      <x:c r="S181" s="70">
+      <x:c r="S181" s="74">
         <x:f>IF(E181&gt;0,E181,IF(D181&gt;0,IF(AND(EchFIXE,R181&gt;0),ROUND((L181-C181)*R181/(1-((1+R181)^-D181)),NbDeci),ROUND(L181/D181,NbDeci)),S180))</x:f>
       </x:c>
     </x:row>
@@ -12818,10 +12820,10 @@
         <x:f>SUM(M182:O182)</x:f>
       </x:c>
       <x:c r="Q182" s="0"/>
-      <x:c r="R182" s="71">
+      <x:c r="R182" s="75">
         <x:f>IF(B182&gt;0,IF(TauxActuariel,((B182+1)^(1/NbEchAn))-1,B182/NbEchAn),R181)</x:f>
       </x:c>
-      <x:c r="S182" s="70">
+      <x:c r="S182" s="74">
         <x:f>IF(E182&gt;0,E182,IF(D182&gt;0,IF(AND(EchFIXE,R182&gt;0),ROUND((L182-C182)*R182/(1-((1+R182)^-D182)),NbDeci),ROUND(L182/D182,NbDeci)),S181))</x:f>
       </x:c>
     </x:row>
@@ -12859,10 +12861,10 @@
         <x:f>SUM(M183:O183)</x:f>
       </x:c>
       <x:c r="Q183" s="0"/>
-      <x:c r="R183" s="71">
+      <x:c r="R183" s="75">
         <x:f>IF(B183&gt;0,IF(TauxActuariel,((B183+1)^(1/NbEchAn))-1,B183/NbEchAn),R182)</x:f>
       </x:c>
-      <x:c r="S183" s="70">
+      <x:c r="S183" s="74">
         <x:f>IF(E183&gt;0,E183,IF(D183&gt;0,IF(AND(EchFIXE,R183&gt;0),ROUND((L183-C183)*R183/(1-((1+R183)^-D183)),NbDeci),ROUND(L183/D183,NbDeci)),S182))</x:f>
       </x:c>
     </x:row>
@@ -12900,10 +12902,10 @@
         <x:f>SUM(M184:O184)</x:f>
       </x:c>
       <x:c r="Q184" s="0"/>
-      <x:c r="R184" s="71">
+      <x:c r="R184" s="75">
         <x:f>IF(B184&gt;0,IF(TauxActuariel,((B184+1)^(1/NbEchAn))-1,B184/NbEchAn),R183)</x:f>
       </x:c>
-      <x:c r="S184" s="70">
+      <x:c r="S184" s="74">
         <x:f>IF(E184&gt;0,E184,IF(D184&gt;0,IF(AND(EchFIXE,R184&gt;0),ROUND((L184-C184)*R184/(1-((1+R184)^-D184)),NbDeci),ROUND(L184/D184,NbDeci)),S183))</x:f>
       </x:c>
     </x:row>
@@ -12941,10 +12943,10 @@
         <x:f>SUM(M185:O185)</x:f>
       </x:c>
       <x:c r="Q185" s="0"/>
-      <x:c r="R185" s="71">
+      <x:c r="R185" s="75">
         <x:f>IF(B185&gt;0,IF(TauxActuariel,((B185+1)^(1/NbEchAn))-1,B185/NbEchAn),R184)</x:f>
       </x:c>
-      <x:c r="S185" s="70">
+      <x:c r="S185" s="74">
         <x:f>IF(E185&gt;0,E185,IF(D185&gt;0,IF(AND(EchFIXE,R185&gt;0),ROUND((L185-C185)*R185/(1-((1+R185)^-D185)),NbDeci),ROUND(L185/D185,NbDeci)),S184))</x:f>
       </x:c>
     </x:row>
@@ -12982,10 +12984,10 @@
         <x:f>SUM(M186:O186)</x:f>
       </x:c>
       <x:c r="Q186" s="0"/>
-      <x:c r="R186" s="71">
+      <x:c r="R186" s="75">
         <x:f>IF(B186&gt;0,IF(TauxActuariel,((B186+1)^(1/NbEchAn))-1,B186/NbEchAn),R185)</x:f>
       </x:c>
-      <x:c r="S186" s="70">
+      <x:c r="S186" s="74">
         <x:f>IF(E186&gt;0,E186,IF(D186&gt;0,IF(AND(EchFIXE,R186&gt;0),ROUND((L186-C186)*R186/(1-((1+R186)^-D186)),NbDeci),ROUND(L186/D186,NbDeci)),S185))</x:f>
       </x:c>
     </x:row>
@@ -13023,10 +13025,10 @@
         <x:f>SUM(M187:O187)</x:f>
       </x:c>
       <x:c r="Q187" s="0"/>
-      <x:c r="R187" s="71">
+      <x:c r="R187" s="75">
         <x:f>IF(B187&gt;0,IF(TauxActuariel,((B187+1)^(1/NbEchAn))-1,B187/NbEchAn),R186)</x:f>
       </x:c>
-      <x:c r="S187" s="70">
+      <x:c r="S187" s="74">
         <x:f>IF(E187&gt;0,E187,IF(D187&gt;0,IF(AND(EchFIXE,R187&gt;0),ROUND((L187-C187)*R187/(1-((1+R187)^-D187)),NbDeci),ROUND(L187/D187,NbDeci)),S186))</x:f>
       </x:c>
     </x:row>
@@ -13064,10 +13066,10 @@
         <x:f>SUM(M188:O188)</x:f>
       </x:c>
       <x:c r="Q188" s="0"/>
-      <x:c r="R188" s="71">
+      <x:c r="R188" s="75">
         <x:f>IF(B188&gt;0,IF(TauxActuariel,((B188+1)^(1/NbEchAn))-1,B188/NbEchAn),R187)</x:f>
       </x:c>
-      <x:c r="S188" s="70">
+      <x:c r="S188" s="74">
         <x:f>IF(E188&gt;0,E188,IF(D188&gt;0,IF(AND(EchFIXE,R188&gt;0),ROUND((L188-C188)*R188/(1-((1+R188)^-D188)),NbDeci),ROUND(L188/D188,NbDeci)),S187))</x:f>
       </x:c>
     </x:row>
@@ -13105,10 +13107,10 @@
         <x:f>SUM(M189:O189)</x:f>
       </x:c>
       <x:c r="Q189" s="0"/>
-      <x:c r="R189" s="71">
+      <x:c r="R189" s="75">
         <x:f>IF(B189&gt;0,IF(TauxActuariel,((B189+1)^(1/NbEchAn))-1,B189/NbEchAn),R188)</x:f>
       </x:c>
-      <x:c r="S189" s="70">
+      <x:c r="S189" s="74">
         <x:f>IF(E189&gt;0,E189,IF(D189&gt;0,IF(AND(EchFIXE,R189&gt;0),ROUND((L189-C189)*R189/(1-((1+R189)^-D189)),NbDeci),ROUND(L189/D189,NbDeci)),S188))</x:f>
       </x:c>
     </x:row>
@@ -13146,10 +13148,10 @@
         <x:f>SUM(M190:O190)</x:f>
       </x:c>
       <x:c r="Q190" s="0"/>
-      <x:c r="R190" s="71">
+      <x:c r="R190" s="75">
         <x:f>IF(B190&gt;0,IF(TauxActuariel,((B190+1)^(1/NbEchAn))-1,B190/NbEchAn),R189)</x:f>
       </x:c>
-      <x:c r="S190" s="70">
+      <x:c r="S190" s="74">
         <x:f>IF(E190&gt;0,E190,IF(D190&gt;0,IF(AND(EchFIXE,R190&gt;0),ROUND((L190-C190)*R190/(1-((1+R190)^-D190)),NbDeci),ROUND(L190/D190,NbDeci)),S189))</x:f>
       </x:c>
     </x:row>
@@ -13187,10 +13189,10 @@
         <x:f>SUM(M191:O191)</x:f>
       </x:c>
       <x:c r="Q191" s="0"/>
-      <x:c r="R191" s="71">
+      <x:c r="R191" s="75">
         <x:f>IF(B191&gt;0,IF(TauxActuariel,((B191+1)^(1/NbEchAn))-1,B191/NbEchAn),R190)</x:f>
       </x:c>
-      <x:c r="S191" s="70">
+      <x:c r="S191" s="74">
         <x:f>IF(E191&gt;0,E191,IF(D191&gt;0,IF(AND(EchFIXE,R191&gt;0),ROUND((L191-C191)*R191/(1-((1+R191)^-D191)),NbDeci),ROUND(L191/D191,NbDeci)),S190))</x:f>
       </x:c>
     </x:row>
@@ -13228,10 +13230,10 @@
         <x:f>SUM(M192:O192)</x:f>
       </x:c>
       <x:c r="Q192" s="0"/>
-      <x:c r="R192" s="71">
+      <x:c r="R192" s="75">
         <x:f>IF(B192&gt;0,IF(TauxActuariel,((B192+1)^(1/NbEchAn))-1,B192/NbEchAn),R191)</x:f>
       </x:c>
-      <x:c r="S192" s="70">
+      <x:c r="S192" s="74">
         <x:f>IF(E192&gt;0,E192,IF(D192&gt;0,IF(AND(EchFIXE,R192&gt;0),ROUND((L192-C192)*R192/(1-((1+R192)^-D192)),NbDeci),ROUND(L192/D192,NbDeci)),S191))</x:f>
       </x:c>
     </x:row>
@@ -13269,10 +13271,10 @@
         <x:f>SUM(M193:O193)</x:f>
       </x:c>
       <x:c r="Q193" s="0"/>
-      <x:c r="R193" s="71">
+      <x:c r="R193" s="75">
         <x:f>IF(B193&gt;0,IF(TauxActuariel,((B193+1)^(1/NbEchAn))-1,B193/NbEchAn),R192)</x:f>
       </x:c>
-      <x:c r="S193" s="70">
+      <x:c r="S193" s="74">
         <x:f>IF(E193&gt;0,E193,IF(D193&gt;0,IF(AND(EchFIXE,R193&gt;0),ROUND((L193-C193)*R193/(1-((1+R193)^-D193)),NbDeci),ROUND(L193/D193,NbDeci)),S192))</x:f>
       </x:c>
     </x:row>
@@ -13310,10 +13312,10 @@
         <x:f>SUM(M194:O194)</x:f>
       </x:c>
       <x:c r="Q194" s="0"/>
-      <x:c r="R194" s="71">
+      <x:c r="R194" s="75">
         <x:f>IF(B194&gt;0,IF(TauxActuariel,((B194+1)^(1/NbEchAn))-1,B194/NbEchAn),R193)</x:f>
       </x:c>
-      <x:c r="S194" s="70">
+      <x:c r="S194" s="74">
         <x:f>IF(E194&gt;0,E194,IF(D194&gt;0,IF(AND(EchFIXE,R194&gt;0),ROUND((L194-C194)*R194/(1-((1+R194)^-D194)),NbDeci),ROUND(L194/D194,NbDeci)),S193))</x:f>
       </x:c>
     </x:row>
@@ -13351,10 +13353,10 @@
         <x:f>SUM(M195:O195)</x:f>
       </x:c>
       <x:c r="Q195" s="0"/>
-      <x:c r="R195" s="71">
+      <x:c r="R195" s="75">
         <x:f>IF(B195&gt;0,IF(TauxActuariel,((B195+1)^(1/NbEchAn))-1,B195/NbEchAn),R194)</x:f>
       </x:c>
-      <x:c r="S195" s="70">
+      <x:c r="S195" s="74">
         <x:f>IF(E195&gt;0,E195,IF(D195&gt;0,IF(AND(EchFIXE,R195&gt;0),ROUND((L195-C195)*R195/(1-((1+R195)^-D195)),NbDeci),ROUND(L195/D195,NbDeci)),S194))</x:f>
       </x:c>
     </x:row>
@@ -13392,10 +13394,10 @@
         <x:f>SUM(M196:O196)</x:f>
       </x:c>
       <x:c r="Q196" s="0"/>
-      <x:c r="R196" s="71">
+      <x:c r="R196" s="75">
         <x:f>IF(B196&gt;0,IF(TauxActuariel,((B196+1)^(1/NbEchAn))-1,B196/NbEchAn),R195)</x:f>
       </x:c>
-      <x:c r="S196" s="70">
+      <x:c r="S196" s="74">
         <x:f>IF(E196&gt;0,E196,IF(D196&gt;0,IF(AND(EchFIXE,R196&gt;0),ROUND((L196-C196)*R196/(1-((1+R196)^-D196)),NbDeci),ROUND(L196/D196,NbDeci)),S195))</x:f>
       </x:c>
     </x:row>
@@ -13433,10 +13435,10 @@
         <x:f>SUM(M197:O197)</x:f>
       </x:c>
       <x:c r="Q197" s="0"/>
-      <x:c r="R197" s="71">
+      <x:c r="R197" s="75">
         <x:f>IF(B197&gt;0,IF(TauxActuariel,((B197+1)^(1/NbEchAn))-1,B197/NbEchAn),R196)</x:f>
       </x:c>
-      <x:c r="S197" s="70">
+      <x:c r="S197" s="74">
         <x:f>IF(E197&gt;0,E197,IF(D197&gt;0,IF(AND(EchFIXE,R197&gt;0),ROUND((L197-C197)*R197/(1-((1+R197)^-D197)),NbDeci),ROUND(L197/D197,NbDeci)),S196))</x:f>
       </x:c>
     </x:row>
@@ -13474,10 +13476,10 @@
         <x:f>SUM(M198:O198)</x:f>
       </x:c>
       <x:c r="Q198" s="0"/>
-      <x:c r="R198" s="71">
+      <x:c r="R198" s="75">
         <x:f>IF(B198&gt;0,IF(TauxActuariel,((B198+1)^(1/NbEchAn))-1,B198/NbEchAn),R197)</x:f>
       </x:c>
-      <x:c r="S198" s="70">
+      <x:c r="S198" s="74">
         <x:f>IF(E198&gt;0,E198,IF(D198&gt;0,IF(AND(EchFIXE,R198&gt;0),ROUND((L198-C198)*R198/(1-((1+R198)^-D198)),NbDeci),ROUND(L198/D198,NbDeci)),S197))</x:f>
       </x:c>
     </x:row>
@@ -13515,10 +13517,10 @@
         <x:f>SUM(M199:O199)</x:f>
       </x:c>
       <x:c r="Q199" s="0"/>
-      <x:c r="R199" s="71">
+      <x:c r="R199" s="75">
         <x:f>IF(B199&gt;0,IF(TauxActuariel,((B199+1)^(1/NbEchAn))-1,B199/NbEchAn),R198)</x:f>
       </x:c>
-      <x:c r="S199" s="70">
+      <x:c r="S199" s="74">
         <x:f>IF(E199&gt;0,E199,IF(D199&gt;0,IF(AND(EchFIXE,R199&gt;0),ROUND((L199-C199)*R199/(1-((1+R199)^-D199)),NbDeci),ROUND(L199/D199,NbDeci)),S198))</x:f>
       </x:c>
     </x:row>
@@ -13556,10 +13558,10 @@
         <x:f>SUM(M200:O200)</x:f>
       </x:c>
       <x:c r="Q200" s="0"/>
-      <x:c r="R200" s="71">
+      <x:c r="R200" s="75">
         <x:f>IF(B200&gt;0,IF(TauxActuariel,((B200+1)^(1/NbEchAn))-1,B200/NbEchAn),R199)</x:f>
       </x:c>
-      <x:c r="S200" s="70">
+      <x:c r="S200" s="74">
         <x:f>IF(E200&gt;0,E200,IF(D200&gt;0,IF(AND(EchFIXE,R200&gt;0),ROUND((L200-C200)*R200/(1-((1+R200)^-D200)),NbDeci),ROUND(L200/D200,NbDeci)),S199))</x:f>
       </x:c>
     </x:row>
@@ -13597,10 +13599,10 @@
         <x:f>SUM(M201:O201)</x:f>
       </x:c>
       <x:c r="Q201" s="0"/>
-      <x:c r="R201" s="71">
+      <x:c r="R201" s="75">
         <x:f>IF(B201&gt;0,IF(TauxActuariel,((B201+1)^(1/NbEchAn))-1,B201/NbEchAn),R200)</x:f>
       </x:c>
-      <x:c r="S201" s="70">
+      <x:c r="S201" s="74">
         <x:f>IF(E201&gt;0,E201,IF(D201&gt;0,IF(AND(EchFIXE,R201&gt;0),ROUND((L201-C201)*R201/(1-((1+R201)^-D201)),NbDeci),ROUND(L201/D201,NbDeci)),S200))</x:f>
       </x:c>
     </x:row>
@@ -13638,10 +13640,10 @@
         <x:f>SUM(M202:O202)</x:f>
       </x:c>
       <x:c r="Q202" s="0"/>
-      <x:c r="R202" s="71">
+      <x:c r="R202" s="75">
         <x:f>IF(B202&gt;0,IF(TauxActuariel,((B202+1)^(1/NbEchAn))-1,B202/NbEchAn),R201)</x:f>
       </x:c>
-      <x:c r="S202" s="70">
+      <x:c r="S202" s="74">
         <x:f>IF(E202&gt;0,E202,IF(D202&gt;0,IF(AND(EchFIXE,R202&gt;0),ROUND((L202-C202)*R202/(1-((1+R202)^-D202)),NbDeci),ROUND(L202/D202,NbDeci)),S201))</x:f>
       </x:c>
     </x:row>
@@ -13679,10 +13681,10 @@
         <x:f>SUM(M203:O203)</x:f>
       </x:c>
       <x:c r="Q203" s="0"/>
-      <x:c r="R203" s="71">
+      <x:c r="R203" s="75">
         <x:f>IF(B203&gt;0,IF(TauxActuariel,((B203+1)^(1/NbEchAn))-1,B203/NbEchAn),R202)</x:f>
       </x:c>
-      <x:c r="S203" s="70">
+      <x:c r="S203" s="74">
         <x:f>IF(E203&gt;0,E203,IF(D203&gt;0,IF(AND(EchFIXE,R203&gt;0),ROUND((L203-C203)*R203/(1-((1+R203)^-D203)),NbDeci),ROUND(L203/D203,NbDeci)),S202))</x:f>
       </x:c>
     </x:row>
@@ -13720,10 +13722,10 @@
         <x:f>SUM(M204:O204)</x:f>
       </x:c>
       <x:c r="Q204" s="0"/>
-      <x:c r="R204" s="71">
+      <x:c r="R204" s="75">
         <x:f>IF(B204&gt;0,IF(TauxActuariel,((B204+1)^(1/NbEchAn))-1,B204/NbEchAn),R203)</x:f>
       </x:c>
-      <x:c r="S204" s="70">
+      <x:c r="S204" s="74">
         <x:f>IF(E204&gt;0,E204,IF(D204&gt;0,IF(AND(EchFIXE,R204&gt;0),ROUND((L204-C204)*R204/(1-((1+R204)^-D204)),NbDeci),ROUND(L204/D204,NbDeci)),S203))</x:f>
       </x:c>
     </x:row>
@@ -13761,10 +13763,10 @@
         <x:f>SUM(M205:O205)</x:f>
       </x:c>
       <x:c r="Q205" s="0"/>
-      <x:c r="R205" s="71">
+      <x:c r="R205" s="75">
         <x:f>IF(B205&gt;0,IF(TauxActuariel,((B205+1)^(1/NbEchAn))-1,B205/NbEchAn),R204)</x:f>
       </x:c>
-      <x:c r="S205" s="70">
+      <x:c r="S205" s="74">
         <x:f>IF(E205&gt;0,E205,IF(D205&gt;0,IF(AND(EchFIXE,R205&gt;0),ROUND((L205-C205)*R205/(1-((1+R205)^-D205)),NbDeci),ROUND(L205/D205,NbDeci)),S204))</x:f>
       </x:c>
     </x:row>
@@ -13802,10 +13804,10 @@
         <x:f>SUM(M206:O206)</x:f>
       </x:c>
       <x:c r="Q206" s="0"/>
-      <x:c r="R206" s="71">
+      <x:c r="R206" s="75">
         <x:f>IF(B206&gt;0,IF(TauxActuariel,((B206+1)^(1/NbEchAn))-1,B206/NbEchAn),R205)</x:f>
       </x:c>
-      <x:c r="S206" s="70">
+      <x:c r="S206" s="74">
         <x:f>IF(E206&gt;0,E206,IF(D206&gt;0,IF(AND(EchFIXE,R206&gt;0),ROUND((L206-C206)*R206/(1-((1+R206)^-D206)),NbDeci),ROUND(L206/D206,NbDeci)),S205))</x:f>
       </x:c>
     </x:row>
@@ -13843,10 +13845,10 @@
         <x:f>SUM(M207:O207)</x:f>
       </x:c>
       <x:c r="Q207" s="0"/>
-      <x:c r="R207" s="71">
+      <x:c r="R207" s="75">
         <x:f>IF(B207&gt;0,IF(TauxActuariel,((B207+1)^(1/NbEchAn))-1,B207/NbEchAn),R206)</x:f>
       </x:c>
-      <x:c r="S207" s="70">
+      <x:c r="S207" s="74">
         <x:f>IF(E207&gt;0,E207,IF(D207&gt;0,IF(AND(EchFIXE,R207&gt;0),ROUND((L207-C207)*R207/(1-((1+R207)^-D207)),NbDeci),ROUND(L207/D207,NbDeci)),S206))</x:f>
       </x:c>
     </x:row>
@@ -13884,10 +13886,10 @@
         <x:f>SUM(M208:O208)</x:f>
       </x:c>
       <x:c r="Q208" s="0"/>
-      <x:c r="R208" s="71">
+      <x:c r="R208" s="75">
         <x:f>IF(B208&gt;0,IF(TauxActuariel,((B208+1)^(1/NbEchAn))-1,B208/NbEchAn),R207)</x:f>
       </x:c>
-      <x:c r="S208" s="70">
+      <x:c r="S208" s="74">
         <x:f>IF(E208&gt;0,E208,IF(D208&gt;0,IF(AND(EchFIXE,R208&gt;0),ROUND((L208-C208)*R208/(1-((1+R208)^-D208)),NbDeci),ROUND(L208/D208,NbDeci)),S207))</x:f>
       </x:c>
     </x:row>
@@ -13925,10 +13927,10 @@
         <x:f>SUM(M209:O209)</x:f>
       </x:c>
       <x:c r="Q209" s="0"/>
-      <x:c r="R209" s="71">
+      <x:c r="R209" s="75">
         <x:f>IF(B209&gt;0,IF(TauxActuariel,((B209+1)^(1/NbEchAn))-1,B209/NbEchAn),R208)</x:f>
       </x:c>
-      <x:c r="S209" s="70">
+      <x:c r="S209" s="74">
         <x:f>IF(E209&gt;0,E209,IF(D209&gt;0,IF(AND(EchFIXE,R209&gt;0),ROUND((L209-C209)*R209/(1-((1+R209)^-D209)),NbDeci),ROUND(L209/D209,NbDeci)),S208))</x:f>
       </x:c>
     </x:row>
@@ -13966,10 +13968,10 @@
         <x:f>SUM(M210:O210)</x:f>
       </x:c>
       <x:c r="Q210" s="0"/>
-      <x:c r="R210" s="71">
+      <x:c r="R210" s="75">
         <x:f>IF(B210&gt;0,IF(TauxActuariel,((B210+1)^(1/NbEchAn))-1,B210/NbEchAn),R209)</x:f>
       </x:c>
-      <x:c r="S210" s="70">
+      <x:c r="S210" s="74">
         <x:f>IF(E210&gt;0,E210,IF(D210&gt;0,IF(AND(EchFIXE,R210&gt;0),ROUND((L210-C210)*R210/(1-((1+R210)^-D210)),NbDeci),ROUND(L210/D210,NbDeci)),S209))</x:f>
       </x:c>
     </x:row>
@@ -14007,10 +14009,10 @@
         <x:f>SUM(M211:O211)</x:f>
       </x:c>
       <x:c r="Q211" s="0"/>
-      <x:c r="R211" s="71">
+      <x:c r="R211" s="75">
         <x:f>IF(B211&gt;0,IF(TauxActuariel,((B211+1)^(1/NbEchAn))-1,B211/NbEchAn),R210)</x:f>
       </x:c>
-      <x:c r="S211" s="70">
+      <x:c r="S211" s="74">
         <x:f>IF(E211&gt;0,E211,IF(D211&gt;0,IF(AND(EchFIXE,R211&gt;0),ROUND((L211-C211)*R211/(1-((1+R211)^-D211)),NbDeci),ROUND(L211/D211,NbDeci)),S210))</x:f>
       </x:c>
     </x:row>
@@ -14048,10 +14050,10 @@
         <x:f>SUM(M212:O212)</x:f>
       </x:c>
       <x:c r="Q212" s="0"/>
-      <x:c r="R212" s="71">
+      <x:c r="R212" s="75">
         <x:f>IF(B212&gt;0,IF(TauxActuariel,((B212+1)^(1/NbEchAn))-1,B212/NbEchAn),R211)</x:f>
       </x:c>
-      <x:c r="S212" s="70">
+      <x:c r="S212" s="74">
         <x:f>IF(E212&gt;0,E212,IF(D212&gt;0,IF(AND(EchFIXE,R212&gt;0),ROUND((L212-C212)*R212/(1-((1+R212)^-D212)),NbDeci),ROUND(L212/D212,NbDeci)),S211))</x:f>
       </x:c>
     </x:row>
@@ -14089,10 +14091,10 @@
         <x:f>SUM(M213:O213)</x:f>
       </x:c>
       <x:c r="Q213" s="0"/>
-      <x:c r="R213" s="71">
+      <x:c r="R213" s="75">
         <x:f>IF(B213&gt;0,IF(TauxActuariel,((B213+1)^(1/NbEchAn))-1,B213/NbEchAn),R212)</x:f>
       </x:c>
-      <x:c r="S213" s="70">
+      <x:c r="S213" s="74">
         <x:f>IF(E213&gt;0,E213,IF(D213&gt;0,IF(AND(EchFIXE,R213&gt;0),ROUND((L213-C213)*R213/(1-((1+R213)^-D213)),NbDeci),ROUND(L213/D213,NbDeci)),S212))</x:f>
       </x:c>
     </x:row>
@@ -14130,10 +14132,10 @@
         <x:f>SUM(M214:O214)</x:f>
       </x:c>
       <x:c r="Q214" s="0"/>
-      <x:c r="R214" s="71">
+      <x:c r="R214" s="75">
         <x:f>IF(B214&gt;0,IF(TauxActuariel,((B214+1)^(1/NbEchAn))-1,B214/NbEchAn),R213)</x:f>
       </x:c>
-      <x:c r="S214" s="70">
+      <x:c r="S214" s="74">
         <x:f>IF(E214&gt;0,E214,IF(D214&gt;0,IF(AND(EchFIXE,R214&gt;0),ROUND((L214-C214)*R214/(1-((1+R214)^-D214)),NbDeci),ROUND(L214/D214,NbDeci)),S213))</x:f>
       </x:c>
     </x:row>
@@ -14171,10 +14173,10 @@
         <x:f>SUM(M215:O215)</x:f>
       </x:c>
       <x:c r="Q215" s="0"/>
-      <x:c r="R215" s="71">
+      <x:c r="R215" s="75">
         <x:f>IF(B215&gt;0,IF(TauxActuariel,((B215+1)^(1/NbEchAn))-1,B215/NbEchAn),R214)</x:f>
       </x:c>
-      <x:c r="S215" s="70">
+      <x:c r="S215" s="74">
         <x:f>IF(E215&gt;0,E215,IF(D215&gt;0,IF(AND(EchFIXE,R215&gt;0),ROUND((L215-C215)*R215/(1-((1+R215)^-D215)),NbDeci),ROUND(L215/D215,NbDeci)),S214))</x:f>
       </x:c>
     </x:row>
@@ -14212,10 +14214,10 @@
         <x:f>SUM(M216:O216)</x:f>
       </x:c>
       <x:c r="Q216" s="0"/>
-      <x:c r="R216" s="71">
+      <x:c r="R216" s="75">
         <x:f>IF(B216&gt;0,IF(TauxActuariel,((B216+1)^(1/NbEchAn))-1,B216/NbEchAn),R215)</x:f>
       </x:c>
-      <x:c r="S216" s="70">
+      <x:c r="S216" s="74">
         <x:f>IF(E216&gt;0,E216,IF(D216&gt;0,IF(AND(EchFIXE,R216&gt;0),ROUND((L216-C216)*R216/(1-((1+R216)^-D216)),NbDeci),ROUND(L216/D216,NbDeci)),S215))</x:f>
       </x:c>
     </x:row>
@@ -14253,10 +14255,10 @@
         <x:f>SUM(M217:O217)</x:f>
       </x:c>
       <x:c r="Q217" s="0"/>
-      <x:c r="R217" s="71">
+      <x:c r="R217" s="75">
         <x:f>IF(B217&gt;0,IF(TauxActuariel,((B217+1)^(1/NbEchAn))-1,B217/NbEchAn),R216)</x:f>
       </x:c>
-      <x:c r="S217" s="70">
+      <x:c r="S217" s="74">
         <x:f>IF(E217&gt;0,E217,IF(D217&gt;0,IF(AND(EchFIXE,R217&gt;0),ROUND((L217-C217)*R217/(1-((1+R217)^-D217)),NbDeci),ROUND(L217/D217,NbDeci)),S216))</x:f>
       </x:c>
     </x:row>
@@ -14294,10 +14296,10 @@
         <x:f>SUM(M218:O218)</x:f>
       </x:c>
       <x:c r="Q218" s="0"/>
-      <x:c r="R218" s="71">
+      <x:c r="R218" s="75">
         <x:f>IF(B218&gt;0,IF(TauxActuariel,((B218+1)^(1/NbEchAn))-1,B218/NbEchAn),R217)</x:f>
       </x:c>
-      <x:c r="S218" s="70">
+      <x:c r="S218" s="74">
         <x:f>IF(E218&gt;0,E218,IF(D218&gt;0,IF(AND(EchFIXE,R218&gt;0),ROUND((L218-C218)*R218/(1-((1+R218)^-D218)),NbDeci),ROUND(L218/D218,NbDeci)),S217))</x:f>
       </x:c>
     </x:row>
@@ -14335,10 +14337,10 @@
         <x:f>SUM(M219:O219)</x:f>
       </x:c>
       <x:c r="Q219" s="0"/>
-      <x:c r="R219" s="71">
+      <x:c r="R219" s="75">
         <x:f>IF(B219&gt;0,IF(TauxActuariel,((B219+1)^(1/NbEchAn))-1,B219/NbEchAn),R218)</x:f>
       </x:c>
-      <x:c r="S219" s="70">
+      <x:c r="S219" s="74">
         <x:f>IF(E219&gt;0,E219,IF(D219&gt;0,IF(AND(EchFIXE,R219&gt;0),ROUND((L219-C219)*R219/(1-((1+R219)^-D219)),NbDeci),ROUND(L219/D219,NbDeci)),S218))</x:f>
       </x:c>
     </x:row>
@@ -14376,10 +14378,10 @@
         <x:f>SUM(M220:O220)</x:f>
       </x:c>
       <x:c r="Q220" s="0"/>
-      <x:c r="R220" s="71">
+      <x:c r="R220" s="75">
         <x:f>IF(B220&gt;0,IF(TauxActuariel,((B220+1)^(1/NbEchAn))-1,B220/NbEchAn),R219)</x:f>
       </x:c>
-      <x:c r="S220" s="70">
+      <x:c r="S220" s="74">
         <x:f>IF(E220&gt;0,E220,IF(D220&gt;0,IF(AND(EchFIXE,R220&gt;0),ROUND((L220-C220)*R220/(1-((1+R220)^-D220)),NbDeci),ROUND(L220/D220,NbDeci)),S219))</x:f>
       </x:c>
     </x:row>
@@ -14417,10 +14419,10 @@
         <x:f>SUM(M221:O221)</x:f>
       </x:c>
       <x:c r="Q221" s="0"/>
-      <x:c r="R221" s="71">
+      <x:c r="R221" s="75">
         <x:f>IF(B221&gt;0,IF(TauxActuariel,((B221+1)^(1/NbEchAn))-1,B221/NbEchAn),R220)</x:f>
       </x:c>
-      <x:c r="S221" s="70">
+      <x:c r="S221" s="74">
         <x:f>IF(E221&gt;0,E221,IF(D221&gt;0,IF(AND(EchFIXE,R221&gt;0),ROUND((L221-C221)*R221/(1-((1+R221)^-D221)),NbDeci),ROUND(L221/D221,NbDeci)),S220))</x:f>
       </x:c>
     </x:row>
@@ -14458,10 +14460,10 @@
         <x:f>SUM(M222:O222)</x:f>
       </x:c>
       <x:c r="Q222" s="0"/>
-      <x:c r="R222" s="71">
+      <x:c r="R222" s="75">
         <x:f>IF(B222&gt;0,IF(TauxActuariel,((B222+1)^(1/NbEchAn))-1,B222/NbEchAn),R221)</x:f>
       </x:c>
-      <x:c r="S222" s="70">
+      <x:c r="S222" s="74">
         <x:f>IF(E222&gt;0,E222,IF(D222&gt;0,IF(AND(EchFIXE,R222&gt;0),ROUND((L222-C222)*R222/(1-((1+R222)^-D222)),NbDeci),ROUND(L222/D222,NbDeci)),S221))</x:f>
       </x:c>
     </x:row>
@@ -14499,10 +14501,10 @@
         <x:f>SUM(M223:O223)</x:f>
       </x:c>
       <x:c r="Q223" s="0"/>
-      <x:c r="R223" s="71">
+      <x:c r="R223" s="75">
         <x:f>IF(B223&gt;0,IF(TauxActuariel,((B223+1)^(1/NbEchAn))-1,B223/NbEchAn),R222)</x:f>
       </x:c>
-      <x:c r="S223" s="70">
+      <x:c r="S223" s="74">
         <x:f>IF(E223&gt;0,E223,IF(D223&gt;0,IF(AND(EchFIXE,R223&gt;0),ROUND((L223-C223)*R223/(1-((1+R223)^-D223)),NbDeci),ROUND(L223/D223,NbDeci)),S222))</x:f>
       </x:c>
     </x:row>
@@ -14540,10 +14542,10 @@
         <x:f>SUM(M224:O224)</x:f>
       </x:c>
       <x:c r="Q224" s="0"/>
-      <x:c r="R224" s="71">
+      <x:c r="R224" s="75">
         <x:f>IF(B224&gt;0,IF(TauxActuariel,((B224+1)^(1/NbEchAn))-1,B224/NbEchAn),R223)</x:f>
       </x:c>
-      <x:c r="S224" s="70">
+      <x:c r="S224" s="74">
         <x:f>IF(E224&gt;0,E224,IF(D224&gt;0,IF(AND(EchFIXE,R224&gt;0),ROUND((L224-C224)*R224/(1-((1+R224)^-D224)),NbDeci),ROUND(L224/D224,NbDeci)),S223))</x:f>
       </x:c>
     </x:row>
@@ -14581,10 +14583,10 @@
         <x:f>SUM(M225:O225)</x:f>
       </x:c>
       <x:c r="Q225" s="0"/>
-      <x:c r="R225" s="71">
+      <x:c r="R225" s="75">
         <x:f>IF(B225&gt;0,IF(TauxActuariel,((B225+1)^(1/NbEchAn))-1,B225/NbEchAn),R224)</x:f>
       </x:c>
-      <x:c r="S225" s="70">
+      <x:c r="S225" s="74">
         <x:f>IF(E225&gt;0,E225,IF(D225&gt;0,IF(AND(EchFIXE,R225&gt;0),ROUND((L225-C225)*R225/(1-((1+R225)^-D225)),NbDeci),ROUND(L225/D225,NbDeci)),S224))</x:f>
       </x:c>
     </x:row>
@@ -14622,10 +14624,10 @@
         <x:f>SUM(M226:O226)</x:f>
       </x:c>
       <x:c r="Q226" s="0"/>
-      <x:c r="R226" s="71">
+      <x:c r="R226" s="75">
         <x:f>IF(B226&gt;0,IF(TauxActuariel,((B226+1)^(1/NbEchAn))-1,B226/NbEchAn),R225)</x:f>
       </x:c>
-      <x:c r="S226" s="70">
+      <x:c r="S226" s="74">
         <x:f>IF(E226&gt;0,E226,IF(D226&gt;0,IF(AND(EchFIXE,R226&gt;0),ROUND((L226-C226)*R226/(1-((1+R226)^-D226)),NbDeci),ROUND(L226/D226,NbDeci)),S225))</x:f>
       </x:c>
     </x:row>
@@ -14663,10 +14665,10 @@
         <x:f>SUM(M227:O227)</x:f>
       </x:c>
       <x:c r="Q227" s="0"/>
-      <x:c r="R227" s="71">
+      <x:c r="R227" s="75">
         <x:f>IF(B227&gt;0,IF(TauxActuariel,((B227+1)^(1/NbEchAn))-1,B227/NbEchAn),R226)</x:f>
       </x:c>
-      <x:c r="S227" s="70">
+      <x:c r="S227" s="74">
         <x:f>IF(E227&gt;0,E227,IF(D227&gt;0,IF(AND(EchFIXE,R227&gt;0),ROUND((L227-C227)*R227/(1-((1+R227)^-D227)),NbDeci),ROUND(L227/D227,NbDeci)),S226))</x:f>
       </x:c>
     </x:row>
@@ -14704,10 +14706,10 @@
         <x:f>SUM(M228:O228)</x:f>
       </x:c>
       <x:c r="Q228" s="0"/>
-      <x:c r="R228" s="71">
+      <x:c r="R228" s="75">
         <x:f>IF(B228&gt;0,IF(TauxActuariel,((B228+1)^(1/NbEchAn))-1,B228/NbEchAn),R227)</x:f>
       </x:c>
-      <x:c r="S228" s="70">
+      <x:c r="S228" s="74">
         <x:f>IF(E228&gt;0,E228,IF(D228&gt;0,IF(AND(EchFIXE,R228&gt;0),ROUND((L228-C228)*R228/(1-((1+R228)^-D228)),NbDeci),ROUND(L228/D228,NbDeci)),S227))</x:f>
       </x:c>
     </x:row>
@@ -14745,10 +14747,10 @@
         <x:f>SUM(M229:O229)</x:f>
       </x:c>
       <x:c r="Q229" s="0"/>
-      <x:c r="R229" s="71">
+      <x:c r="R229" s="75">
         <x:f>IF(B229&gt;0,IF(TauxActuariel,((B229+1)^(1/NbEchAn))-1,B229/NbEchAn),R228)</x:f>
       </x:c>
-      <x:c r="S229" s="70">
+      <x:c r="S229" s="74">
         <x:f>IF(E229&gt;0,E229,IF(D229&gt;0,IF(AND(EchFIXE,R229&gt;0),ROUND((L229-C229)*R229/(1-((1+R229)^-D229)),NbDeci),ROUND(L229/D229,NbDeci)),S228))</x:f>
       </x:c>
     </x:row>
@@ -14786,10 +14788,10 @@
         <x:f>SUM(M230:O230)</x:f>
       </x:c>
       <x:c r="Q230" s="0"/>
-      <x:c r="R230" s="71">
+      <x:c r="R230" s="75">
         <x:f>IF(B230&gt;0,IF(TauxActuariel,((B230+1)^(1/NbEchAn))-1,B230/NbEchAn),R229)</x:f>
       </x:c>
-      <x:c r="S230" s="70">
+      <x:c r="S230" s="74">
         <x:f>IF(E230&gt;0,E230,IF(D230&gt;0,IF(AND(EchFIXE,R230&gt;0),ROUND((L230-C230)*R230/(1-((1+R230)^-D230)),NbDeci),ROUND(L230/D230,NbDeci)),S229))</x:f>
       </x:c>
     </x:row>
@@ -14827,10 +14829,10 @@
         <x:f>SUM(M231:O231)</x:f>
       </x:c>
       <x:c r="Q231" s="0"/>
-      <x:c r="R231" s="71">
+      <x:c r="R231" s="75">
         <x:f>IF(B231&gt;0,IF(TauxActuariel,((B231+1)^(1/NbEchAn))-1,B231/NbEchAn),R230)</x:f>
       </x:c>
-      <x:c r="S231" s="70">
+      <x:c r="S231" s="74">
         <x:f>IF(E231&gt;0,E231,IF(D231&gt;0,IF(AND(EchFIXE,R231&gt;0),ROUND((L231-C231)*R231/(1-((1+R231)^-D231)),NbDeci),ROUND(L231/D231,NbDeci)),S230))</x:f>
       </x:c>
     </x:row>
@@ -14868,10 +14870,10 @@
         <x:f>SUM(M232:O232)</x:f>
       </x:c>
       <x:c r="Q232" s="0"/>
-      <x:c r="R232" s="71">
+      <x:c r="R232" s="75">
         <x:f>IF(B232&gt;0,IF(TauxActuariel,((B232+1)^(1/NbEchAn))-1,B232/NbEchAn),R231)</x:f>
       </x:c>
-      <x:c r="S232" s="70">
+      <x:c r="S232" s="74">
         <x:f>IF(E232&gt;0,E232,IF(D232&gt;0,IF(AND(EchFIXE,R232&gt;0),ROUND((L232-C232)*R232/(1-((1+R232)^-D232)),NbDeci),ROUND(L232/D232,NbDeci)),S231))</x:f>
       </x:c>
     </x:row>
@@ -14909,10 +14911,10 @@
         <x:f>SUM(M233:O233)</x:f>
       </x:c>
       <x:c r="Q233" s="0"/>
-      <x:c r="R233" s="71">
+      <x:c r="R233" s="75">
         <x:f>IF(B233&gt;0,IF(TauxActuariel,((B233+1)^(1/NbEchAn))-1,B233/NbEchAn),R232)</x:f>
       </x:c>
-      <x:c r="S233" s="70">
+      <x:c r="S233" s="74">
         <x:f>IF(E233&gt;0,E233,IF(D233&gt;0,IF(AND(EchFIXE,R233&gt;0),ROUND((L233-C233)*R233/(1-((1+R233)^-D233)),NbDeci),ROUND(L233/D233,NbDeci)),S232))</x:f>
       </x:c>
     </x:row>
@@ -14950,10 +14952,10 @@
         <x:f>SUM(M234:O234)</x:f>
       </x:c>
       <x:c r="Q234" s="0"/>
-      <x:c r="R234" s="71">
+      <x:c r="R234" s="75">
         <x:f>IF(B234&gt;0,IF(TauxActuariel,((B234+1)^(1/NbEchAn))-1,B234/NbEchAn),R233)</x:f>
       </x:c>
-      <x:c r="S234" s="70">
+      <x:c r="S234" s="74">
         <x:f>IF(E234&gt;0,E234,IF(D234&gt;0,IF(AND(EchFIXE,R234&gt;0),ROUND((L234-C234)*R234/(1-((1+R234)^-D234)),NbDeci),ROUND(L234/D234,NbDeci)),S233))</x:f>
       </x:c>
     </x:row>
@@ -14991,10 +14993,10 @@
         <x:f>SUM(M235:O235)</x:f>
       </x:c>
       <x:c r="Q235" s="0"/>
-      <x:c r="R235" s="71">
+      <x:c r="R235" s="75">
         <x:f>IF(B235&gt;0,IF(TauxActuariel,((B235+1)^(1/NbEchAn))-1,B235/NbEchAn),R234)</x:f>
       </x:c>
-      <x:c r="S235" s="70">
+      <x:c r="S235" s="74">
         <x:f>IF(E235&gt;0,E235,IF(D235&gt;0,IF(AND(EchFIXE,R235&gt;0),ROUND((L235-C235)*R235/(1-((1+R235)^-D235)),NbDeci),ROUND(L235/D235,NbDeci)),S234))</x:f>
       </x:c>
     </x:row>
@@ -15032,10 +15034,10 @@
         <x:f>SUM(M236:O236)</x:f>
       </x:c>
       <x:c r="Q236" s="0"/>
-      <x:c r="R236" s="71">
+      <x:c r="R236" s="75">
         <x:f>IF(B236&gt;0,IF(TauxActuariel,((B236+1)^(1/NbEchAn))-1,B236/NbEchAn),R235)</x:f>
       </x:c>
-      <x:c r="S236" s="70">
+      <x:c r="S236" s="74">
         <x:f>IF(E236&gt;0,E236,IF(D236&gt;0,IF(AND(EchFIXE,R236&gt;0),ROUND((L236-C236)*R236/(1-((1+R236)^-D236)),NbDeci),ROUND(L236/D236,NbDeci)),S235))</x:f>
       </x:c>
     </x:row>
@@ -15073,10 +15075,10 @@
         <x:f>SUM(M237:O237)</x:f>
       </x:c>
       <x:c r="Q237" s="0"/>
-      <x:c r="R237" s="71">
+      <x:c r="R237" s="75">
         <x:f>IF(B237&gt;0,IF(TauxActuariel,((B237+1)^(1/NbEchAn))-1,B237/NbEchAn),R236)</x:f>
       </x:c>
-      <x:c r="S237" s="70">
+      <x:c r="S237" s="74">
         <x:f>IF(E237&gt;0,E237,IF(D237&gt;0,IF(AND(EchFIXE,R237&gt;0),ROUND((L237-C237)*R237/(1-((1+R237)^-D237)),NbDeci),ROUND(L237/D237,NbDeci)),S236))</x:f>
       </x:c>
     </x:row>
@@ -15114,10 +15116,10 @@
         <x:f>SUM(M238:O238)</x:f>
       </x:c>
       <x:c r="Q238" s="0"/>
-      <x:c r="R238" s="71">
+      <x:c r="R238" s="75">
         <x:f>IF(B238&gt;0,IF(TauxActuariel,((B238+1)^(1/NbEchAn))-1,B238/NbEchAn),R237)</x:f>
       </x:c>
-      <x:c r="S238" s="70">
+      <x:c r="S238" s="74">
         <x:f>IF(E238&gt;0,E238,IF(D238&gt;0,IF(AND(EchFIXE,R238&gt;0),ROUND((L238-C238)*R238/(1-((1+R238)^-D238)),NbDeci),ROUND(L238/D238,NbDeci)),S237))</x:f>
       </x:c>
     </x:row>
@@ -15155,10 +15157,10 @@
         <x:f>SUM(M239:O239)</x:f>
       </x:c>
       <x:c r="Q239" s="0"/>
-      <x:c r="R239" s="71">
+      <x:c r="R239" s="75">
         <x:f>IF(B239&gt;0,IF(TauxActuariel,((B239+1)^(1/NbEchAn))-1,B239/NbEchAn),R238)</x:f>
       </x:c>
-      <x:c r="S239" s="70">
+      <x:c r="S239" s="74">
         <x:f>IF(E239&gt;0,E239,IF(D239&gt;0,IF(AND(EchFIXE,R239&gt;0),ROUND((L239-C239)*R239/(1-((1+R239)^-D239)),NbDeci),ROUND(L239/D239,NbDeci)),S238))</x:f>
       </x:c>
     </x:row>
@@ -15196,10 +15198,10 @@
         <x:f>SUM(M240:O240)</x:f>
       </x:c>
       <x:c r="Q240" s="0"/>
-      <x:c r="R240" s="71">
+      <x:c r="R240" s="75">
         <x:f>IF(B240&gt;0,IF(TauxActuariel,((B240+1)^(1/NbEchAn))-1,B240/NbEchAn),R239)</x:f>
       </x:c>
-      <x:c r="S240" s="70">
+      <x:c r="S240" s="74">
         <x:f>IF(E240&gt;0,E240,IF(D240&gt;0,IF(AND(EchFIXE,R240&gt;0),ROUND((L240-C240)*R240/(1-((1+R240)^-D240)),NbDeci),ROUND(L240/D240,NbDeci)),S239))</x:f>
       </x:c>
     </x:row>
@@ -15237,10 +15239,10 @@
         <x:f>SUM(M241:O241)</x:f>
       </x:c>
       <x:c r="Q241" s="0"/>
-      <x:c r="R241" s="71">
+      <x:c r="R241" s="75">
         <x:f>IF(B241&gt;0,IF(TauxActuariel,((B241+1)^(1/NbEchAn))-1,B241/NbEchAn),R240)</x:f>
       </x:c>
-      <x:c r="S241" s="70">
+      <x:c r="S241" s="74">
         <x:f>IF(E241&gt;0,E241,IF(D241&gt;0,IF(AND(EchFIXE,R241&gt;0),ROUND((L241-C241)*R241/(1-((1+R241)^-D241)),NbDeci),ROUND(L241/D241,NbDeci)),S240))</x:f>
       </x:c>
     </x:row>
@@ -15278,10 +15280,10 @@
         <x:f>SUM(M242:O242)</x:f>
       </x:c>
       <x:c r="Q242" s="0"/>
-      <x:c r="R242" s="71">
+      <x:c r="R242" s="75">
         <x:f>IF(B242&gt;0,IF(TauxActuariel,((B242+1)^(1/NbEchAn))-1,B242/NbEchAn),R241)</x:f>
       </x:c>
-      <x:c r="S242" s="70">
+      <x:c r="S242" s="74">
         <x:f>IF(E242&gt;0,E242,IF(D242&gt;0,IF(AND(EchFIXE,R242&gt;0),ROUND((L242-C242)*R242/(1-((1+R242)^-D242)),NbDeci),ROUND(L242/D242,NbDeci)),S241))</x:f>
       </x:c>
     </x:row>
@@ -15319,10 +15321,10 @@
         <x:f>SUM(M243:O243)</x:f>
       </x:c>
       <x:c r="Q243" s="0"/>
-      <x:c r="R243" s="71">
+      <x:c r="R243" s="75">
         <x:f>IF(B243&gt;0,IF(TauxActuariel,((B243+1)^(1/NbEchAn))-1,B243/NbEchAn),R242)</x:f>
       </x:c>
-      <x:c r="S243" s="70">
+      <x:c r="S243" s="74">
         <x:f>IF(E243&gt;0,E243,IF(D243&gt;0,IF(AND(EchFIXE,R243&gt;0),ROUND((L243-C243)*R243/(1-((1+R243)^-D243)),NbDeci),ROUND(L243/D243,NbDeci)),S242))</x:f>
       </x:c>
     </x:row>
@@ -15360,10 +15362,10 @@
         <x:f>SUM(M244:O244)</x:f>
       </x:c>
       <x:c r="Q244" s="0"/>
-      <x:c r="R244" s="71">
+      <x:c r="R244" s="75">
         <x:f>IF(B244&gt;0,IF(TauxActuariel,((B244+1)^(1/NbEchAn))-1,B244/NbEchAn),R243)</x:f>
       </x:c>
-      <x:c r="S244" s="70">
+      <x:c r="S244" s="74">
         <x:f>IF(E244&gt;0,E244,IF(D244&gt;0,IF(AND(EchFIXE,R244&gt;0),ROUND((L244-C244)*R244/(1-((1+R244)^-D244)),NbDeci),ROUND(L244/D244,NbDeci)),S243))</x:f>
       </x:c>
     </x:row>
@@ -15401,10 +15403,10 @@
         <x:f>SUM(M245:O245)</x:f>
       </x:c>
       <x:c r="Q245" s="0"/>
-      <x:c r="R245" s="71">
+      <x:c r="R245" s="75">
         <x:f>IF(B245&gt;0,IF(TauxActuariel,((B245+1)^(1/NbEchAn))-1,B245/NbEchAn),R244)</x:f>
       </x:c>
-      <x:c r="S245" s="70">
+      <x:c r="S245" s="74">
         <x:f>IF(E245&gt;0,E245,IF(D245&gt;0,IF(AND(EchFIXE,R245&gt;0),ROUND((L245-C245)*R245/(1-((1+R245)^-D245)),NbDeci),ROUND(L245/D245,NbDeci)),S244))</x:f>
       </x:c>
     </x:row>
@@ -15442,10 +15444,10 @@
         <x:f>SUM(M246:O246)</x:f>
       </x:c>
       <x:c r="Q246" s="0"/>
-      <x:c r="R246" s="71">
+      <x:c r="R246" s="75">
         <x:f>IF(B246&gt;0,IF(TauxActuariel,((B246+1)^(1/NbEchAn))-1,B246/NbEchAn),R245)</x:f>
       </x:c>
-      <x:c r="S246" s="70">
+      <x:c r="S246" s="74">
         <x:f>IF(E246&gt;0,E246,IF(D246&gt;0,IF(AND(EchFIXE,R246&gt;0),ROUND((L246-C246)*R246/(1-((1+R246)^-D246)),NbDeci),ROUND(L246/D246,NbDeci)),S245))</x:f>
       </x:c>
     </x:row>
@@ -15483,10 +15485,10 @@
         <x:f>SUM(M247:O247)</x:f>
       </x:c>
       <x:c r="Q247" s="0"/>
-      <x:c r="R247" s="71">
+      <x:c r="R247" s="75">
         <x:f>IF(B247&gt;0,IF(TauxActuariel,((B247+1)^(1/NbEchAn))-1,B247/NbEchAn),R246)</x:f>
       </x:c>
-      <x:c r="S247" s="70">
+      <x:c r="S247" s="74">
         <x:f>IF(E247&gt;0,E247,IF(D247&gt;0,IF(AND(EchFIXE,R247&gt;0),ROUND((L247-C247)*R247/(1-((1+R247)^-D247)),NbDeci),ROUND(L247/D247,NbDeci)),S246))</x:f>
       </x:c>
     </x:row>
@@ -15524,10 +15526,10 @@
         <x:f>SUM(M248:O248)</x:f>
       </x:c>
       <x:c r="Q248" s="0"/>
-      <x:c r="R248" s="71">
+      <x:c r="R248" s="75">
         <x:f>IF(B248&gt;0,IF(TauxActuariel,((B248+1)^(1/NbEchAn))-1,B248/NbEchAn),R247)</x:f>
       </x:c>
-      <x:c r="S248" s="70">
+      <x:c r="S248" s="74">
         <x:f>IF(E248&gt;0,E248,IF(D248&gt;0,IF(AND(EchFIXE,R248&gt;0),ROUND((L248-C248)*R248/(1-((1+R248)^-D248)),NbDeci),ROUND(L248/D248,NbDeci)),S247))</x:f>
       </x:c>
     </x:row>
@@ -15565,10 +15567,10 @@
         <x:f>SUM(M249:O249)</x:f>
       </x:c>
       <x:c r="Q249" s="0"/>
-      <x:c r="R249" s="71">
+      <x:c r="R249" s="75">
         <x:f>IF(B249&gt;0,IF(TauxActuariel,((B249+1)^(1/NbEchAn))-1,B249/NbEchAn),R248)</x:f>
       </x:c>
-      <x:c r="S249" s="70">
+      <x:c r="S249" s="74">
         <x:f>IF(E249&gt;0,E249,IF(D249&gt;0,IF(AND(EchFIXE,R249&gt;0),ROUND((L249-C249)*R249/(1-((1+R249)^-D249)),NbDeci),ROUND(L249/D249,NbDeci)),S248))</x:f>
       </x:c>
     </x:row>
@@ -15606,10 +15608,10 @@
         <x:f>SUM(M250:O250)</x:f>
       </x:c>
       <x:c r="Q250" s="0"/>
-      <x:c r="R250" s="71">
+      <x:c r="R250" s="75">
         <x:f>IF(B250&gt;0,IF(TauxActuariel,((B250+1)^(1/NbEchAn))-1,B250/NbEchAn),R249)</x:f>
       </x:c>
-      <x:c r="S250" s="70">
+      <x:c r="S250" s="74">
         <x:f>IF(E250&gt;0,E250,IF(D250&gt;0,IF(AND(EchFIXE,R250&gt;0),ROUND((L250-C250)*R250/(1-((1+R250)^-D250)),NbDeci),ROUND(L250/D250,NbDeci)),S249))</x:f>
       </x:c>
     </x:row>
@@ -15647,10 +15649,10 @@
         <x:f>SUM(M251:O251)</x:f>
       </x:c>
       <x:c r="Q251" s="0"/>
-      <x:c r="R251" s="71">
+      <x:c r="R251" s="75">
         <x:f>IF(B251&gt;0,IF(TauxActuariel,((B251+1)^(1/NbEchAn))-1,B251/NbEchAn),R250)</x:f>
       </x:c>
-      <x:c r="S251" s="70">
+      <x:c r="S251" s="74">
         <x:f>IF(E251&gt;0,E251,IF(D251&gt;0,IF(AND(EchFIXE,R251&gt;0),ROUND((L251-C251)*R251/(1-((1+R251)^-D251)),NbDeci),ROUND(L251/D251,NbDeci)),S250))</x:f>
       </x:c>
     </x:row>
@@ -15688,10 +15690,10 @@
         <x:f>SUM(M252:O252)</x:f>
       </x:c>
       <x:c r="Q252" s="0"/>
-      <x:c r="R252" s="71">
+      <x:c r="R252" s="75">
         <x:f>IF(B252&gt;0,IF(TauxActuariel,((B252+1)^(1/NbEchAn))-1,B252/NbEchAn),R251)</x:f>
       </x:c>
-      <x:c r="S252" s="70">
+      <x:c r="S252" s="74">
         <x:f>IF(E252&gt;0,E252,IF(D252&gt;0,IF(AND(EchFIXE,R252&gt;0),ROUND((L252-C252)*R252/(1-((1+R252)^-D252)),NbDeci),ROUND(L252/D252,NbDeci)),S251))</x:f>
       </x:c>
     </x:row>
@@ -15729,10 +15731,10 @@
         <x:f>SUM(M253:O253)</x:f>
       </x:c>
       <x:c r="Q253" s="0"/>
-      <x:c r="R253" s="71">
+      <x:c r="R253" s="75">
         <x:f>IF(B253&gt;0,IF(TauxActuariel,((B253+1)^(1/NbEchAn))-1,B253/NbEchAn),R252)</x:f>
       </x:c>
-      <x:c r="S253" s="70">
+      <x:c r="S253" s="74">
         <x:f>IF(E253&gt;0,E253,IF(D253&gt;0,IF(AND(EchFIXE,R253&gt;0),ROUND((L253-C253)*R253/(1-((1+R253)^-D253)),NbDeci),ROUND(L253/D253,NbDeci)),S252))</x:f>
       </x:c>
     </x:row>
@@ -15770,10 +15772,10 @@
         <x:f>SUM(M254:O254)</x:f>
       </x:c>
       <x:c r="Q254" s="0"/>
-      <x:c r="R254" s="71">
+      <x:c r="R254" s="75">
         <x:f>IF(B254&gt;0,IF(TauxActuariel,((B254+1)^(1/NbEchAn))-1,B254/NbEchAn),R253)</x:f>
       </x:c>
-      <x:c r="S254" s="70">
+      <x:c r="S254" s="74">
         <x:f>IF(E254&gt;0,E254,IF(D254&gt;0,IF(AND(EchFIXE,R254&gt;0),ROUND((L254-C254)*R254/(1-((1+R254)^-D254)),NbDeci),ROUND(L254/D254,NbDeci)),S253))</x:f>
       </x:c>
     </x:row>
@@ -15811,10 +15813,10 @@
         <x:f>SUM(M255:O255)</x:f>
       </x:c>
       <x:c r="Q255" s="0"/>
-      <x:c r="R255" s="71">
+      <x:c r="R255" s="75">
         <x:f>IF(B255&gt;0,IF(TauxActuariel,((B255+1)^(1/NbEchAn))-1,B255/NbEchAn),R254)</x:f>
       </x:c>
-      <x:c r="S255" s="70">
+      <x:c r="S255" s="74">
         <x:f>IF(E255&gt;0,E255,IF(D255&gt;0,IF(AND(EchFIXE,R255&gt;0),ROUND((L255-C255)*R255/(1-((1+R255)^-D255)),NbDeci),ROUND(L255/D255,NbDeci)),S254))</x:f>
       </x:c>
     </x:row>
@@ -15852,10 +15854,10 @@
         <x:f>SUM(M256:O256)</x:f>
       </x:c>
       <x:c r="Q256" s="0"/>
-      <x:c r="R256" s="71">
+      <x:c r="R256" s="75">
         <x:f>IF(B256&gt;0,IF(TauxActuariel,((B256+1)^(1/NbEchAn))-1,B256/NbEchAn),R255)</x:f>
       </x:c>
-      <x:c r="S256" s="70">
+      <x:c r="S256" s="74">
         <x:f>IF(E256&gt;0,E256,IF(D256&gt;0,IF(AND(EchFIXE,R256&gt;0),ROUND((L256-C256)*R256/(1-((1+R256)^-D256)),NbDeci),ROUND(L256/D256,NbDeci)),S255))</x:f>
       </x:c>
     </x:row>
@@ -15893,10 +15895,10 @@
         <x:f>SUM(M257:O257)</x:f>
       </x:c>
       <x:c r="Q257" s="0"/>
-      <x:c r="R257" s="71">
+      <x:c r="R257" s="75">
         <x:f>IF(B257&gt;0,IF(TauxActuariel,((B257+1)^(1/NbEchAn))-1,B257/NbEchAn),R256)</x:f>
       </x:c>
-      <x:c r="S257" s="70">
+      <x:c r="S257" s="74">
         <x:f>IF(E257&gt;0,E257,IF(D257&gt;0,IF(AND(EchFIXE,R257&gt;0),ROUND((L257-C257)*R257/(1-((1+R257)^-D257)),NbDeci),ROUND(L257/D257,NbDeci)),S256))</x:f>
       </x:c>
     </x:row>
@@ -15934,10 +15936,10 @@
         <x:f>SUM(M258:O258)</x:f>
       </x:c>
       <x:c r="Q258" s="0"/>
-      <x:c r="R258" s="71">
+      <x:c r="R258" s="75">
         <x:f>IF(B258&gt;0,IF(TauxActuariel,((B258+1)^(1/NbEchAn))-1,B258/NbEchAn),R257)</x:f>
       </x:c>
-      <x:c r="S258" s="70">
+      <x:c r="S258" s="74">
         <x:f>IF(E258&gt;0,E258,IF(D258&gt;0,IF(AND(EchFIXE,R258&gt;0),ROUND((L258-C258)*R258/(1-((1+R258)^-D258)),NbDeci),ROUND(L258/D258,NbDeci)),S257))</x:f>
       </x:c>
     </x:row>
@@ -15975,10 +15977,10 @@
         <x:f>SUM(M259:O259)</x:f>
       </x:c>
       <x:c r="Q259" s="0"/>
-      <x:c r="R259" s="71">
+      <x:c r="R259" s="75">
         <x:f>IF(B259&gt;0,IF(TauxActuariel,((B259+1)^(1/NbEchAn))-1,B259/NbEchAn),R258)</x:f>
       </x:c>
-      <x:c r="S259" s="70">
+      <x:c r="S259" s="74">
         <x:f>IF(E259&gt;0,E259,IF(D259&gt;0,IF(AND(EchFIXE,R259&gt;0),ROUND((L259-C259)*R259/(1-((1+R259)^-D259)),NbDeci),ROUND(L259/D259,NbDeci)),S258))</x:f>
       </x:c>
     </x:row>
@@ -16016,10 +16018,10 @@
         <x:f>SUM(M260:O260)</x:f>
       </x:c>
       <x:c r="Q260" s="0"/>
-      <x:c r="R260" s="71">
+      <x:c r="R260" s="75">
         <x:f>IF(B260&gt;0,IF(TauxActuariel,((B260+1)^(1/NbEchAn))-1,B260/NbEchAn),R259)</x:f>
       </x:c>
-      <x:c r="S260" s="70">
+      <x:c r="S260" s="74">
         <x:f>IF(E260&gt;0,E260,IF(D260&gt;0,IF(AND(EchFIXE,R260&gt;0),ROUND((L260-C260)*R260/(1-((1+R260)^-D260)),NbDeci),ROUND(L260/D260,NbDeci)),S259))</x:f>
       </x:c>
     </x:row>
@@ -16057,10 +16059,10 @@
         <x:f>SUM(M261:O261)</x:f>
       </x:c>
       <x:c r="Q261" s="0"/>
-      <x:c r="R261" s="71">
+      <x:c r="R261" s="75">
         <x:f>IF(B261&gt;0,IF(TauxActuariel,((B261+1)^(1/NbEchAn))-1,B261/NbEchAn),R260)</x:f>
       </x:c>
-      <x:c r="S261" s="70">
+      <x:c r="S261" s="74">
         <x:f>IF(E261&gt;0,E261,IF(D261&gt;0,IF(AND(EchFIXE,R261&gt;0),ROUND((L261-C261)*R261/(1-((1+R261)^-D261)),NbDeci),ROUND(L261/D261,NbDeci)),S260))</x:f>
       </x:c>
     </x:row>
@@ -16098,10 +16100,10 @@
         <x:f>SUM(M262:O262)</x:f>
       </x:c>
       <x:c r="Q262" s="0"/>
-      <x:c r="R262" s="71">
+      <x:c r="R262" s="75">
         <x:f>IF(B262&gt;0,IF(TauxActuariel,((B262+1)^(1/NbEchAn))-1,B262/NbEchAn),R261)</x:f>
       </x:c>
-      <x:c r="S262" s="70">
+      <x:c r="S262" s="74">
         <x:f>IF(E262&gt;0,E262,IF(D262&gt;0,IF(AND(EchFIXE,R262&gt;0),ROUND((L262-C262)*R262/(1-((1+R262)^-D262)),NbDeci),ROUND(L262/D262,NbDeci)),S261))</x:f>
       </x:c>
     </x:row>
@@ -16139,10 +16141,10 @@
         <x:f>SUM(M263:O263)</x:f>
       </x:c>
       <x:c r="Q263" s="0"/>
-      <x:c r="R263" s="71">
+      <x:c r="R263" s="75">
         <x:f>IF(B263&gt;0,IF(TauxActuariel,((B263+1)^(1/NbEchAn))-1,B263/NbEchAn),R262)</x:f>
       </x:c>
-      <x:c r="S263" s="70">
+      <x:c r="S263" s="74">
         <x:f>IF(E263&gt;0,E263,IF(D263&gt;0,IF(AND(EchFIXE,R263&gt;0),ROUND((L263-C263)*R263/(1-((1+R263)^-D263)),NbDeci),ROUND(L263/D263,NbDeci)),S262))</x:f>
       </x:c>
     </x:row>
@@ -16180,10 +16182,10 @@
         <x:f>SUM(M264:O264)</x:f>
       </x:c>
       <x:c r="Q264" s="0"/>
-      <x:c r="R264" s="71">
+      <x:c r="R264" s="75">
         <x:f>IF(B264&gt;0,IF(TauxActuariel,((B264+1)^(1/NbEchAn))-1,B264/NbEchAn),R263)</x:f>
       </x:c>
-      <x:c r="S264" s="70">
+      <x:c r="S264" s="74">
         <x:f>IF(E264&gt;0,E264,IF(D264&gt;0,IF(AND(EchFIXE,R264&gt;0),ROUND((L264-C264)*R264/(1-((1+R264)^-D264)),NbDeci),ROUND(L264/D264,NbDeci)),S263))</x:f>
       </x:c>
     </x:row>
@@ -16221,10 +16223,10 @@
         <x:f>SUM(M265:O265)</x:f>
       </x:c>
       <x:c r="Q265" s="0"/>
-      <x:c r="R265" s="71">
+      <x:c r="R265" s="75">
         <x:f>IF(B265&gt;0,IF(TauxActuariel,((B265+1)^(1/NbEchAn))-1,B265/NbEchAn),R264)</x:f>
       </x:c>
-      <x:c r="S265" s="70">
+      <x:c r="S265" s="74">
         <x:f>IF(E265&gt;0,E265,IF(D265&gt;0,IF(AND(EchFIXE,R265&gt;0),ROUND((L265-C265)*R265/(1-((1+R265)^-D265)),NbDeci),ROUND(L265/D265,NbDeci)),S264))</x:f>
       </x:c>
     </x:row>
@@ -16262,10 +16264,10 @@
         <x:f>SUM(M266:O266)</x:f>
       </x:c>
       <x:c r="Q266" s="0"/>
-      <x:c r="R266" s="71">
+      <x:c r="R266" s="75">
         <x:f>IF(B266&gt;0,IF(TauxActuariel,((B266+1)^(1/NbEchAn))-1,B266/NbEchAn),R265)</x:f>
       </x:c>
-      <x:c r="S266" s="70">
+      <x:c r="S266" s="74">
         <x:f>IF(E266&gt;0,E266,IF(D266&gt;0,IF(AND(EchFIXE,R266&gt;0),ROUND((L266-C266)*R266/(1-((1+R266)^-D266)),NbDeci),ROUND(L266/D266,NbDeci)),S265))</x:f>
       </x:c>
     </x:row>
@@ -16303,10 +16305,10 @@
         <x:f>SUM(M267:O267)</x:f>
       </x:c>
       <x:c r="Q267" s="0"/>
-      <x:c r="R267" s="71">
+      <x:c r="R267" s="75">
         <x:f>IF(B267&gt;0,IF(TauxActuariel,((B267+1)^(1/NbEchAn))-1,B267/NbEchAn),R266)</x:f>
       </x:c>
-      <x:c r="S267" s="70">
+      <x:c r="S267" s="74">
         <x:f>IF(E267&gt;0,E267,IF(D267&gt;0,IF(AND(EchFIXE,R267&gt;0),ROUND((L267-C267)*R267/(1-((1+R267)^-D267)),NbDeci),ROUND(L267/D267,NbDeci)),S266))</x:f>
       </x:c>
     </x:row>
@@ -16344,10 +16346,10 @@
         <x:f>SUM(M268:O268)</x:f>
       </x:c>
       <x:c r="Q268" s="0"/>
-      <x:c r="R268" s="71">
+      <x:c r="R268" s="75">
         <x:f>IF(B268&gt;0,IF(TauxActuariel,((B268+1)^(1/NbEchAn))-1,B268/NbEchAn),R267)</x:f>
       </x:c>
-      <x:c r="S268" s="70">
+      <x:c r="S268" s="74">
         <x:f>IF(E268&gt;0,E268,IF(D268&gt;0,IF(AND(EchFIXE,R268&gt;0),ROUND((L268-C268)*R268/(1-((1+R268)^-D268)),NbDeci),ROUND(L268/D268,NbDeci)),S267))</x:f>
       </x:c>
     </x:row>
@@ -16385,10 +16387,10 @@
         <x:f>SUM(M269:O269)</x:f>
       </x:c>
       <x:c r="Q269" s="0"/>
-      <x:c r="R269" s="71">
+      <x:c r="R269" s="75">
         <x:f>IF(B269&gt;0,IF(TauxActuariel,((B269+1)^(1/NbEchAn))-1,B269/NbEchAn),R268)</x:f>
       </x:c>
-      <x:c r="S269" s="70">
+      <x:c r="S269" s="74">
         <x:f>IF(E269&gt;0,E269,IF(D269&gt;0,IF(AND(EchFIXE,R269&gt;0),ROUND((L269-C269)*R269/(1-((1+R269)^-D269)),NbDeci),ROUND(L269/D269,NbDeci)),S268))</x:f>
       </x:c>
     </x:row>
@@ -16426,10 +16428,10 @@
         <x:f>SUM(M270:O270)</x:f>
       </x:c>
       <x:c r="Q270" s="0"/>
-      <x:c r="R270" s="71">
+      <x:c r="R270" s="75">
         <x:f>IF(B270&gt;0,IF(TauxActuariel,((B270+1)^(1/NbEchAn))-1,B270/NbEchAn),R269)</x:f>
       </x:c>
-      <x:c r="S270" s="70">
+      <x:c r="S270" s="74">
         <x:f>IF(E270&gt;0,E270,IF(D270&gt;0,IF(AND(EchFIXE,R270&gt;0),ROUND((L270-C270)*R270/(1-((1+R270)^-D270)),NbDeci),ROUND(L270/D270,NbDeci)),S269))</x:f>
       </x:c>
     </x:row>
@@ -16467,10 +16469,10 @@
         <x:f>SUM(M271:O271)</x:f>
       </x:c>
       <x:c r="Q271" s="0"/>
-      <x:c r="R271" s="71">
+      <x:c r="R271" s="75">
         <x:f>IF(B271&gt;0,IF(TauxActuariel,((B271+1)^(1/NbEchAn))-1,B271/NbEchAn),R270)</x:f>
       </x:c>
-      <x:c r="S271" s="70">
+      <x:c r="S271" s="74">
         <x:f>IF(E271&gt;0,E271,IF(D271&gt;0,IF(AND(EchFIXE,R271&gt;0),ROUND((L271-C271)*R271/(1-((1+R271)^-D271)),NbDeci),ROUND(L271/D271,NbDeci)),S270))</x:f>
       </x:c>
     </x:row>
@@ -16508,10 +16510,10 @@
         <x:f>SUM(M272:O272)</x:f>
       </x:c>
       <x:c r="Q272" s="0"/>
-      <x:c r="R272" s="71">
+      <x:c r="R272" s="75">
         <x:f>IF(B272&gt;0,IF(TauxActuariel,((B272+1)^(1/NbEchAn))-1,B272/NbEchAn),R271)</x:f>
       </x:c>
-      <x:c r="S272" s="70">
+      <x:c r="S272" s="74">
         <x:f>IF(E272&gt;0,E272,IF(D272&gt;0,IF(AND(EchFIXE,R272&gt;0),ROUND((L272-C272)*R272/(1-((1+R272)^-D272)),NbDeci),ROUND(L272/D272,NbDeci)),S271))</x:f>
       </x:c>
     </x:row>
@@ -16549,10 +16551,10 @@
         <x:f>SUM(M273:O273)</x:f>
       </x:c>
       <x:c r="Q273" s="0"/>
-      <x:c r="R273" s="71">
+      <x:c r="R273" s="75">
         <x:f>IF(B273&gt;0,IF(TauxActuariel,((B273+1)^(1/NbEchAn))-1,B273/NbEchAn),R272)</x:f>
       </x:c>
-      <x:c r="S273" s="70">
+      <x:c r="S273" s="74">
         <x:f>IF(E273&gt;0,E273,IF(D273&gt;0,IF(AND(EchFIXE,R273&gt;0),ROUND((L273-C273)*R273/(1-((1+R273)^-D273)),NbDeci),ROUND(L273/D273,NbDeci)),S272))</x:f>
       </x:c>
     </x:row>
@@ -16590,10 +16592,10 @@
         <x:f>SUM(M274:O274)</x:f>
       </x:c>
       <x:c r="Q274" s="0"/>
-      <x:c r="R274" s="71">
+      <x:c r="R274" s="75">
         <x:f>IF(B274&gt;0,IF(TauxActuariel,((B274+1)^(1/NbEchAn))-1,B274/NbEchAn),R273)</x:f>
       </x:c>
-      <x:c r="S274" s="70">
+      <x:c r="S274" s="74">
         <x:f>IF(E274&gt;0,E274,IF(D274&gt;0,IF(AND(EchFIXE,R274&gt;0),ROUND((L274-C274)*R274/(1-((1+R274)^-D274)),NbDeci),ROUND(L274/D274,NbDeci)),S273))</x:f>
       </x:c>
     </x:row>
@@ -16631,10 +16633,10 @@
         <x:f>SUM(M275:O275)</x:f>
       </x:c>
       <x:c r="Q275" s="0"/>
-      <x:c r="R275" s="71">
+      <x:c r="R275" s="75">
         <x:f>IF(B275&gt;0,IF(TauxActuariel,((B275+1)^(1/NbEchAn))-1,B275/NbEchAn),R274)</x:f>
       </x:c>
-      <x:c r="S275" s="70">
+      <x:c r="S275" s="74">
         <x:f>IF(E275&gt;0,E275,IF(D275&gt;0,IF(AND(EchFIXE,R275&gt;0),ROUND((L275-C275)*R275/(1-((1+R275)^-D275)),NbDeci),ROUND(L275/D275,NbDeci)),S274))</x:f>
       </x:c>
     </x:row>
@@ -16672,10 +16674,10 @@
         <x:f>SUM(M276:O276)</x:f>
       </x:c>
       <x:c r="Q276" s="0"/>
-      <x:c r="R276" s="71">
+      <x:c r="R276" s="75">
         <x:f>IF(B276&gt;0,IF(TauxActuariel,((B276+1)^(1/NbEchAn))-1,B276/NbEchAn),R275)</x:f>
       </x:c>
-      <x:c r="S276" s="70">
+      <x:c r="S276" s="74">
         <x:f>IF(E276&gt;0,E276,IF(D276&gt;0,IF(AND(EchFIXE,R276&gt;0),ROUND((L276-C276)*R276/(1-((1+R276)^-D276)),NbDeci),ROUND(L276/D276,NbDeci)),S275))</x:f>
       </x:c>
     </x:row>
@@ -16713,10 +16715,10 @@
         <x:f>SUM(M277:O277)</x:f>
       </x:c>
       <x:c r="Q277" s="0"/>
-      <x:c r="R277" s="71">
+      <x:c r="R277" s="75">
         <x:f>IF(B277&gt;0,IF(TauxActuariel,((B277+1)^(1/NbEchAn))-1,B277/NbEchAn),R276)</x:f>
       </x:c>
-      <x:c r="S277" s="70">
+      <x:c r="S277" s="74">
         <x:f>IF(E277&gt;0,E277,IF(D277&gt;0,IF(AND(EchFIXE,R277&gt;0),ROUND((L277-C277)*R277/(1-((1+R277)^-D277)),NbDeci),ROUND(L277/D277,NbDeci)),S276))</x:f>
       </x:c>
     </x:row>
@@ -16754,10 +16756,10 @@
         <x:f>SUM(M278:O278)</x:f>
       </x:c>
       <x:c r="Q278" s="0"/>
-      <x:c r="R278" s="71">
+      <x:c r="R278" s="75">
         <x:f>IF(B278&gt;0,IF(TauxActuariel,((B278+1)^(1/NbEchAn))-1,B278/NbEchAn),R277)</x:f>
       </x:c>
-      <x:c r="S278" s="70">
+      <x:c r="S278" s="74">
         <x:f>IF(E278&gt;0,E278,IF(D278&gt;0,IF(AND(EchFIXE,R278&gt;0),ROUND((L278-C278)*R278/(1-((1+R278)^-D278)),NbDeci),ROUND(L278/D278,NbDeci)),S277))</x:f>
       </x:c>
     </x:row>
@@ -16795,10 +16797,10 @@
         <x:f>SUM(M279:O279)</x:f>
       </x:c>
       <x:c r="Q279" s="0"/>
-      <x:c r="R279" s="71">
+      <x:c r="R279" s="75">
         <x:f>IF(B279&gt;0,IF(TauxActuariel,((B279+1)^(1/NbEchAn))-1,B279/NbEchAn),R278)</x:f>
       </x:c>
-      <x:c r="S279" s="70">
+      <x:c r="S279" s="74">
         <x:f>IF(E279&gt;0,E279,IF(D279&gt;0,IF(AND(EchFIXE,R279&gt;0),ROUND((L279-C279)*R279/(1-((1+R279)^-D279)),NbDeci),ROUND(L279/D279,NbDeci)),S278))</x:f>
       </x:c>
     </x:row>
@@ -16836,10 +16838,10 @@
         <x:f>SUM(M280:O280)</x:f>
       </x:c>
       <x:c r="Q280" s="0"/>
-      <x:c r="R280" s="71">
+      <x:c r="R280" s="75">
         <x:f>IF(B280&gt;0,IF(TauxActuariel,((B280+1)^(1/NbEchAn))-1,B280/NbEchAn),R279)</x:f>
       </x:c>
-      <x:c r="S280" s="70">
+      <x:c r="S280" s="74">
         <x:f>IF(E280&gt;0,E280,IF(D280&gt;0,IF(AND(EchFIXE,R280&gt;0),ROUND((L280-C280)*R280/(1-((1+R280)^-D280)),NbDeci),ROUND(L280/D280,NbDeci)),S279))</x:f>
       </x:c>
     </x:row>
@@ -16877,10 +16879,10 @@
         <x:f>SUM(M281:O281)</x:f>
       </x:c>
       <x:c r="Q281" s="0"/>
-      <x:c r="R281" s="71">
+      <x:c r="R281" s="75">
         <x:f>IF(B281&gt;0,IF(TauxActuariel,((B281+1)^(1/NbEchAn))-1,B281/NbEchAn),R280)</x:f>
       </x:c>
-      <x:c r="S281" s="70">
+      <x:c r="S281" s="74">
         <x:f>IF(E281&gt;0,E281,IF(D281&gt;0,IF(AND(EchFIXE,R281&gt;0),ROUND((L281-C281)*R281/(1-((1+R281)^-D281)),NbDeci),ROUND(L281/D281,NbDeci)),S280))</x:f>
       </x:c>
     </x:row>
@@ -16918,10 +16920,10 @@
         <x:f>SUM(M282:O282)</x:f>
       </x:c>
       <x:c r="Q282" s="0"/>
-      <x:c r="R282" s="71">
+      <x:c r="R282" s="75">
         <x:f>IF(B282&gt;0,IF(TauxActuariel,((B282+1)^(1/NbEchAn))-1,B282/NbEchAn),R281)</x:f>
       </x:c>
-      <x:c r="S282" s="70">
+      <x:c r="S282" s="74">
         <x:f>IF(E282&gt;0,E282,IF(D282&gt;0,IF(AND(EchFIXE,R282&gt;0),ROUND((L282-C282)*R282/(1-((1+R282)^-D282)),NbDeci),ROUND(L282/D282,NbDeci)),S281))</x:f>
       </x:c>
     </x:row>
@@ -16959,10 +16961,10 @@
         <x:f>SUM(M283:O283)</x:f>
       </x:c>
       <x:c r="Q283" s="0"/>
-      <x:c r="R283" s="71">
+      <x:c r="R283" s="75">
         <x:f>IF(B283&gt;0,IF(TauxActuariel,((B283+1)^(1/NbEchAn))-1,B283/NbEchAn),R282)</x:f>
       </x:c>
-      <x:c r="S283" s="70">
+      <x:c r="S283" s="74">
         <x:f>IF(E283&gt;0,E283,IF(D283&gt;0,IF(AND(EchFIXE,R283&gt;0),ROUND((L283-C283)*R283/(1-((1+R283)^-D283)),NbDeci),ROUND(L283/D283,NbDeci)),S282))</x:f>
       </x:c>
     </x:row>
@@ -17000,10 +17002,10 @@
         <x:f>SUM(M284:O284)</x:f>
       </x:c>
       <x:c r="Q284" s="0"/>
-      <x:c r="R284" s="71">
+      <x:c r="R284" s="75">
         <x:f>IF(B284&gt;0,IF(TauxActuariel,((B284+1)^(1/NbEchAn))-1,B284/NbEchAn),R283)</x:f>
       </x:c>
-      <x:c r="S284" s="70">
+      <x:c r="S284" s="74">
         <x:f>IF(E284&gt;0,E284,IF(D284&gt;0,IF(AND(EchFIXE,R284&gt;0),ROUND((L284-C284)*R284/(1-((1+R284)^-D284)),NbDeci),ROUND(L284/D284,NbDeci)),S283))</x:f>
       </x:c>
     </x:row>
@@ -17041,10 +17043,10 @@
         <x:f>SUM(M285:O285)</x:f>
       </x:c>
       <x:c r="Q285" s="0"/>
-      <x:c r="R285" s="71">
+      <x:c r="R285" s="75">
         <x:f>IF(B285&gt;0,IF(TauxActuariel,((B285+1)^(1/NbEchAn))-1,B285/NbEchAn),R284)</x:f>
       </x:c>
-      <x:c r="S285" s="70">
+      <x:c r="S285" s="74">
         <x:f>IF(E285&gt;0,E285,IF(D285&gt;0,IF(AND(EchFIXE,R285&gt;0),ROUND((L285-C285)*R285/(1-((1+R285)^-D285)),NbDeci),ROUND(L285/D285,NbDeci)),S284))</x:f>
       </x:c>
     </x:row>
@@ -17082,10 +17084,10 @@
         <x:f>SUM(M286:O286)</x:f>
       </x:c>
       <x:c r="Q286" s="0"/>
-      <x:c r="R286" s="71">
+      <x:c r="R286" s="75">
         <x:f>IF(B286&gt;0,IF(TauxActuariel,((B286+1)^(1/NbEchAn))-1,B286/NbEchAn),R285)</x:f>
       </x:c>
-      <x:c r="S286" s="70">
+      <x:c r="S286" s="74">
         <x:f>IF(E286&gt;0,E286,IF(D286&gt;0,IF(AND(EchFIXE,R286&gt;0),ROUND((L286-C286)*R286/(1-((1+R286)^-D286)),NbDeci),ROUND(L286/D286,NbDeci)),S285))</x:f>
       </x:c>
     </x:row>
@@ -17123,10 +17125,10 @@
         <x:f>SUM(M287:O287)</x:f>
       </x:c>
       <x:c r="Q287" s="0"/>
-      <x:c r="R287" s="71">
+      <x:c r="R287" s="75">
         <x:f>IF(B287&gt;0,IF(TauxActuariel,((B287+1)^(1/NbEchAn))-1,B287/NbEchAn),R286)</x:f>
       </x:c>
-      <x:c r="S287" s="70">
+      <x:c r="S287" s="74">
         <x:f>IF(E287&gt;0,E287,IF(D287&gt;0,IF(AND(EchFIXE,R287&gt;0),ROUND((L287-C287)*R287/(1-((1+R287)^-D287)),NbDeci),ROUND(L287/D287,NbDeci)),S286))</x:f>
       </x:c>
     </x:row>
@@ -17164,10 +17166,10 @@
         <x:f>SUM(M288:O288)</x:f>
       </x:c>
       <x:c r="Q288" s="0"/>
-      <x:c r="R288" s="71">
+      <x:c r="R288" s="75">
         <x:f>IF(B288&gt;0,IF(TauxActuariel,((B288+1)^(1/NbEchAn))-1,B288/NbEchAn),R287)</x:f>
       </x:c>
-      <x:c r="S288" s="70">
+      <x:c r="S288" s="74">
         <x:f>IF(E288&gt;0,E288,IF(D288&gt;0,IF(AND(EchFIXE,R288&gt;0),ROUND((L288-C288)*R288/(1-((1+R288)^-D288)),NbDeci),ROUND(L288/D288,NbDeci)),S287))</x:f>
       </x:c>
     </x:row>
@@ -17205,10 +17207,10 @@
         <x:f>SUM(M289:O289)</x:f>
       </x:c>
       <x:c r="Q289" s="0"/>
-      <x:c r="R289" s="71">
+      <x:c r="R289" s="75">
         <x:f>IF(B289&gt;0,IF(TauxActuariel,((B289+1)^(1/NbEchAn))-1,B289/NbEchAn),R288)</x:f>
       </x:c>
-      <x:c r="S289" s="70">
+      <x:c r="S289" s="74">
         <x:f>IF(E289&gt;0,E289,IF(D289&gt;0,IF(AND(EchFIXE,R289&gt;0),ROUND((L289-C289)*R289/(1-((1+R289)^-D289)),NbDeci),ROUND(L289/D289,NbDeci)),S288))</x:f>
       </x:c>
     </x:row>
@@ -17246,10 +17248,10 @@
         <x:f>SUM(M290:O290)</x:f>
       </x:c>
       <x:c r="Q290" s="0"/>
-      <x:c r="R290" s="71">
+      <x:c r="R290" s="75">
         <x:f>IF(B290&gt;0,IF(TauxActuariel,((B290+1)^(1/NbEchAn))-1,B290/NbEchAn),R289)</x:f>
       </x:c>
-      <x:c r="S290" s="70">
+      <x:c r="S290" s="74">
         <x:f>IF(E290&gt;0,E290,IF(D290&gt;0,IF(AND(EchFIXE,R290&gt;0),ROUND((L290-C290)*R290/(1-((1+R290)^-D290)),NbDeci),ROUND(L290/D290,NbDeci)),S289))</x:f>
       </x:c>
     </x:row>
@@ -17287,10 +17289,10 @@
         <x:f>SUM(M291:O291)</x:f>
       </x:c>
       <x:c r="Q291" s="0"/>
-      <x:c r="R291" s="71">
+      <x:c r="R291" s="75">
         <x:f>IF(B291&gt;0,IF(TauxActuariel,((B291+1)^(1/NbEchAn))-1,B291/NbEchAn),R290)</x:f>
       </x:c>
-      <x:c r="S291" s="70">
+      <x:c r="S291" s="74">
         <x:f>IF(E291&gt;0,E291,IF(D291&gt;0,IF(AND(EchFIXE,R291&gt;0),ROUND((L291-C291)*R291/(1-((1+R291)^-D291)),NbDeci),ROUND(L291/D291,NbDeci)),S290))</x:f>
       </x:c>
     </x:row>
@@ -17328,10 +17330,10 @@
         <x:f>SUM(M292:O292)</x:f>
       </x:c>
       <x:c r="Q292" s="0"/>
-      <x:c r="R292" s="71">
+      <x:c r="R292" s="75">
         <x:f>IF(B292&gt;0,IF(TauxActuariel,((B292+1)^(1/NbEchAn))-1,B292/NbEchAn),R291)</x:f>
       </x:c>
-      <x:c r="S292" s="70">
+      <x:c r="S292" s="74">
         <x:f>IF(E292&gt;0,E292,IF(D292&gt;0,IF(AND(EchFIXE,R292&gt;0),ROUND((L292-C292)*R292/(1-((1+R292)^-D292)),NbDeci),ROUND(L292/D292,NbDeci)),S291))</x:f>
       </x:c>
     </x:row>
@@ -17369,10 +17371,10 @@
         <x:f>SUM(M293:O293)</x:f>
       </x:c>
       <x:c r="Q293" s="0"/>
-      <x:c r="R293" s="71">
+      <x:c r="R293" s="75">
         <x:f>IF(B293&gt;0,IF(TauxActuariel,((B293+1)^(1/NbEchAn))-1,B293/NbEchAn),R292)</x:f>
       </x:c>
-      <x:c r="S293" s="70">
+      <x:c r="S293" s="74">
         <x:f>IF(E293&gt;0,E293,IF(D293&gt;0,IF(AND(EchFIXE,R293&gt;0),ROUND((L293-C293)*R293/(1-((1+R293)^-D293)),NbDeci),ROUND(L293/D293,NbDeci)),S292))</x:f>
       </x:c>
     </x:row>
@@ -17410,10 +17412,10 @@
         <x:f>SUM(M294:O294)</x:f>
       </x:c>
       <x:c r="Q294" s="0"/>
-      <x:c r="R294" s="71">
+      <x:c r="R294" s="75">
         <x:f>IF(B294&gt;0,IF(TauxActuariel,((B294+1)^(1/NbEchAn))-1,B294/NbEchAn),R293)</x:f>
       </x:c>
-      <x:c r="S294" s="70">
+      <x:c r="S294" s="74">
         <x:f>IF(E294&gt;0,E294,IF(D294&gt;0,IF(AND(EchFIXE,R294&gt;0),ROUND((L294-C294)*R294/(1-((1+R294)^-D294)),NbDeci),ROUND(L294/D294,NbDeci)),S293))</x:f>
       </x:c>
     </x:row>
@@ -17451,10 +17453,10 @@
         <x:f>SUM(M295:O295)</x:f>
       </x:c>
       <x:c r="Q295" s="0"/>
-      <x:c r="R295" s="71">
+      <x:c r="R295" s="75">
         <x:f>IF(B295&gt;0,IF(TauxActuariel,((B295+1)^(1/NbEchAn))-1,B295/NbEchAn),R294)</x:f>
       </x:c>
-      <x:c r="S295" s="70">
+      <x:c r="S295" s="74">
         <x:f>IF(E295&gt;0,E295,IF(D295&gt;0,IF(AND(EchFIXE,R295&gt;0),ROUND((L295-C295)*R295/(1-((1+R295)^-D295)),NbDeci),ROUND(L295/D295,NbDeci)),S294))</x:f>
       </x:c>
     </x:row>
@@ -17492,10 +17494,10 @@
         <x:f>SUM(M296:O296)</x:f>
       </x:c>
       <x:c r="Q296" s="0"/>
-      <x:c r="R296" s="71">
+      <x:c r="R296" s="75">
         <x:f>IF(B296&gt;0,IF(TauxActuariel,((B296+1)^(1/NbEchAn))-1,B296/NbEchAn),R295)</x:f>
       </x:c>
-      <x:c r="S296" s="70">
+      <x:c r="S296" s="74">
         <x:f>IF(E296&gt;0,E296,IF(D296&gt;0,IF(AND(EchFIXE,R296&gt;0),ROUND((L296-C296)*R296/(1-((1+R296)^-D296)),NbDeci),ROUND(L296/D296,NbDeci)),S295))</x:f>
       </x:c>
     </x:row>
@@ -17533,10 +17535,10 @@
         <x:f>SUM(M297:O297)</x:f>
       </x:c>
       <x:c r="Q297" s="0"/>
-      <x:c r="R297" s="71">
+      <x:c r="R297" s="75">
         <x:f>IF(B297&gt;0,IF(TauxActuariel,((B297+1)^(1/NbEchAn))-1,B297/NbEchAn),R296)</x:f>
       </x:c>
-      <x:c r="S297" s="70">
+      <x:c r="S297" s="74">
         <x:f>IF(E297&gt;0,E297,IF(D297&gt;0,IF(AND(EchFIXE,R297&gt;0),ROUND((L297-C297)*R297/(1-((1+R297)^-D297)),NbDeci),ROUND(L297/D297,NbDeci)),S296))</x:f>
       </x:c>
     </x:row>
@@ -17574,10 +17576,10 @@
         <x:f>SUM(M298:O298)</x:f>
       </x:c>
       <x:c r="Q298" s="0"/>
-      <x:c r="R298" s="71">
+      <x:c r="R298" s="75">
         <x:f>IF(B298&gt;0,IF(TauxActuariel,((B298+1)^(1/NbEchAn))-1,B298/NbEchAn),R297)</x:f>
       </x:c>
-      <x:c r="S298" s="70">
+      <x:c r="S298" s="74">
         <x:f>IF(E298&gt;0,E298,IF(D298&gt;0,IF(AND(EchFIXE,R298&gt;0),ROUND((L298-C298)*R298/(1-((1+R298)^-D298)),NbDeci),ROUND(L298/D298,NbDeci)),S297))</x:f>
       </x:c>
     </x:row>
@@ -17615,10 +17617,10 @@
         <x:f>SUM(M299:O299)</x:f>
       </x:c>
       <x:c r="Q299" s="0"/>
-      <x:c r="R299" s="71">
+      <x:c r="R299" s="75">
         <x:f>IF(B299&gt;0,IF(TauxActuariel,((B299+1)^(1/NbEchAn))-1,B299/NbEchAn),R298)</x:f>
       </x:c>
-      <x:c r="S299" s="70">
+      <x:c r="S299" s="74">
         <x:f>IF(E299&gt;0,E299,IF(D299&gt;0,IF(AND(EchFIXE,R299&gt;0),ROUND((L299-C299)*R299/(1-((1+R299)^-D299)),NbDeci),ROUND(L299/D299,NbDeci)),S298))</x:f>
       </x:c>
     </x:row>
@@ -17656,10 +17658,10 @@
         <x:f>SUM(M300:O300)</x:f>
       </x:c>
       <x:c r="Q300" s="0"/>
-      <x:c r="R300" s="71">
+      <x:c r="R300" s="75">
         <x:f>IF(B300&gt;0,IF(TauxActuariel,((B300+1)^(1/NbEchAn))-1,B300/NbEchAn),R299)</x:f>
       </x:c>
-      <x:c r="S300" s="70">
+      <x:c r="S300" s="74">
         <x:f>IF(E300&gt;0,E300,IF(D300&gt;0,IF(AND(EchFIXE,R300&gt;0),ROUND((L300-C300)*R300/(1-((1+R300)^-D300)),NbDeci),ROUND(L300/D300,NbDeci)),S299))</x:f>
       </x:c>
     </x:row>
@@ -17697,10 +17699,10 @@
         <x:f>SUM(M301:O301)</x:f>
       </x:c>
       <x:c r="Q301" s="0"/>
-      <x:c r="R301" s="71">
+      <x:c r="R301" s="75">
         <x:f>IF(B301&gt;0,IF(TauxActuariel,((B301+1)^(1/NbEchAn))-1,B301/NbEchAn),R300)</x:f>
       </x:c>
-      <x:c r="S301" s="70">
+      <x:c r="S301" s="74">
         <x:f>IF(E301&gt;0,E301,IF(D301&gt;0,IF(AND(EchFIXE,R301&gt;0),ROUND((L301-C301)*R301/(1-((1+R301)^-D301)),NbDeci),ROUND(L301/D301,NbDeci)),S300))</x:f>
       </x:c>
     </x:row>
@@ -17738,10 +17740,10 @@
         <x:f>SUM(M302:O302)</x:f>
       </x:c>
       <x:c r="Q302" s="0"/>
-      <x:c r="R302" s="71">
+      <x:c r="R302" s="75">
         <x:f>IF(B302&gt;0,IF(TauxActuariel,((B302+1)^(1/NbEchAn))-1,B302/NbEchAn),R301)</x:f>
       </x:c>
-      <x:c r="S302" s="70">
+      <x:c r="S302" s="74">
         <x:f>IF(E302&gt;0,E302,IF(D302&gt;0,IF(AND(EchFIXE,R302&gt;0),ROUND((L302-C302)*R302/(1-((1+R302)^-D302)),NbDeci),ROUND(L302/D302,NbDeci)),S301))</x:f>
       </x:c>
     </x:row>
@@ -17779,10 +17781,10 @@
         <x:f>SUM(M303:O303)</x:f>
       </x:c>
       <x:c r="Q303" s="0"/>
-      <x:c r="R303" s="71">
+      <x:c r="R303" s="75">
         <x:f>IF(B303&gt;0,IF(TauxActuariel,((B303+1)^(1/NbEchAn))-1,B303/NbEchAn),R302)</x:f>
       </x:c>
-      <x:c r="S303" s="70">
+      <x:c r="S303" s="74">
         <x:f>IF(E303&gt;0,E303,IF(D303&gt;0,IF(AND(EchFIXE,R303&gt;0),ROUND((L303-C303)*R303/(1-((1+R303)^-D303)),NbDeci),ROUND(L303/D303,NbDeci)),S302))</x:f>
       </x:c>
     </x:row>
@@ -17820,10 +17822,10 @@
         <x:f>SUM(M304:O304)</x:f>
       </x:c>
       <x:c r="Q304" s="0"/>
-      <x:c r="R304" s="71">
+      <x:c r="R304" s="75">
         <x:f>IF(B304&gt;0,IF(TauxActuariel,((B304+1)^(1/NbEchAn))-1,B304/NbEchAn),R303)</x:f>
       </x:c>
-      <x:c r="S304" s="70">
+      <x:c r="S304" s="74">
         <x:f>IF(E304&gt;0,E304,IF(D304&gt;0,IF(AND(EchFIXE,R304&gt;0),ROUND((L304-C304)*R304/(1-((1+R304)^-D304)),NbDeci),ROUND(L304/D304,NbDeci)),S303))</x:f>
       </x:c>
     </x:row>
@@ -17861,10 +17863,10 @@
         <x:f>SUM(M305:O305)</x:f>
       </x:c>
       <x:c r="Q305" s="0"/>
-      <x:c r="R305" s="71">
+      <x:c r="R305" s="75">
         <x:f>IF(B305&gt;0,IF(TauxActuariel,((B305+1)^(1/NbEchAn))-1,B305/NbEchAn),R304)</x:f>
       </x:c>
-      <x:c r="S305" s="70">
+      <x:c r="S305" s="74">
         <x:f>IF(E305&gt;0,E305,IF(D305&gt;0,IF(AND(EchFIXE,R305&gt;0),ROUND((L305-C305)*R305/(1-((1+R305)^-D305)),NbDeci),ROUND(L305/D305,NbDeci)),S304))</x:f>
       </x:c>
     </x:row>
@@ -17902,10 +17904,10 @@
         <x:f>SUM(M306:O306)</x:f>
       </x:c>
       <x:c r="Q306" s="0"/>
-      <x:c r="R306" s="71">
+      <x:c r="R306" s="75">
         <x:f>IF(B306&gt;0,IF(TauxActuariel,((B306+1)^(1/NbEchAn))-1,B306/NbEchAn),R305)</x:f>
       </x:c>
-      <x:c r="S306" s="70">
+      <x:c r="S306" s="74">
         <x:f>IF(E306&gt;0,E306,IF(D306&gt;0,IF(AND(EchFIXE,R306&gt;0),ROUND((L306-C306)*R306/(1-((1+R306)^-D306)),NbDeci),ROUND(L306/D306,NbDeci)),S305))</x:f>
       </x:c>
     </x:row>
@@ -17943,10 +17945,10 @@
         <x:f>SUM(M307:O307)</x:f>
       </x:c>
       <x:c r="Q307" s="0"/>
-      <x:c r="R307" s="71">
+      <x:c r="R307" s="75">
         <x:f>IF(B307&gt;0,IF(TauxActuariel,((B307+1)^(1/NbEchAn))-1,B307/NbEchAn),R306)</x:f>
       </x:c>
-      <x:c r="S307" s="70">
+      <x:c r="S307" s="74">
         <x:f>IF(E307&gt;0,E307,IF(D307&gt;0,IF(AND(EchFIXE,R307&gt;0),ROUND((L307-C307)*R307/(1-((1+R307)^-D307)),NbDeci),ROUND(L307/D307,NbDeci)),S306))</x:f>
       </x:c>
     </x:row>
@@ -17984,10 +17986,10 @@
         <x:f>SUM(M308:O308)</x:f>
       </x:c>
       <x:c r="Q308" s="0"/>
-      <x:c r="R308" s="71">
+      <x:c r="R308" s="75">
         <x:f>IF(B308&gt;0,IF(TauxActuariel,((B308+1)^(1/NbEchAn))-1,B308/NbEchAn),R307)</x:f>
       </x:c>
-      <x:c r="S308" s="70">
+      <x:c r="S308" s="74">
         <x:f>IF(E308&gt;0,E308,IF(D308&gt;0,IF(AND(EchFIXE,R308&gt;0),ROUND((L308-C308)*R308/(1-((1+R308)^-D308)),NbDeci),ROUND(L308/D308,NbDeci)),S307))</x:f>
       </x:c>
     </x:row>
@@ -18025,10 +18027,10 @@
         <x:f>SUM(M309:O309)</x:f>
       </x:c>
       <x:c r="Q309" s="0"/>
-      <x:c r="R309" s="71">
+      <x:c r="R309" s="75">
         <x:f>IF(B309&gt;0,IF(TauxActuariel,((B309+1)^(1/NbEchAn))-1,B309/NbEchAn),R308)</x:f>
       </x:c>
-      <x:c r="S309" s="70">
+      <x:c r="S309" s="74">
         <x:f>IF(E309&gt;0,E309,IF(D309&gt;0,IF(AND(EchFIXE,R309&gt;0),ROUND((L309-C309)*R309/(1-((1+R309)^-D309)),NbDeci),ROUND(L309/D309,NbDeci)),S308))</x:f>
       </x:c>
     </x:row>
@@ -18066,10 +18068,10 @@
         <x:f>SUM(M310:O310)</x:f>
       </x:c>
       <x:c r="Q310" s="0"/>
-      <x:c r="R310" s="71">
+      <x:c r="R310" s="75">
         <x:f>IF(B310&gt;0,IF(TauxActuariel,((B310+1)^(1/NbEchAn))-1,B310/NbEchAn),R309)</x:f>
       </x:c>
-      <x:c r="S310" s="70">
+      <x:c r="S310" s="74">
         <x:f>IF(E310&gt;0,E310,IF(D310&gt;0,IF(AND(EchFIXE,R310&gt;0),ROUND((L310-C310)*R310/(1-((1+R310)^-D310)),NbDeci),ROUND(L310/D310,NbDeci)),S309))</x:f>
       </x:c>
     </x:row>
@@ -18107,10 +18109,10 @@
         <x:f>SUM(M311:O311)</x:f>
       </x:c>
       <x:c r="Q311" s="0"/>
-      <x:c r="R311" s="71">
+      <x:c r="R311" s="75">
         <x:f>IF(B311&gt;0,IF(TauxActuariel,((B311+1)^(1/NbEchAn))-1,B311/NbEchAn),R310)</x:f>
       </x:c>
-      <x:c r="S311" s="70">
+      <x:c r="S311" s="74">
         <x:f>IF(E311&gt;0,E311,IF(D311&gt;0,IF(AND(EchFIXE,R311&gt;0),ROUND((L311-C311)*R311/(1-((1+R311)^-D311)),NbDeci),ROUND(L311/D311,NbDeci)),S310))</x:f>
       </x:c>
     </x:row>
@@ -18148,10 +18150,10 @@
         <x:f>SUM(M312:O312)</x:f>
       </x:c>
       <x:c r="Q312" s="0"/>
-      <x:c r="R312" s="71">
+      <x:c r="R312" s="75">
         <x:f>IF(B312&gt;0,IF(TauxActuariel,((B312+1)^(1/NbEchAn))-1,B312/NbEchAn),R311)</x:f>
       </x:c>
-      <x:c r="S312" s="70">
+      <x:c r="S312" s="74">
         <x:f>IF(E312&gt;0,E312,IF(D312&gt;0,IF(AND(EchFIXE,R312&gt;0),ROUND((L312-C312)*R312/(1-((1+R312)^-D312)),NbDeci),ROUND(L312/D312,NbDeci)),S311))</x:f>
       </x:c>
     </x:row>
@@ -18189,10 +18191,10 @@
         <x:f>SUM(M313:O313)</x:f>
       </x:c>
       <x:c r="Q313" s="0"/>
-      <x:c r="R313" s="71">
+      <x:c r="R313" s="75">
         <x:f>IF(B313&gt;0,IF(TauxActuariel,((B313+1)^(1/NbEchAn))-1,B313/NbEchAn),R312)</x:f>
       </x:c>
-      <x:c r="S313" s="70">
+      <x:c r="S313" s="74">
         <x:f>IF(E313&gt;0,E313,IF(D313&gt;0,IF(AND(EchFIXE,R313&gt;0),ROUND((L313-C313)*R313/(1-((1+R313)^-D313)),NbDeci),ROUND(L313/D313,NbDeci)),S312))</x:f>
       </x:c>
     </x:row>
@@ -18230,10 +18232,10 @@
         <x:f>SUM(M314:O314)</x:f>
       </x:c>
       <x:c r="Q314" s="0"/>
-      <x:c r="R314" s="71">
+      <x:c r="R314" s="75">
         <x:f>IF(B314&gt;0,IF(TauxActuariel,((B314+1)^(1/NbEchAn))-1,B314/NbEchAn),R313)</x:f>
       </x:c>
-      <x:c r="S314" s="70">
+      <x:c r="S314" s="74">
         <x:f>IF(E314&gt;0,E314,IF(D314&gt;0,IF(AND(EchFIXE,R314&gt;0),ROUND((L314-C314)*R314/(1-((1+R314)^-D314)),NbDeci),ROUND(L314/D314,NbDeci)),S313))</x:f>
       </x:c>
     </x:row>
@@ -18271,10 +18273,10 @@
         <x:f>SUM(M315:O315)</x:f>
       </x:c>
       <x:c r="Q315" s="0"/>
-      <x:c r="R315" s="71">
+      <x:c r="R315" s="75">
         <x:f>IF(B315&gt;0,IF(TauxActuariel,((B315+1)^(1/NbEchAn))-1,B315/NbEchAn),R314)</x:f>
       </x:c>
-      <x:c r="S315" s="70">
+      <x:c r="S315" s="74">
         <x:f>IF(E315&gt;0,E315,IF(D315&gt;0,IF(AND(EchFIXE,R315&gt;0),ROUND((L315-C315)*R315/(1-((1+R315)^-D315)),NbDeci),ROUND(L315/D315,NbDeci)),S314))</x:f>
       </x:c>
     </x:row>
@@ -18312,10 +18314,10 @@
         <x:f>SUM(M316:O316)</x:f>
       </x:c>
       <x:c r="Q316" s="0"/>
-      <x:c r="R316" s="71">
+      <x:c r="R316" s="75">
         <x:f>IF(B316&gt;0,IF(TauxActuariel,((B316+1)^(1/NbEchAn))-1,B316/NbEchAn),R315)</x:f>
       </x:c>
-      <x:c r="S316" s="70">
+      <x:c r="S316" s="74">
         <x:f>IF(E316&gt;0,E316,IF(D316&gt;0,IF(AND(EchFIXE,R316&gt;0),ROUND((L316-C316)*R316/(1-((1+R316)^-D316)),NbDeci),ROUND(L316/D316,NbDeci)),S315))</x:f>
       </x:c>
     </x:row>
@@ -18353,10 +18355,10 @@
         <x:f>SUM(M317:O317)</x:f>
       </x:c>
       <x:c r="Q317" s="0"/>
-      <x:c r="R317" s="71">
+      <x:c r="R317" s="75">
         <x:f>IF(B317&gt;0,IF(TauxActuariel,((B317+1)^(1/NbEchAn))-1,B317/NbEchAn),R316)</x:f>
       </x:c>
-      <x:c r="S317" s="70">
+      <x:c r="S317" s="74">
         <x:f>IF(E317&gt;0,E317,IF(D317&gt;0,IF(AND(EchFIXE,R317&gt;0),ROUND((L317-C317)*R317/(1-((1+R317)^-D317)),NbDeci),ROUND(L317/D317,NbDeci)),S316))</x:f>
       </x:c>
     </x:row>
@@ -18394,10 +18396,10 @@
         <x:f>SUM(M318:O318)</x:f>
       </x:c>
       <x:c r="Q318" s="0"/>
-      <x:c r="R318" s="71">
+      <x:c r="R318" s="75">
         <x:f>IF(B318&gt;0,IF(TauxActuariel,((B318+1)^(1/NbEchAn))-1,B318/NbEchAn),R317)</x:f>
       </x:c>
-      <x:c r="S318" s="70">
+      <x:c r="S318" s="74">
         <x:f>IF(E318&gt;0,E318,IF(D318&gt;0,IF(AND(EchFIXE,R318&gt;0),ROUND((L318-C318)*R318/(1-((1+R318)^-D318)),NbDeci),ROUND(L318/D318,NbDeci)),S317))</x:f>
       </x:c>
     </x:row>
@@ -18435,10 +18437,10 @@
         <x:f>SUM(M319:O319)</x:f>
       </x:c>
       <x:c r="Q319" s="0"/>
-      <x:c r="R319" s="71">
+      <x:c r="R319" s="75">
         <x:f>IF(B319&gt;0,IF(TauxActuariel,((B319+1)^(1/NbEchAn))-1,B319/NbEchAn),R318)</x:f>
       </x:c>
-      <x:c r="S319" s="70">
+      <x:c r="S319" s="74">
         <x:f>IF(E319&gt;0,E319,IF(D319&gt;0,IF(AND(EchFIXE,R319&gt;0),ROUND((L319-C319)*R319/(1-((1+R319)^-D319)),NbDeci),ROUND(L319/D319,NbDeci)),S318))</x:f>
       </x:c>
     </x:row>
@@ -18476,10 +18478,10 @@
         <x:f>SUM(M320:O320)</x:f>
       </x:c>
       <x:c r="Q320" s="0"/>
-      <x:c r="R320" s="71">
+      <x:c r="R320" s="75">
         <x:f>IF(B320&gt;0,IF(TauxActuariel,((B320+1)^(1/NbEchAn))-1,B320/NbEchAn),R319)</x:f>
       </x:c>
-      <x:c r="S320" s="70">
+      <x:c r="S320" s="74">
         <x:f>IF(E320&gt;0,E320,IF(D320&gt;0,IF(AND(EchFIXE,R320&gt;0),ROUND((L320-C320)*R320/(1-((1+R320)^-D320)),NbDeci),ROUND(L320/D320,NbDeci)),S319))</x:f>
       </x:c>
     </x:row>
@@ -18517,10 +18519,10 @@
         <x:f>SUM(M321:O321)</x:f>
       </x:c>
       <x:c r="Q321" s="0"/>
-      <x:c r="R321" s="71">
+      <x:c r="R321" s="75">
         <x:f>IF(B321&gt;0,IF(TauxActuariel,((B321+1)^(1/NbEchAn))-1,B321/NbEchAn),R320)</x:f>
       </x:c>
-      <x:c r="S321" s="70">
+      <x:c r="S321" s="74">
         <x:f>IF(E321&gt;0,E321,IF(D321&gt;0,IF(AND(EchFIXE,R321&gt;0),ROUND((L321-C321)*R321/(1-((1+R321)^-D321)),NbDeci),ROUND(L321/D321,NbDeci)),S320))</x:f>
       </x:c>
     </x:row>
@@ -18558,10 +18560,10 @@
         <x:f>SUM(M322:O322)</x:f>
       </x:c>
       <x:c r="Q322" s="0"/>
-      <x:c r="R322" s="71">
+      <x:c r="R322" s="75">
         <x:f>IF(B322&gt;0,IF(TauxActuariel,((B322+1)^(1/NbEchAn))-1,B322/NbEchAn),R321)</x:f>
       </x:c>
-      <x:c r="S322" s="70">
+      <x:c r="S322" s="74">
         <x:f>IF(E322&gt;0,E322,IF(D322&gt;0,IF(AND(EchFIXE,R322&gt;0),ROUND((L322-C322)*R322/(1-((1+R322)^-D322)),NbDeci),ROUND(L322/D322,NbDeci)),S321))</x:f>
       </x:c>
     </x:row>
@@ -18599,10 +18601,10 @@
         <x:f>SUM(M323:O323)</x:f>
       </x:c>
       <x:c r="Q323" s="0"/>
-      <x:c r="R323" s="71">
+      <x:c r="R323" s="75">
         <x:f>IF(B323&gt;0,IF(TauxActuariel,((B323+1)^(1/NbEchAn))-1,B323/NbEchAn),R322)</x:f>
       </x:c>
-      <x:c r="S323" s="70">
+      <x:c r="S323" s="74">
         <x:f>IF(E323&gt;0,E323,IF(D323&gt;0,IF(AND(EchFIXE,R323&gt;0),ROUND((L323-C323)*R323/(1-((1+R323)^-D323)),NbDeci),ROUND(L323/D323,NbDeci)),S322))</x:f>
       </x:c>
     </x:row>
@@ -18640,10 +18642,10 @@
         <x:f>SUM(M324:O324)</x:f>
       </x:c>
       <x:c r="Q324" s="0"/>
-      <x:c r="R324" s="71">
+      <x:c r="R324" s="75">
         <x:f>IF(B324&gt;0,IF(TauxActuariel,((B324+1)^(1/NbEchAn))-1,B324/NbEchAn),R323)</x:f>
       </x:c>
-      <x:c r="S324" s="70">
+      <x:c r="S324" s="74">
         <x:f>IF(E324&gt;0,E324,IF(D324&gt;0,IF(AND(EchFIXE,R324&gt;0),ROUND((L324-C324)*R324/(1-((1+R324)^-D324)),NbDeci),ROUND(L324/D324,NbDeci)),S323))</x:f>
       </x:c>
     </x:row>
@@ -18681,10 +18683,10 @@
         <x:f>SUM(M325:O325)</x:f>
       </x:c>
       <x:c r="Q325" s="0"/>
-      <x:c r="R325" s="71">
+      <x:c r="R325" s="75">
         <x:f>IF(B325&gt;0,IF(TauxActuariel,((B325+1)^(1/NbEchAn))-1,B325/NbEchAn),R324)</x:f>
       </x:c>
-      <x:c r="S325" s="70">
+      <x:c r="S325" s="74">
         <x:f>IF(E325&gt;0,E325,IF(D325&gt;0,IF(AND(EchFIXE,R325&gt;0),ROUND((L325-C325)*R325/(1-((1+R325)^-D325)),NbDeci),ROUND(L325/D325,NbDeci)),S324))</x:f>
       </x:c>
     </x:row>
@@ -18722,10 +18724,10 @@
         <x:f>SUM(M326:O326)</x:f>
       </x:c>
       <x:c r="Q326" s="0"/>
-      <x:c r="R326" s="71">
+      <x:c r="R326" s="75">
         <x:f>IF(B326&gt;0,IF(TauxActuariel,((B326+1)^(1/NbEchAn))-1,B326/NbEchAn),R325)</x:f>
       </x:c>
-      <x:c r="S326" s="70">
+      <x:c r="S326" s="74">
         <x:f>IF(E326&gt;0,E326,IF(D326&gt;0,IF(AND(EchFIXE,R326&gt;0),ROUND((L326-C326)*R326/(1-((1+R326)^-D326)),NbDeci),ROUND(L326/D326,NbDeci)),S325))</x:f>
       </x:c>
     </x:row>
@@ -18763,10 +18765,10 @@
         <x:f>SUM(M327:O327)</x:f>
       </x:c>
       <x:c r="Q327" s="0"/>
-      <x:c r="R327" s="71">
+      <x:c r="R327" s="75">
         <x:f>IF(B327&gt;0,IF(TauxActuariel,((B327+1)^(1/NbEchAn))-1,B327/NbEchAn),R326)</x:f>
       </x:c>
-      <x:c r="S327" s="70">
+      <x:c r="S327" s="74">
         <x:f>IF(E327&gt;0,E327,IF(D327&gt;0,IF(AND(EchFIXE,R327&gt;0),ROUND((L327-C327)*R327/(1-((1+R327)^-D327)),NbDeci),ROUND(L327/D327,NbDeci)),S326))</x:f>
       </x:c>
     </x:row>
@@ -18804,10 +18806,10 @@
         <x:f>SUM(M328:O328)</x:f>
       </x:c>
       <x:c r="Q328" s="0"/>
-      <x:c r="R328" s="71">
+      <x:c r="R328" s="75">
         <x:f>IF(B328&gt;0,IF(TauxActuariel,((B328+1)^(1/NbEchAn))-1,B328/NbEchAn),R327)</x:f>
       </x:c>
-      <x:c r="S328" s="70">
+      <x:c r="S328" s="74">
         <x:f>IF(E328&gt;0,E328,IF(D328&gt;0,IF(AND(EchFIXE,R328&gt;0),ROUND((L328-C328)*R328/(1-((1+R328)^-D328)),NbDeci),ROUND(L328/D328,NbDeci)),S327))</x:f>
       </x:c>
     </x:row>
@@ -18845,10 +18847,10 @@
         <x:f>SUM(M329:O329)</x:f>
       </x:c>
       <x:c r="Q329" s="0"/>
-      <x:c r="R329" s="71">
+      <x:c r="R329" s="75">
         <x:f>IF(B329&gt;0,IF(TauxActuariel,((B329+1)^(1/NbEchAn))-1,B329/NbEchAn),R328)</x:f>
       </x:c>
-      <x:c r="S329" s="70">
+      <x:c r="S329" s="74">
         <x:f>IF(E329&gt;0,E329,IF(D329&gt;0,IF(AND(EchFIXE,R329&gt;0),ROUND((L329-C329)*R329/(1-((1+R329)^-D329)),NbDeci),ROUND(L329/D329,NbDeci)),S328))</x:f>
       </x:c>
     </x:row>
@@ -18886,10 +18888,10 @@
         <x:f>SUM(M330:O330)</x:f>
       </x:c>
       <x:c r="Q330" s="0"/>
-      <x:c r="R330" s="71">
+      <x:c r="R330" s="75">
         <x:f>IF(B330&gt;0,IF(TauxActuariel,((B330+1)^(1/NbEchAn))-1,B330/NbEchAn),R329)</x:f>
       </x:c>
-      <x:c r="S330" s="70">
+      <x:c r="S330" s="74">
         <x:f>IF(E330&gt;0,E330,IF(D330&gt;0,IF(AND(EchFIXE,R330&gt;0),ROUND((L330-C330)*R330/(1-((1+R330)^-D330)),NbDeci),ROUND(L330/D330,NbDeci)),S329))</x:f>
       </x:c>
     </x:row>
@@ -18927,10 +18929,10 @@
         <x:f>SUM(M331:O331)</x:f>
       </x:c>
       <x:c r="Q331" s="0"/>
-      <x:c r="R331" s="71">
+      <x:c r="R331" s="75">
         <x:f>IF(B331&gt;0,IF(TauxActuariel,((B331+1)^(1/NbEchAn))-1,B331/NbEchAn),R330)</x:f>
       </x:c>
-      <x:c r="S331" s="70">
+      <x:c r="S331" s="74">
         <x:f>IF(E331&gt;0,E331,IF(D331&gt;0,IF(AND(EchFIXE,R331&gt;0),ROUND((L331-C331)*R331/(1-((1+R331)^-D331)),NbDeci),ROUND(L331/D331,NbDeci)),S330))</x:f>
       </x:c>
     </x:row>
@@ -18968,10 +18970,10 @@
         <x:f>SUM(M332:O332)</x:f>
       </x:c>
       <x:c r="Q332" s="0"/>
-      <x:c r="R332" s="71">
+      <x:c r="R332" s="75">
         <x:f>IF(B332&gt;0,IF(TauxActuariel,((B332+1)^(1/NbEchAn))-1,B332/NbEchAn),R331)</x:f>
       </x:c>
-      <x:c r="S332" s="70">
+      <x:c r="S332" s="74">
         <x:f>IF(E332&gt;0,E332,IF(D332&gt;0,IF(AND(EchFIXE,R332&gt;0),ROUND((L332-C332)*R332/(1-((1+R332)^-D332)),NbDeci),ROUND(L332/D332,NbDeci)),S331))</x:f>
       </x:c>
     </x:row>
@@ -19009,10 +19011,10 @@
         <x:f>SUM(M333:O333)</x:f>
       </x:c>
       <x:c r="Q333" s="0"/>
-      <x:c r="R333" s="71">
+      <x:c r="R333" s="75">
         <x:f>IF(B333&gt;0,IF(TauxActuariel,((B333+1)^(1/NbEchAn))-1,B333/NbEchAn),R332)</x:f>
       </x:c>
-      <x:c r="S333" s="70">
+      <x:c r="S333" s="74">
         <x:f>IF(E333&gt;0,E333,IF(D333&gt;0,IF(AND(EchFIXE,R333&gt;0),ROUND((L333-C333)*R333/(1-((1+R333)^-D333)),NbDeci),ROUND(L333/D333,NbDeci)),S332))</x:f>
       </x:c>
     </x:row>
@@ -19050,10 +19052,10 @@
         <x:f>SUM(M334:O334)</x:f>
       </x:c>
       <x:c r="Q334" s="0"/>
-      <x:c r="R334" s="71">
+      <x:c r="R334" s="75">
         <x:f>IF(B334&gt;0,IF(TauxActuariel,((B334+1)^(1/NbEchAn))-1,B334/NbEchAn),R333)</x:f>
       </x:c>
-      <x:c r="S334" s="70">
+      <x:c r="S334" s="74">
         <x:f>IF(E334&gt;0,E334,IF(D334&gt;0,IF(AND(EchFIXE,R334&gt;0),ROUND((L334-C334)*R334/(1-((1+R334)^-D334)),NbDeci),ROUND(L334/D334,NbDeci)),S333))</x:f>
       </x:c>
     </x:row>
@@ -19091,10 +19093,10 @@
         <x:f>SUM(M335:O335)</x:f>
       </x:c>
       <x:c r="Q335" s="0"/>
-      <x:c r="R335" s="71">
+      <x:c r="R335" s="75">
         <x:f>IF(B335&gt;0,IF(TauxActuariel,((B335+1)^(1/NbEchAn))-1,B335/NbEchAn),R334)</x:f>
       </x:c>
-      <x:c r="S335" s="70">
+      <x:c r="S335" s="74">
         <x:f>IF(E335&gt;0,E335,IF(D335&gt;0,IF(AND(EchFIXE,R335&gt;0),ROUND((L335-C335)*R335/(1-((1+R335)^-D335)),NbDeci),ROUND(L335/D335,NbDeci)),S334))</x:f>
       </x:c>
     </x:row>
@@ -19132,10 +19134,10 @@
         <x:f>SUM(M336:O336)</x:f>
       </x:c>
       <x:c r="Q336" s="0"/>
-      <x:c r="R336" s="71">
+      <x:c r="R336" s="75">
         <x:f>IF(B336&gt;0,IF(TauxActuariel,((B336+1)^(1/NbEchAn))-1,B336/NbEchAn),R335)</x:f>
       </x:c>
-      <x:c r="S336" s="70">
+      <x:c r="S336" s="74">
         <x:f>IF(E336&gt;0,E336,IF(D336&gt;0,IF(AND(EchFIXE,R336&gt;0),ROUND((L336-C336)*R336/(1-((1+R336)^-D336)),NbDeci),ROUND(L336/D336,NbDeci)),S335))</x:f>
       </x:c>
     </x:row>
@@ -19173,10 +19175,10 @@
         <x:f>SUM(M337:O337)</x:f>
       </x:c>
       <x:c r="Q337" s="0"/>
-      <x:c r="R337" s="71">
+      <x:c r="R337" s="75">
         <x:f>IF(B337&gt;0,IF(TauxActuariel,((B337+1)^(1/NbEchAn))-1,B337/NbEchAn),R336)</x:f>
       </x:c>
-      <x:c r="S337" s="70">
+      <x:c r="S337" s="74">
         <x:f>IF(E337&gt;0,E337,IF(D337&gt;0,IF(AND(EchFIXE,R337&gt;0),ROUND((L337-C337)*R337/(1-((1+R337)^-D337)),NbDeci),ROUND(L337/D337,NbDeci)),S336))</x:f>
       </x:c>
     </x:row>
@@ -19214,10 +19216,10 @@
         <x:f>SUM(M338:O338)</x:f>
       </x:c>
       <x:c r="Q338" s="0"/>
-      <x:c r="R338" s="71">
+      <x:c r="R338" s="75">
         <x:f>IF(B338&gt;0,IF(TauxActuariel,((B338+1)^(1/NbEchAn))-1,B338/NbEchAn),R337)</x:f>
       </x:c>
-      <x:c r="S338" s="70">
+      <x:c r="S338" s="74">
         <x:f>IF(E338&gt;0,E338,IF(D338&gt;0,IF(AND(EchFIXE,R338&gt;0),ROUND((L338-C338)*R338/(1-((1+R338)^-D338)),NbDeci),ROUND(L338/D338,NbDeci)),S337))</x:f>
       </x:c>
     </x:row>
@@ -19255,10 +19257,10 @@
         <x:f>SUM(M339:O339)</x:f>
       </x:c>
       <x:c r="Q339" s="0"/>
-      <x:c r="R339" s="71">
+      <x:c r="R339" s="75">
         <x:f>IF(B339&gt;0,IF(TauxActuariel,((B339+1)^(1/NbEchAn))-1,B339/NbEchAn),R338)</x:f>
       </x:c>
-      <x:c r="S339" s="70">
+      <x:c r="S339" s="74">
         <x:f>IF(E339&gt;0,E339,IF(D339&gt;0,IF(AND(EchFIXE,R339&gt;0),ROUND((L339-C339)*R339/(1-((1+R339)^-D339)),NbDeci),ROUND(L339/D339,NbDeci)),S338))</x:f>
       </x:c>
     </x:row>
@@ -19296,10 +19298,10 @@
         <x:f>SUM(M340:O340)</x:f>
       </x:c>
       <x:c r="Q340" s="0"/>
-      <x:c r="R340" s="71">
+      <x:c r="R340" s="75">
         <x:f>IF(B340&gt;0,IF(TauxActuariel,((B340+1)^(1/NbEchAn))-1,B340/NbEchAn),R339)</x:f>
       </x:c>
-      <x:c r="S340" s="70">
+      <x:c r="S340" s="74">
         <x:f>IF(E340&gt;0,E340,IF(D340&gt;0,IF(AND(EchFIXE,R340&gt;0),ROUND((L340-C340)*R340/(1-((1+R340)^-D340)),NbDeci),ROUND(L340/D340,NbDeci)),S339))</x:f>
       </x:c>
     </x:row>
@@ -19337,10 +19339,10 @@
         <x:f>SUM(M341:O341)</x:f>
       </x:c>
       <x:c r="Q341" s="0"/>
-      <x:c r="R341" s="71">
+      <x:c r="R341" s="75">
         <x:f>IF(B341&gt;0,IF(TauxActuariel,((B341+1)^(1/NbEchAn))-1,B341/NbEchAn),R340)</x:f>
       </x:c>
-      <x:c r="S341" s="70">
+      <x:c r="S341" s="74">
         <x:f>IF(E341&gt;0,E341,IF(D341&gt;0,IF(AND(EchFIXE,R341&gt;0),ROUND((L341-C341)*R341/(1-((1+R341)^-D341)),NbDeci),ROUND(L341/D341,NbDeci)),S340))</x:f>
       </x:c>
     </x:row>
@@ -19378,10 +19380,10 @@
         <x:f>SUM(M342:O342)</x:f>
       </x:c>
       <x:c r="Q342" s="0"/>
-      <x:c r="R342" s="71">
+      <x:c r="R342" s="75">
         <x:f>IF(B342&gt;0,IF(TauxActuariel,((B342+1)^(1/NbEchAn))-1,B342/NbEchAn),R341)</x:f>
       </x:c>
-      <x:c r="S342" s="70">
+      <x:c r="S342" s="74">
         <x:f>IF(E342&gt;0,E342,IF(D342&gt;0,IF(AND(EchFIXE,R342&gt;0),ROUND((L342-C342)*R342/(1-((1+R342)^-D342)),NbDeci),ROUND(L342/D342,NbDeci)),S341))</x:f>
       </x:c>
     </x:row>
@@ -19419,10 +19421,10 @@
         <x:f>SUM(M343:O343)</x:f>
       </x:c>
       <x:c r="Q343" s="0"/>
-      <x:c r="R343" s="71">
+      <x:c r="R343" s="75">
         <x:f>IF(B343&gt;0,IF(TauxActuariel,((B343+1)^(1/NbEchAn))-1,B343/NbEchAn),R342)</x:f>
       </x:c>
-      <x:c r="S343" s="70">
+      <x:c r="S343" s="74">
         <x:f>IF(E343&gt;0,E343,IF(D343&gt;0,IF(AND(EchFIXE,R343&gt;0),ROUND((L343-C343)*R343/(1-((1+R343)^-D343)),NbDeci),ROUND(L343/D343,NbDeci)),S342))</x:f>
       </x:c>
     </x:row>
@@ -19460,10 +19462,10 @@
         <x:f>SUM(M344:O344)</x:f>
       </x:c>
       <x:c r="Q344" s="0"/>
-      <x:c r="R344" s="71">
+      <x:c r="R344" s="75">
         <x:f>IF(B344&gt;0,IF(TauxActuariel,((B344+1)^(1/NbEchAn))-1,B344/NbEchAn),R343)</x:f>
       </x:c>
-      <x:c r="S344" s="70">
+      <x:c r="S344" s="74">
         <x:f>IF(E344&gt;0,E344,IF(D344&gt;0,IF(AND(EchFIXE,R344&gt;0),ROUND((L344-C344)*R344/(1-((1+R344)^-D344)),NbDeci),ROUND(L344/D344,NbDeci)),S343))</x:f>
       </x:c>
     </x:row>
@@ -19501,10 +19503,10 @@
         <x:f>SUM(M345:O345)</x:f>
       </x:c>
       <x:c r="Q345" s="0"/>
-      <x:c r="R345" s="71">
+      <x:c r="R345" s="75">
         <x:f>IF(B345&gt;0,IF(TauxActuariel,((B345+1)^(1/NbEchAn))-1,B345/NbEchAn),R344)</x:f>
       </x:c>
-      <x:c r="S345" s="70">
+      <x:c r="S345" s="74">
         <x:f>IF(E345&gt;0,E345,IF(D345&gt;0,IF(AND(EchFIXE,R345&gt;0),ROUND((L345-C345)*R345/(1-((1+R345)^-D345)),NbDeci),ROUND(L345/D345,NbDeci)),S344))</x:f>
       </x:c>
     </x:row>
@@ -19542,10 +19544,10 @@
         <x:f>SUM(M346:O346)</x:f>
       </x:c>
       <x:c r="Q346" s="0"/>
-      <x:c r="R346" s="71">
+      <x:c r="R346" s="75">
         <x:f>IF(B346&gt;0,IF(TauxActuariel,((B346+1)^(1/NbEchAn))-1,B346/NbEchAn),R345)</x:f>
       </x:c>
-      <x:c r="S346" s="70">
+      <x:c r="S346" s="74">
         <x:f>IF(E346&gt;0,E346,IF(D346&gt;0,IF(AND(EchFIXE,R346&gt;0),ROUND((L346-C346)*R346/(1-((1+R346)^-D346)),NbDeci),ROUND(L346/D346,NbDeci)),S345))</x:f>
       </x:c>
     </x:row>
@@ -19583,10 +19585,10 @@
         <x:f>SUM(M347:O347)</x:f>
       </x:c>
       <x:c r="Q347" s="0"/>
-      <x:c r="R347" s="71">
+      <x:c r="R347" s="75">
         <x:f>IF(B347&gt;0,IF(TauxActuariel,((B347+1)^(1/NbEchAn))-1,B347/NbEchAn),R346)</x:f>
       </x:c>
-      <x:c r="S347" s="70">
+      <x:c r="S347" s="74">
         <x:f>IF(E347&gt;0,E347,IF(D347&gt;0,IF(AND(EchFIXE,R347&gt;0),ROUND((L347-C347)*R347/(1-((1+R347)^-D347)),NbDeci),ROUND(L347/D347,NbDeci)),S346))</x:f>
       </x:c>
     </x:row>
@@ -19624,10 +19626,10 @@
         <x:f>SUM(M348:O348)</x:f>
       </x:c>
       <x:c r="Q348" s="0"/>
-      <x:c r="R348" s="71">
+      <x:c r="R348" s="75">
         <x:f>IF(B348&gt;0,IF(TauxActuariel,((B348+1)^(1/NbEchAn))-1,B348/NbEchAn),R347)</x:f>
       </x:c>
-      <x:c r="S348" s="70">
+      <x:c r="S348" s="74">
         <x:f>IF(E348&gt;0,E348,IF(D348&gt;0,IF(AND(EchFIXE,R348&gt;0),ROUND((L348-C348)*R348/(1-((1+R348)^-D348)),NbDeci),ROUND(L348/D348,NbDeci)),S347))</x:f>
       </x:c>
     </x:row>
@@ -19665,10 +19667,10 @@
         <x:f>SUM(M349:O349)</x:f>
       </x:c>
       <x:c r="Q349" s="0"/>
-      <x:c r="R349" s="71">
+      <x:c r="R349" s="75">
         <x:f>IF(B349&gt;0,IF(TauxActuariel,((B349+1)^(1/NbEchAn))-1,B349/NbEchAn),R348)</x:f>
       </x:c>
-      <x:c r="S349" s="70">
+      <x:c r="S349" s="74">
         <x:f>IF(E349&gt;0,E349,IF(D349&gt;0,IF(AND(EchFIXE,R349&gt;0),ROUND((L349-C349)*R349/(1-((1+R349)^-D349)),NbDeci),ROUND(L349/D349,NbDeci)),S348))</x:f>
       </x:c>
     </x:row>
@@ -19706,10 +19708,10 @@
         <x:f>SUM(M350:O350)</x:f>
       </x:c>
       <x:c r="Q350" s="0"/>
-      <x:c r="R350" s="71">
+      <x:c r="R350" s="75">
         <x:f>IF(B350&gt;0,IF(TauxActuariel,((B350+1)^(1/NbEchAn))-1,B350/NbEchAn),R349)</x:f>
       </x:c>
-      <x:c r="S350" s="70">
+      <x:c r="S350" s="74">
         <x:f>IF(E350&gt;0,E350,IF(D350&gt;0,IF(AND(EchFIXE,R350&gt;0),ROUND((L350-C350)*R350/(1-((1+R350)^-D350)),NbDeci),ROUND(L350/D350,NbDeci)),S349))</x:f>
       </x:c>
     </x:row>
@@ -19747,10 +19749,10 @@
         <x:f>SUM(M351:O351)</x:f>
       </x:c>
       <x:c r="Q351" s="0"/>
-      <x:c r="R351" s="71">
+      <x:c r="R351" s="75">
         <x:f>IF(B351&gt;0,IF(TauxActuariel,((B351+1)^(1/NbEchAn))-1,B351/NbEchAn),R350)</x:f>
       </x:c>
-      <x:c r="S351" s="70">
+      <x:c r="S351" s="74">
         <x:f>IF(E351&gt;0,E351,IF(D351&gt;0,IF(AND(EchFIXE,R351&gt;0),ROUND((L351-C351)*R351/(1-((1+R351)^-D351)),NbDeci),ROUND(L351/D351,NbDeci)),S350))</x:f>
       </x:c>
     </x:row>
@@ -19788,10 +19790,10 @@
         <x:f>SUM(M352:O352)</x:f>
       </x:c>
       <x:c r="Q352" s="0"/>
-      <x:c r="R352" s="71">
+      <x:c r="R352" s="75">
         <x:f>IF(B352&gt;0,IF(TauxActuariel,((B352+1)^(1/NbEchAn))-1,B352/NbEchAn),R351)</x:f>
       </x:c>
-      <x:c r="S352" s="70">
+      <x:c r="S352" s="74">
         <x:f>IF(E352&gt;0,E352,IF(D352&gt;0,IF(AND(EchFIXE,R352&gt;0),ROUND((L352-C352)*R352/(1-((1+R352)^-D352)),NbDeci),ROUND(L352/D352,NbDeci)),S351))</x:f>
       </x:c>
     </x:row>
@@ -19829,10 +19831,10 @@
         <x:f>SUM(M353:O353)</x:f>
       </x:c>
       <x:c r="Q353" s="0"/>
-      <x:c r="R353" s="71">
+      <x:c r="R353" s="75">
         <x:f>IF(B353&gt;0,IF(TauxActuariel,((B353+1)^(1/NbEchAn))-1,B353/NbEchAn),R352)</x:f>
       </x:c>
-      <x:c r="S353" s="70">
+      <x:c r="S353" s="74">
         <x:f>IF(E353&gt;0,E353,IF(D353&gt;0,IF(AND(EchFIXE,R353&gt;0),ROUND((L353-C353)*R353/(1-((1+R353)^-D353)),NbDeci),ROUND(L353/D353,NbDeci)),S352))</x:f>
       </x:c>
     </x:row>
@@ -19870,10 +19872,10 @@
         <x:f>SUM(M354:O354)</x:f>
       </x:c>
       <x:c r="Q354" s="0"/>
-      <x:c r="R354" s="71">
+      <x:c r="R354" s="75">
         <x:f>IF(B354&gt;0,IF(TauxActuariel,((B354+1)^(1/NbEchAn))-1,B354/NbEchAn),R353)</x:f>
       </x:c>
-      <x:c r="S354" s="70">
+      <x:c r="S354" s="74">
         <x:f>IF(E354&gt;0,E354,IF(D354&gt;0,IF(AND(EchFIXE,R354&gt;0),ROUND((L354-C354)*R354/(1-((1+R354)^-D354)),NbDeci),ROUND(L354/D354,NbDeci)),S353))</x:f>
       </x:c>
     </x:row>
@@ -19911,10 +19913,10 @@
         <x:f>SUM(M355:O355)</x:f>
       </x:c>
       <x:c r="Q355" s="0"/>
-      <x:c r="R355" s="71">
+      <x:c r="R355" s="75">
         <x:f>IF(B355&gt;0,IF(TauxActuariel,((B355+1)^(1/NbEchAn))-1,B355/NbEchAn),R354)</x:f>
       </x:c>
-      <x:c r="S355" s="70">
+      <x:c r="S355" s="74">
         <x:f>IF(E355&gt;0,E355,IF(D355&gt;0,IF(AND(EchFIXE,R355&gt;0),ROUND((L355-C355)*R355/(1-((1+R355)^-D355)),NbDeci),ROUND(L355/D355,NbDeci)),S354))</x:f>
       </x:c>
     </x:row>
@@ -19952,10 +19954,10 @@
         <x:f>SUM(M356:O356)</x:f>
       </x:c>
       <x:c r="Q356" s="0"/>
-      <x:c r="R356" s="71">
+      <x:c r="R356" s="75">
         <x:f>IF(B356&gt;0,IF(TauxActuariel,((B356+1)^(1/NbEchAn))-1,B356/NbEchAn),R355)</x:f>
       </x:c>
-      <x:c r="S356" s="70">
+      <x:c r="S356" s="74">
         <x:f>IF(E356&gt;0,E356,IF(D356&gt;0,IF(AND(EchFIXE,R356&gt;0),ROUND((L356-C356)*R356/(1-((1+R356)^-D356)),NbDeci),ROUND(L356/D356,NbDeci)),S355))</x:f>
       </x:c>
     </x:row>
@@ -19993,10 +19995,10 @@
         <x:f>SUM(M357:O357)</x:f>
       </x:c>
       <x:c r="Q357" s="0"/>
-      <x:c r="R357" s="71">
+      <x:c r="R357" s="75">
         <x:f>IF(B357&gt;0,IF(TauxActuariel,((B357+1)^(1/NbEchAn))-1,B357/NbEchAn),R356)</x:f>
       </x:c>
-      <x:c r="S357" s="70">
+      <x:c r="S357" s="74">
         <x:f>IF(E357&gt;0,E357,IF(D357&gt;0,IF(AND(EchFIXE,R357&gt;0),ROUND((L357-C357)*R357/(1-((1+R357)^-D357)),NbDeci),ROUND(L357/D357,NbDeci)),S356))</x:f>
       </x:c>
     </x:row>
@@ -20034,10 +20036,10 @@
         <x:f>SUM(M358:O358)</x:f>
       </x:c>
       <x:c r="Q358" s="0"/>
-      <x:c r="R358" s="71">
+      <x:c r="R358" s="75">
         <x:f>IF(B358&gt;0,IF(TauxActuariel,((B358+1)^(1/NbEchAn))-1,B358/NbEchAn),R357)</x:f>
       </x:c>
-      <x:c r="S358" s="70">
+      <x:c r="S358" s="74">
         <x:f>IF(E358&gt;0,E358,IF(D358&gt;0,IF(AND(EchFIXE,R358&gt;0),ROUND((L358-C358)*R358/(1-((1+R358)^-D358)),NbDeci),ROUND(L358/D358,NbDeci)),S357))</x:f>
       </x:c>
     </x:row>
@@ -20075,10 +20077,10 @@
         <x:f>SUM(M359:O359)</x:f>
       </x:c>
       <x:c r="Q359" s="0"/>
-      <x:c r="R359" s="71">
+      <x:c r="R359" s="75">
         <x:f>IF(B359&gt;0,IF(TauxActuariel,((B359+1)^(1/NbEchAn))-1,B359/NbEchAn),R358)</x:f>
       </x:c>
-      <x:c r="S359" s="70">
+      <x:c r="S359" s="74">
         <x:f>IF(E359&gt;0,E359,IF(D359&gt;0,IF(AND(EchFIXE,R359&gt;0),ROUND((L359-C359)*R359/(1-((1+R359)^-D359)),NbDeci),ROUND(L359/D359,NbDeci)),S358))</x:f>
       </x:c>
     </x:row>
@@ -20116,10 +20118,10 @@
         <x:f>SUM(M360:O360)</x:f>
       </x:c>
       <x:c r="Q360" s="0"/>
-      <x:c r="R360" s="71">
+      <x:c r="R360" s="75">
         <x:f>IF(B360&gt;0,IF(TauxActuariel,((B360+1)^(1/NbEchAn))-1,B360/NbEchAn),R359)</x:f>
       </x:c>
-      <x:c r="S360" s="70">
+      <x:c r="S360" s="74">
         <x:f>IF(E360&gt;0,E360,IF(D360&gt;0,IF(AND(EchFIXE,R360&gt;0),ROUND((L360-C360)*R360/(1-((1+R360)^-D360)),NbDeci),ROUND(L360/D360,NbDeci)),S359))</x:f>
       </x:c>
     </x:row>
@@ -20157,10 +20159,10 @@
         <x:f>SUM(M361:O361)</x:f>
       </x:c>
       <x:c r="Q361" s="0"/>
-      <x:c r="R361" s="71">
+      <x:c r="R361" s="75">
         <x:f>IF(B361&gt;0,IF(TauxActuariel,((B361+1)^(1/NbEchAn))-1,B361/NbEchAn),R360)</x:f>
       </x:c>
-      <x:c r="S361" s="70">
+      <x:c r="S361" s="74">
         <x:f>IF(E361&gt;0,E361,IF(D361&gt;0,IF(AND(EchFIXE,R361&gt;0),ROUND((L361-C361)*R361/(1-((1+R361)^-D361)),NbDeci),ROUND(L361/D361,NbDeci)),S360))</x:f>
       </x:c>
     </x:row>
@@ -20198,10 +20200,10 @@
         <x:f>SUM(M362:O362)</x:f>
       </x:c>
       <x:c r="Q362" s="0"/>
-      <x:c r="R362" s="71">
+      <x:c r="R362" s="75">
         <x:f>IF(B362&gt;0,IF(TauxActuariel,((B362+1)^(1/NbEchAn))-1,B362/NbEchAn),R361)</x:f>
       </x:c>
-      <x:c r="S362" s="70">
+      <x:c r="S362" s="74">
         <x:f>IF(E362&gt;0,E362,IF(D362&gt;0,IF(AND(EchFIXE,R362&gt;0),ROUND((L362-C362)*R362/(1-((1+R362)^-D362)),NbDeci),ROUND(L362/D362,NbDeci)),S361))</x:f>
       </x:c>
     </x:row>
@@ -20239,10 +20241,10 @@
         <x:f>SUM(M363:O363)</x:f>
       </x:c>
       <x:c r="Q363" s="0"/>
-      <x:c r="R363" s="71">
+      <x:c r="R363" s="75">
         <x:f>IF(B363&gt;0,IF(TauxActuariel,((B363+1)^(1/NbEchAn))-1,B363/NbEchAn),R362)</x:f>
       </x:c>
-      <x:c r="S363" s="70">
+      <x:c r="S363" s="74">
         <x:f>IF(E363&gt;0,E363,IF(D363&gt;0,IF(AND(EchFIXE,R363&gt;0),ROUND((L363-C363)*R363/(1-((1+R363)^-D363)),NbDeci),ROUND(L363/D363,NbDeci)),S362))</x:f>
       </x:c>
     </x:row>
@@ -20280,10 +20282,10 @@
         <x:f>SUM(M364:O364)</x:f>
       </x:c>
       <x:c r="Q364" s="0"/>
-      <x:c r="R364" s="71">
+      <x:c r="R364" s="75">
         <x:f>IF(B364&gt;0,IF(TauxActuariel,((B364+1)^(1/NbEchAn))-1,B364/NbEchAn),R363)</x:f>
       </x:c>
-      <x:c r="S364" s="70">
+      <x:c r="S364" s="74">
         <x:f>IF(E364&gt;0,E364,IF(D364&gt;0,IF(AND(EchFIXE,R364&gt;0),ROUND((L364-C364)*R364/(1-((1+R364)^-D364)),NbDeci),ROUND(L364/D364,NbDeci)),S363))</x:f>
       </x:c>
     </x:row>
@@ -20321,10 +20323,10 @@
         <x:f>SUM(M365:O365)</x:f>
       </x:c>
       <x:c r="Q365" s="0"/>
-      <x:c r="R365" s="71">
+      <x:c r="R365" s="75">
         <x:f>IF(B365&gt;0,IF(TauxActuariel,((B365+1)^(1/NbEchAn))-1,B365/NbEchAn),R364)</x:f>
       </x:c>
-      <x:c r="S365" s="70">
+      <x:c r="S365" s="74">
         <x:f>IF(E365&gt;0,E365,IF(D365&gt;0,IF(AND(EchFIXE,R365&gt;0),ROUND((L365-C365)*R365/(1-((1+R365)^-D365)),NbDeci),ROUND(L365/D365,NbDeci)),S364))</x:f>
       </x:c>
     </x:row>
@@ -20362,10 +20364,10 @@
         <x:f>SUM(M366:O366)</x:f>
       </x:c>
       <x:c r="Q366" s="0"/>
-      <x:c r="R366" s="71">
+      <x:c r="R366" s="75">
         <x:f>IF(B366&gt;0,IF(TauxActuariel,((B366+1)^(1/NbEchAn))-1,B366/NbEchAn),R365)</x:f>
       </x:c>
-      <x:c r="S366" s="70">
+      <x:c r="S366" s="74">
         <x:f>IF(E366&gt;0,E366,IF(D366&gt;0,IF(AND(EchFIXE,R366&gt;0),ROUND((L366-C366)*R366/(1-((1+R366)^-D366)),NbDeci),ROUND(L366/D366,NbDeci)),S365))</x:f>
       </x:c>
     </x:row>
@@ -20403,10 +20405,10 @@
         <x:f>SUM(M367:O367)</x:f>
       </x:c>
       <x:c r="Q367" s="0"/>
-      <x:c r="R367" s="71">
+      <x:c r="R367" s="75">
         <x:f>IF(B367&gt;0,IF(TauxActuariel,((B367+1)^(1/NbEchAn))-1,B367/NbEchAn),R366)</x:f>
       </x:c>
-      <x:c r="S367" s="70">
+      <x:c r="S367" s="74">
         <x:f>IF(E367&gt;0,E367,IF(D367&gt;0,IF(AND(EchFIXE,R367&gt;0),ROUND((L367-C367)*R367/(1-((1+R367)^-D367)),NbDeci),ROUND(L367/D367,NbDeci)),S366))</x:f>
       </x:c>
     </x:row>
@@ -20444,10 +20446,10 @@
         <x:f>SUM(M368:O368)</x:f>
       </x:c>
       <x:c r="Q368" s="0"/>
-      <x:c r="R368" s="71">
+      <x:c r="R368" s="75">
         <x:f>IF(B368&gt;0,IF(TauxActuariel,((B368+1)^(1/NbEchAn))-1,B368/NbEchAn),R367)</x:f>
       </x:c>
-      <x:c r="S368" s="70">
+      <x:c r="S368" s="74">
         <x:f>IF(E368&gt;0,E368,IF(D368&gt;0,IF(AND(EchFIXE,R368&gt;0),ROUND((L368-C368)*R368/(1-((1+R368)^-D368)),NbDeci),ROUND(L368/D368,NbDeci)),S367))</x:f>
       </x:c>
     </x:row>
@@ -20485,10 +20487,10 @@
         <x:f>SUM(M369:O369)</x:f>
       </x:c>
       <x:c r="Q369" s="0"/>
-      <x:c r="R369" s="71">
+      <x:c r="R369" s="75">
         <x:f>IF(B369&gt;0,IF(TauxActuariel,((B369+1)^(1/NbEchAn))-1,B369/NbEchAn),R368)</x:f>
       </x:c>
-      <x:c r="S369" s="70">
+      <x:c r="S369" s="74">
         <x:f>IF(E369&gt;0,E369,IF(D369&gt;0,IF(AND(EchFIXE,R369&gt;0),ROUND((L369-C369)*R369/(1-((1+R369)^-D369)),NbDeci),ROUND(L369/D369,NbDeci)),S368))</x:f>
       </x:c>
     </x:row>
@@ -20526,10 +20528,10 @@
         <x:f>SUM(M370:O370)</x:f>
       </x:c>
       <x:c r="Q370" s="0"/>
-      <x:c r="R370" s="71">
+      <x:c r="R370" s="75">
         <x:f>IF(B370&gt;0,IF(TauxActuariel,((B370+1)^(1/NbEchAn))-1,B370/NbEchAn),R369)</x:f>
       </x:c>
-      <x:c r="S370" s="70">
+      <x:c r="S370" s="74">
         <x:f>IF(E370&gt;0,E370,IF(D370&gt;0,IF(AND(EchFIXE,R370&gt;0),ROUND((L370-C370)*R370/(1-((1+R370)^-D370)),NbDeci),ROUND(L370/D370,NbDeci)),S369))</x:f>
       </x:c>
     </x:row>
@@ -20567,10 +20569,10 @@
         <x:f>SUM(M371:O371)</x:f>
       </x:c>
       <x:c r="Q371" s="0"/>
-      <x:c r="R371" s="71">
+      <x:c r="R371" s="75">
         <x:f>IF(B371&gt;0,IF(TauxActuariel,((B371+1)^(1/NbEchAn))-1,B371/NbEchAn),R370)</x:f>
       </x:c>
-      <x:c r="S371" s="70">
+      <x:c r="S371" s="74">
         <x:f>IF(E371&gt;0,E371,IF(D371&gt;0,IF(AND(EchFIXE,R371&gt;0),ROUND((L371-C371)*R371/(1-((1+R371)^-D371)),NbDeci),ROUND(L371/D371,NbDeci)),S370))</x:f>
       </x:c>
     </x:row>
@@ -20608,10 +20610,10 @@
         <x:f>SUM(M372:O372)</x:f>
       </x:c>
       <x:c r="Q372" s="0"/>
-      <x:c r="R372" s="71">
+      <x:c r="R372" s="75">
         <x:f>IF(B372&gt;0,IF(TauxActuariel,((B372+1)^(1/NbEchAn))-1,B372/NbEchAn),R371)</x:f>
       </x:c>
-      <x:c r="S372" s="70">
+      <x:c r="S372" s="74">
         <x:f>IF(E372&gt;0,E372,IF(D372&gt;0,IF(AND(EchFIXE,R372&gt;0),ROUND((L372-C372)*R372/(1-((1+R372)^-D372)),NbDeci),ROUND(L372/D372,NbDeci)),S371))</x:f>
       </x:c>
     </x:row>
@@ -20649,10 +20651,10 @@
         <x:f>SUM(M373:O373)</x:f>
       </x:c>
       <x:c r="Q373" s="0"/>
-      <x:c r="R373" s="71">
+      <x:c r="R373" s="75">
         <x:f>IF(B373&gt;0,IF(TauxActuariel,((B373+1)^(1/NbEchAn))-1,B373/NbEchAn),R372)</x:f>
       </x:c>
-      <x:c r="S373" s="70">
+      <x:c r="S373" s="74">
         <x:f>IF(E373&gt;0,E373,IF(D373&gt;0,IF(AND(EchFIXE,R373&gt;0),ROUND((L373-C373)*R373/(1-((1+R373)^-D373)),NbDeci),ROUND(L373/D373,NbDeci)),S372))</x:f>
       </x:c>
     </x:row>
@@ -20690,10 +20692,10 @@
         <x:f>SUM(M374:O374)</x:f>
       </x:c>
       <x:c r="Q374" s="0"/>
-      <x:c r="R374" s="71">
+      <x:c r="R374" s="75">
         <x:f>IF(B374&gt;0,IF(TauxActuariel,((B374+1)^(1/NbEchAn))-1,B374/NbEchAn),R373)</x:f>
       </x:c>
-      <x:c r="S374" s="70">
+      <x:c r="S374" s="74">
         <x:f>IF(E374&gt;0,E374,IF(D374&gt;0,IF(AND(EchFIXE,R374&gt;0),ROUND((L374-C374)*R374/(1-((1+R374)^-D374)),NbDeci),ROUND(L374/D374,NbDeci)),S373))</x:f>
       </x:c>
     </x:row>
@@ -20731,10 +20733,10 @@
         <x:f>SUM(M375:O375)</x:f>
       </x:c>
       <x:c r="Q375" s="0"/>
-      <x:c r="R375" s="71">
+      <x:c r="R375" s="75">
         <x:f>IF(B375&gt;0,IF(TauxActuariel,((B375+1)^(1/NbEchAn))-1,B375/NbEchAn),R374)</x:f>
       </x:c>
-      <x:c r="S375" s="70">
+      <x:c r="S375" s="74">
         <x:f>IF(E375&gt;0,E375,IF(D375&gt;0,IF(AND(EchFIXE,R375&gt;0),ROUND((L375-C375)*R375/(1-((1+R375)^-D375)),NbDeci),ROUND(L375/D375,NbDeci)),S374))</x:f>
       </x:c>
     </x:row>
@@ -20772,10 +20774,10 @@
         <x:f>SUM(M376:O376)</x:f>
       </x:c>
       <x:c r="Q376" s="0"/>
-      <x:c r="R376" s="71">
+      <x:c r="R376" s="75">
         <x:f>IF(B376&gt;0,IF(TauxActuariel,((B376+1)^(1/NbEchAn))-1,B376/NbEchAn),R375)</x:f>
       </x:c>
-      <x:c r="S376" s="70">
+      <x:c r="S376" s="74">
         <x:f>IF(E376&gt;0,E376,IF(D376&gt;0,IF(AND(EchFIXE,R376&gt;0),ROUND((L376-C376)*R376/(1-((1+R376)^-D376)),NbDeci),ROUND(L376/D376,NbDeci)),S375))</x:f>
       </x:c>
     </x:row>
@@ -20813,10 +20815,10 @@
         <x:f>SUM(M377:O377)</x:f>
       </x:c>
       <x:c r="Q377" s="0"/>
-      <x:c r="R377" s="71">
+      <x:c r="R377" s="75">
         <x:f>IF(B377&gt;0,IF(TauxActuariel,((B377+1)^(1/NbEchAn))-1,B377/NbEchAn),R376)</x:f>
       </x:c>
-      <x:c r="S377" s="70">
+      <x:c r="S377" s="74">
         <x:f>IF(E377&gt;0,E377,IF(D377&gt;0,IF(AND(EchFIXE,R377&gt;0),ROUND((L377-C377)*R377/(1-((1+R377)^-D377)),NbDeci),ROUND(L377/D377,NbDeci)),S376))</x:f>
       </x:c>
     </x:row>
@@ -20854,10 +20856,10 @@
         <x:f>SUM(M378:O378)</x:f>
       </x:c>
       <x:c r="Q378" s="0"/>
-      <x:c r="R378" s="71">
+      <x:c r="R378" s="75">
         <x:f>IF(B378&gt;0,IF(TauxActuariel,((B378+1)^(1/NbEchAn))-1,B378/NbEchAn),R377)</x:f>
       </x:c>
-      <x:c r="S378" s="70">
+      <x:c r="S378" s="74">
         <x:f>IF(E378&gt;0,E378,IF(D378&gt;0,IF(AND(EchFIXE,R378&gt;0),ROUND((L378-C378)*R378/(1-((1+R378)^-D378)),NbDeci),ROUND(L378/D378,NbDeci)),S377))</x:f>
       </x:c>
     </x:row>
@@ -20895,10 +20897,10 @@
         <x:f>SUM(M379:O379)</x:f>
       </x:c>
       <x:c r="Q379" s="0"/>
-      <x:c r="R379" s="71">
+      <x:c r="R379" s="75">
         <x:f>IF(B379&gt;0,IF(TauxActuariel,((B379+1)^(1/NbEchAn))-1,B379/NbEchAn),R378)</x:f>
       </x:c>
-      <x:c r="S379" s="70">
+      <x:c r="S379" s="74">
         <x:f>IF(E379&gt;0,E379,IF(D379&gt;0,IF(AND(EchFIXE,R379&gt;0),ROUND((L379-C379)*R379/(1-((1+R379)^-D379)),NbDeci),ROUND(L379/D379,NbDeci)),S378))</x:f>
       </x:c>
     </x:row>
@@ -20936,10 +20938,10 @@
         <x:f>SUM(M380:O380)</x:f>
       </x:c>
       <x:c r="Q380" s="0"/>
-      <x:c r="R380" s="71">
+      <x:c r="R380" s="75">
         <x:f>IF(B380&gt;0,IF(TauxActuariel,((B380+1)^(1/NbEchAn))-1,B380/NbEchAn),R379)</x:f>
       </x:c>
-      <x:c r="S380" s="70">
+      <x:c r="S380" s="74">
         <x:f>IF(E380&gt;0,E380,IF(D380&gt;0,IF(AND(EchFIXE,R380&gt;0),ROUND((L380-C380)*R380/(1-((1+R380)^-D380)),NbDeci),ROUND(L380/D380,NbDeci)),S379))</x:f>
       </x:c>
     </x:row>
@@ -20977,10 +20979,10 @@
         <x:f>SUM(M381:O381)</x:f>
       </x:c>
       <x:c r="Q381" s="0"/>
-      <x:c r="R381" s="71">
+      <x:c r="R381" s="75">
         <x:f>IF(B381&gt;0,IF(TauxActuariel,((B381+1)^(1/NbEchAn))-1,B381/NbEchAn),R380)</x:f>
       </x:c>
-      <x:c r="S381" s="70">
+      <x:c r="S381" s="74">
         <x:f>IF(E381&gt;0,E381,IF(D381&gt;0,IF(AND(EchFIXE,R381&gt;0),ROUND((L381-C381)*R381/(1-((1+R381)^-D381)),NbDeci),ROUND(L381/D381,NbDeci)),S380))</x:f>
       </x:c>
     </x:row>
@@ -21018,10 +21020,10 @@
         <x:f>SUM(M382:O382)</x:f>
       </x:c>
       <x:c r="Q382" s="0"/>
-      <x:c r="R382" s="71">
+      <x:c r="R382" s="75">
         <x:f>IF(B382&gt;0,IF(TauxActuariel,((B382+1)^(1/NbEchAn))-1,B382/NbEchAn),R381)</x:f>
       </x:c>
-      <x:c r="S382" s="70">
+      <x:c r="S382" s="74">
         <x:f>IF(E382&gt;0,E382,IF(D382&gt;0,IF(AND(EchFIXE,R382&gt;0),ROUND((L382-C382)*R382/(1-((1+R382)^-D382)),NbDeci),ROUND(L382/D382,NbDeci)),S381))</x:f>
       </x:c>
     </x:row>
@@ -21059,10 +21061,10 @@
         <x:f>SUM(M383:O383)</x:f>
       </x:c>
       <x:c r="Q383" s="0"/>
-      <x:c r="R383" s="71">
+      <x:c r="R383" s="75">
         <x:f>IF(B383&gt;0,IF(TauxActuariel,((B383+1)^(1/NbEchAn))-1,B383/NbEchAn),R382)</x:f>
       </x:c>
-      <x:c r="S383" s="70">
+      <x:c r="S383" s="74">
         <x:f>IF(E383&gt;0,E383,IF(D383&gt;0,IF(AND(EchFIXE,R383&gt;0),ROUND((L383-C383)*R383/(1-((1+R383)^-D383)),NbDeci),ROUND(L383/D383,NbDeci)),S382))</x:f>
       </x:c>
     </x:row>
@@ -21100,10 +21102,10 @@
         <x:f>SUM(M384:O384)</x:f>
       </x:c>
       <x:c r="Q384" s="0"/>
-      <x:c r="R384" s="71">
+      <x:c r="R384" s="75">
         <x:f>IF(B384&gt;0,IF(TauxActuariel,((B384+1)^(1/NbEchAn))-1,B384/NbEchAn),R383)</x:f>
       </x:c>
-      <x:c r="S384" s="70">
+      <x:c r="S384" s="74">
         <x:f>IF(E384&gt;0,E384,IF(D384&gt;0,IF(AND(EchFIXE,R384&gt;0),ROUND((L384-C384)*R384/(1-((1+R384)^-D384)),NbDeci),ROUND(L384/D384,NbDeci)),S383))</x:f>
       </x:c>
     </x:row>
@@ -21141,10 +21143,10 @@
         <x:f>SUM(M385:O385)</x:f>
       </x:c>
       <x:c r="Q385" s="0"/>
-      <x:c r="R385" s="71">
+      <x:c r="R385" s="75">
         <x:f>IF(B385&gt;0,IF(TauxActuariel,((B385+1)^(1/NbEchAn))-1,B385/NbEchAn),R384)</x:f>
       </x:c>
-      <x:c r="S385" s="70">
+      <x:c r="S385" s="74">
         <x:f>IF(E385&gt;0,E385,IF(D385&gt;0,IF(AND(EchFIXE,R385&gt;0),ROUND((L385-C385)*R385/(1-((1+R385)^-D385)),NbDeci),ROUND(L385/D385,NbDeci)),S384))</x:f>
       </x:c>
     </x:row>
@@ -21182,10 +21184,10 @@
         <x:f>SUM(M386:O386)</x:f>
       </x:c>
       <x:c r="Q386" s="0"/>
-      <x:c r="R386" s="71">
+      <x:c r="R386" s="75">
         <x:f>IF(B386&gt;0,IF(TauxActuariel,((B386+1)^(1/NbEchAn))-1,B386/NbEchAn),R385)</x:f>
       </x:c>
-      <x:c r="S386" s="70">
+      <x:c r="S386" s="74">
         <x:f>IF(E386&gt;0,E386,IF(D386&gt;0,IF(AND(EchFIXE,R386&gt;0),ROUND((L386-C386)*R386/(1-((1+R386)^-D386)),NbDeci),ROUND(L386/D386,NbDeci)),S385))</x:f>
       </x:c>
     </x:row>
@@ -21223,10 +21225,10 @@
         <x:f>SUM(M387:O387)</x:f>
       </x:c>
       <x:c r="Q387" s="0"/>
-      <x:c r="R387" s="71">
+      <x:c r="R387" s="75">
         <x:f>IF(B387&gt;0,IF(TauxActuariel,((B387+1)^(1/NbEchAn))-1,B387/NbEchAn),R386)</x:f>
       </x:c>
-      <x:c r="S387" s="70">
+      <x:c r="S387" s="74">
         <x:f>IF(E387&gt;0,E387,IF(D387&gt;0,IF(AND(EchFIXE,R387&gt;0),ROUND((L387-C387)*R387/(1-((1+R387)^-D387)),NbDeci),ROUND(L387/D387,NbDeci)),S386))</x:f>
       </x:c>
     </x:row>
@@ -21264,10 +21266,10 @@
         <x:f>SUM(M388:O388)</x:f>
       </x:c>
       <x:c r="Q388" s="0"/>
-      <x:c r="R388" s="71">
+      <x:c r="R388" s="75">
         <x:f>IF(B388&gt;0,IF(TauxActuariel,((B388+1)^(1/NbEchAn))-1,B388/NbEchAn),R387)</x:f>
       </x:c>
-      <x:c r="S388" s="70">
+      <x:c r="S388" s="74">
         <x:f>IF(E388&gt;0,E388,IF(D388&gt;0,IF(AND(EchFIXE,R388&gt;0),ROUND((L388-C388)*R388/(1-((1+R388)^-D388)),NbDeci),ROUND(L388/D388,NbDeci)),S387))</x:f>
       </x:c>
     </x:row>
@@ -21305,10 +21307,10 @@
         <x:f>SUM(M389:O389)</x:f>
       </x:c>
       <x:c r="Q389" s="0"/>
-      <x:c r="R389" s="71">
+      <x:c r="R389" s="75">
         <x:f>IF(B389&gt;0,IF(TauxActuariel,((B389+1)^(1/NbEchAn))-1,B389/NbEchAn),R388)</x:f>
       </x:c>
-      <x:c r="S389" s="70">
+      <x:c r="S389" s="74">
         <x:f>IF(E389&gt;0,E389,IF(D389&gt;0,IF(AND(EchFIXE,R389&gt;0),ROUND((L389-C389)*R389/(1-((1+R389)^-D389)),NbDeci),ROUND(L389/D389,NbDeci)),S388))</x:f>
       </x:c>
     </x:row>
@@ -21346,10 +21348,10 @@
         <x:f>SUM(M390:O390)</x:f>
       </x:c>
       <x:c r="Q390" s="0"/>
-      <x:c r="R390" s="71">
+      <x:c r="R390" s="75">
         <x:f>IF(B390&gt;0,IF(TauxActuariel,((B390+1)^(1/NbEchAn))-1,B390/NbEchAn),R389)</x:f>
       </x:c>
-      <x:c r="S390" s="70">
+      <x:c r="S390" s="74">
         <x:f>IF(E390&gt;0,E390,IF(D390&gt;0,IF(AND(EchFIXE,R390&gt;0),ROUND((L390-C390)*R390/(1-((1+R390)^-D390)),NbDeci),ROUND(L390/D390,NbDeci)),S389))</x:f>
       </x:c>
     </x:row>
@@ -21387,10 +21389,10 @@
         <x:f>SUM(M391:O391)</x:f>
       </x:c>
       <x:c r="Q391" s="0"/>
-      <x:c r="R391" s="71">
+      <x:c r="R391" s="75">
         <x:f>IF(B391&gt;0,IF(TauxActuariel,((B391+1)^(1/NbEchAn))-1,B391/NbEchAn),R390)</x:f>
       </x:c>
-      <x:c r="S391" s="70">
+      <x:c r="S391" s="74">
         <x:f>IF(E391&gt;0,E391,IF(D391&gt;0,IF(AND(EchFIXE,R391&gt;0),ROUND((L391-C391)*R391/(1-((1+R391)^-D391)),NbDeci),ROUND(L391/D391,NbDeci)),S390))</x:f>
       </x:c>
     </x:row>
@@ -21428,10 +21430,10 @@
         <x:f>SUM(M392:O392)</x:f>
       </x:c>
       <x:c r="Q392" s="0"/>
-      <x:c r="R392" s="71">
+      <x:c r="R392" s="75">
         <x:f>IF(B392&gt;0,IF(TauxActuariel,((B392+1)^(1/NbEchAn))-1,B392/NbEchAn),R391)</x:f>
       </x:c>
-      <x:c r="S392" s="70">
+      <x:c r="S392" s="74">
         <x:f>IF(E392&gt;0,E392,IF(D392&gt;0,IF(AND(EchFIXE,R392&gt;0),ROUND((L392-C392)*R392/(1-((1+R392)^-D392)),NbDeci),ROUND(L392/D392,NbDeci)),S391))</x:f>
       </x:c>
     </x:row>
@@ -21469,10 +21471,10 @@
         <x:f>SUM(M393:O393)</x:f>
       </x:c>
       <x:c r="Q393" s="0"/>
-      <x:c r="R393" s="71">
+      <x:c r="R393" s="75">
         <x:f>IF(B393&gt;0,IF(TauxActuariel,((B393+1)^(1/NbEchAn))-1,B393/NbEchAn),R392)</x:f>
       </x:c>
-      <x:c r="S393" s="70">
+      <x:c r="S393" s="74">
         <x:f>IF(E393&gt;0,E393,IF(D393&gt;0,IF(AND(EchFIXE,R393&gt;0),ROUND((L393-C393)*R393/(1-((1+R393)^-D393)),NbDeci),ROUND(L393/D393,NbDeci)),S392))</x:f>
       </x:c>
     </x:row>
@@ -21510,10 +21512,10 @@
         <x:f>SUM(M394:O394)</x:f>
       </x:c>
       <x:c r="Q394" s="0"/>
-      <x:c r="R394" s="71">
+      <x:c r="R394" s="75">
         <x:f>IF(B394&gt;0,IF(TauxActuariel,((B394+1)^(1/NbEchAn))-1,B394/NbEchAn),R393)</x:f>
       </x:c>
-      <x:c r="S394" s="70">
+      <x:c r="S394" s="74">
         <x:f>IF(E394&gt;0,E394,IF(D394&gt;0,IF(AND(EchFIXE,R394&gt;0),ROUND((L394-C394)*R394/(1-((1+R394)^-D394)),NbDeci),ROUND(L394/D394,NbDeci)),S393))</x:f>
       </x:c>
     </x:row>
@@ -21551,10 +21553,10 @@
         <x:f>SUM(M395:O395)</x:f>
       </x:c>
       <x:c r="Q395" s="0"/>
-      <x:c r="R395" s="71">
+      <x:c r="R395" s="75">
         <x:f>IF(B395&gt;0,IF(TauxActuariel,((B395+1)^(1/NbEchAn))-1,B395/NbEchAn),R394)</x:f>
       </x:c>
-      <x:c r="S395" s="70">
+      <x:c r="S395" s="74">
         <x:f>IF(E395&gt;0,E395,IF(D395&gt;0,IF(AND(EchFIXE,R395&gt;0),ROUND((L395-C395)*R395/(1-((1+R395)^-D395)),NbDeci),ROUND(L395/D395,NbDeci)),S394))</x:f>
       </x:c>
     </x:row>
@@ -21592,10 +21594,10 @@
         <x:f>SUM(M396:O396)</x:f>
       </x:c>
       <x:c r="Q396" s="0"/>
-      <x:c r="R396" s="71">
+      <x:c r="R396" s="75">
         <x:f>IF(B396&gt;0,IF(TauxActuariel,((B396+1)^(1/NbEchAn))-1,B396/NbEchAn),R395)</x:f>
       </x:c>
-      <x:c r="S396" s="70">
+      <x:c r="S396" s="74">
         <x:f>IF(E396&gt;0,E396,IF(D396&gt;0,IF(AND(EchFIXE,R396&gt;0),ROUND((L396-C396)*R396/(1-((1+R396)^-D396)),NbDeci),ROUND(L396/D396,NbDeci)),S395))</x:f>
       </x:c>
     </x:row>
@@ -21633,10 +21635,10 @@
         <x:f>SUM(M397:O397)</x:f>
       </x:c>
       <x:c r="Q397" s="0"/>
-      <x:c r="R397" s="71">
+      <x:c r="R397" s="75">
         <x:f>IF(B397&gt;0,IF(TauxActuariel,((B397+1)^(1/NbEchAn))-1,B397/NbEchAn),R396)</x:f>
       </x:c>
-      <x:c r="S397" s="70">
+      <x:c r="S397" s="74">
         <x:f>IF(E397&gt;0,E397,IF(D397&gt;0,IF(AND(EchFIXE,R397&gt;0),ROUND((L397-C397)*R397/(1-((1+R397)^-D397)),NbDeci),ROUND(L397/D397,NbDeci)),S396))</x:f>
       </x:c>
     </x:row>
@@ -21674,10 +21676,10 @@
         <x:f>SUM(M398:O398)</x:f>
       </x:c>
       <x:c r="Q398" s="0"/>
-      <x:c r="R398" s="71">
+      <x:c r="R398" s="75">
         <x:f>IF(B398&gt;0,IF(TauxActuariel,((B398+1)^(1/NbEchAn))-1,B398/NbEchAn),R397)</x:f>
       </x:c>
-      <x:c r="S398" s="70">
+      <x:c r="S398" s="74">
         <x:f>IF(E398&gt;0,E398,IF(D398&gt;0,IF(AND(EchFIXE,R398&gt;0),ROUND((L398-C398)*R398/(1-((1+R398)^-D398)),NbDeci),ROUND(L398/D398,NbDeci)),S397))</x:f>
       </x:c>
     </x:row>
@@ -21715,10 +21717,10 @@
         <x:f>SUM(M399:O399)</x:f>
       </x:c>
       <x:c r="Q399" s="0"/>
-      <x:c r="R399" s="71">
+      <x:c r="R399" s="75">
         <x:f>IF(B399&gt;0,IF(TauxActuariel,((B399+1)^(1/NbEchAn))-1,B399/NbEchAn),R398)</x:f>
       </x:c>
-      <x:c r="S399" s="70">
+      <x:c r="S399" s="74">
         <x:f>IF(E399&gt;0,E399,IF(D399&gt;0,IF(AND(EchFIXE,R399&gt;0),ROUND((L399-C399)*R399/(1-((1+R399)^-D399)),NbDeci),ROUND(L399/D399,NbDeci)),S398))</x:f>
       </x:c>
     </x:row>
@@ -21756,10 +21758,10 @@
         <x:f>SUM(M400:O400)</x:f>
       </x:c>
       <x:c r="Q400" s="0"/>
-      <x:c r="R400" s="71">
+      <x:c r="R400" s="75">
         <x:f>IF(B400&gt;0,IF(TauxActuariel,((B400+1)^(1/NbEchAn))-1,B400/NbEchAn),R399)</x:f>
       </x:c>
-      <x:c r="S400" s="70">
+      <x:c r="S400" s="74">
         <x:f>IF(E400&gt;0,E400,IF(D400&gt;0,IF(AND(EchFIXE,R400&gt;0),ROUND((L400-C400)*R400/(1-((1+R400)^-D400)),NbDeci),ROUND(L400/D400,NbDeci)),S399))</x:f>
       </x:c>
     </x:row>
@@ -21797,10 +21799,10 @@
         <x:f>SUM(M401:O401)</x:f>
       </x:c>
       <x:c r="Q401" s="0"/>
-      <x:c r="R401" s="71">
+      <x:c r="R401" s="75">
         <x:f>IF(B401&gt;0,IF(TauxActuariel,((B401+1)^(1/NbEchAn))-1,B401/NbEchAn),R400)</x:f>
       </x:c>
-      <x:c r="S401" s="70">
+      <x:c r="S401" s="74">
         <x:f>IF(E401&gt;0,E401,IF(D401&gt;0,IF(AND(EchFIXE,R401&gt;0),ROUND((L401-C401)*R401/(1-((1+R401)^-D401)),NbDeci),ROUND(L401/D401,NbDeci)),S400))</x:f>
       </x:c>
     </x:row>
@@ -21838,10 +21840,10 @@
         <x:f>SUM(M402:O402)</x:f>
       </x:c>
       <x:c r="Q402" s="0"/>
-      <x:c r="R402" s="71">
+      <x:c r="R402" s="75">
         <x:f>IF(B402&gt;0,IF(TauxActuariel,((B402+1)^(1/NbEchAn))-1,B402/NbEchAn),R401)</x:f>
       </x:c>
-      <x:c r="S402" s="70">
+      <x:c r="S402" s="74">
         <x:f>IF(E402&gt;0,E402,IF(D402&gt;0,IF(AND(EchFIXE,R402&gt;0),ROUND((L402-C402)*R402/(1-((1+R402)^-D402)),NbDeci),ROUND(L402/D402,NbDeci)),S401))</x:f>
       </x:c>
     </x:row>
@@ -21879,10 +21881,10 @@
         <x:f>SUM(M403:O403)</x:f>
       </x:c>
       <x:c r="Q403" s="0"/>
-      <x:c r="R403" s="71">
+      <x:c r="R403" s="75">
         <x:f>IF(B403&gt;0,IF(TauxActuariel,((B403+1)^(1/NbEchAn))-1,B403/NbEchAn),R402)</x:f>
       </x:c>
-      <x:c r="S403" s="70">
+      <x:c r="S403" s="74">
         <x:f>IF(E403&gt;0,E403,IF(D403&gt;0,IF(AND(EchFIXE,R403&gt;0),ROUND((L403-C403)*R403/(1-((1+R403)^-D403)),NbDeci),ROUND(L403/D403,NbDeci)),S402))</x:f>
       </x:c>
     </x:row>
@@ -21920,10 +21922,10 @@
         <x:f>SUM(M404:O404)</x:f>
       </x:c>
       <x:c r="Q404" s="0"/>
-      <x:c r="R404" s="71">
+      <x:c r="R404" s="75">
         <x:f>IF(B404&gt;0,IF(TauxActuariel,((B404+1)^(1/NbEchAn))-1,B404/NbEchAn),R403)</x:f>
       </x:c>
-      <x:c r="S404" s="70">
+      <x:c r="S404" s="74">
         <x:f>IF(E404&gt;0,E404,IF(D404&gt;0,IF(AND(EchFIXE,R404&gt;0),ROUND((L404-C404)*R404/(1-((1+R404)^-D404)),NbDeci),ROUND(L404/D404,NbDeci)),S403))</x:f>
       </x:c>
     </x:row>
@@ -21961,10 +21963,10 @@
         <x:f>SUM(M405:O405)</x:f>
       </x:c>
       <x:c r="Q405" s="0"/>
-      <x:c r="R405" s="71">
+      <x:c r="R405" s="75">
         <x:f>IF(B405&gt;0,IF(TauxActuariel,((B405+1)^(1/NbEchAn))-1,B405/NbEchAn),R404)</x:f>
       </x:c>
-      <x:c r="S405" s="70">
+      <x:c r="S405" s="74">
         <x:f>IF(E405&gt;0,E405,IF(D405&gt;0,IF(AND(EchFIXE,R405&gt;0),ROUND((L405-C405)*R405/(1-((1+R405)^-D405)),NbDeci),ROUND(L405/D405,NbDeci)),S404))</x:f>
       </x:c>
     </x:row>
@@ -22002,10 +22004,10 @@
         <x:f>SUM(M406:O406)</x:f>
       </x:c>
       <x:c r="Q406" s="0"/>
-      <x:c r="R406" s="71">
+      <x:c r="R406" s="75">
         <x:f>IF(B406&gt;0,IF(TauxActuariel,((B406+1)^(1/NbEchAn))-1,B406/NbEchAn),R405)</x:f>
       </x:c>
-      <x:c r="S406" s="70">
+      <x:c r="S406" s="74">
         <x:f>IF(E406&gt;0,E406,IF(D406&gt;0,IF(AND(EchFIXE,R406&gt;0),ROUND((L406-C406)*R406/(1-((1+R406)^-D406)),NbDeci),ROUND(L406/D406,NbDeci)),S405))</x:f>
       </x:c>
     </x:row>
@@ -22043,10 +22045,10 @@
         <x:f>SUM(M407:O407)</x:f>
       </x:c>
       <x:c r="Q407" s="0"/>
-      <x:c r="R407" s="71">
+      <x:c r="R407" s="75">
         <x:f>IF(B407&gt;0,IF(TauxActuariel,((B407+1)^(1/NbEchAn))-1,B407/NbEchAn),R406)</x:f>
       </x:c>
-      <x:c r="S407" s="70">
+      <x:c r="S407" s="74">
         <x:f>IF(E407&gt;0,E407,IF(D407&gt;0,IF(AND(EchFIXE,R407&gt;0),ROUND((L407-C407)*R407/(1-((1+R407)^-D407)),NbDeci),ROUND(L407/D407,NbDeci)),S406))</x:f>
       </x:c>
     </x:row>
@@ -22084,10 +22086,10 @@
         <x:f>SUM(M408:O408)</x:f>
       </x:c>
       <x:c r="Q408" s="0"/>
-      <x:c r="R408" s="71">
+      <x:c r="R408" s="75">
         <x:f>IF(B408&gt;0,IF(TauxActuariel,((B408+1)^(1/NbEchAn))-1,B408/NbEchAn),R407)</x:f>
       </x:c>
-      <x:c r="S408" s="70">
+      <x:c r="S408" s="74">
         <x:f>IF(E408&gt;0,E408,IF(D408&gt;0,IF(AND(EchFIXE,R408&gt;0),ROUND((L408-C408)*R408/(1-((1+R408)^-D408)),NbDeci),ROUND(L408/D408,NbDeci)),S407))</x:f>
       </x:c>
     </x:row>
@@ -22125,10 +22127,10 @@
         <x:f>SUM(M409:O409)</x:f>
       </x:c>
       <x:c r="Q409" s="0"/>
-      <x:c r="R409" s="71">
+      <x:c r="R409" s="75">
         <x:f>IF(B409&gt;0,IF(TauxActuariel,((B409+1)^(1/NbEchAn))-1,B409/NbEchAn),R408)</x:f>
       </x:c>
-      <x:c r="S409" s="70">
+      <x:c r="S409" s="74">
         <x:f>IF(E409&gt;0,E409,IF(D409&gt;0,IF(AND(EchFIXE,R409&gt;0),ROUND((L409-C409)*R409/(1-((1+R409)^-D409)),NbDeci),ROUND(L409/D409,NbDeci)),S408))</x:f>
       </x:c>
     </x:row>
@@ -22166,10 +22168,10 @@
         <x:f>SUM(M410:O410)</x:f>
       </x:c>
       <x:c r="Q410" s="0"/>
-      <x:c r="R410" s="71">
+      <x:c r="R410" s="75">
         <x:f>IF(B410&gt;0,IF(TauxActuariel,((B410+1)^(1/NbEchAn))-1,B410/NbEchAn),R409)</x:f>
       </x:c>
-      <x:c r="S410" s="70">
+      <x:c r="S410" s="74">
         <x:f>IF(E410&gt;0,E410,IF(D410&gt;0,IF(AND(EchFIXE,R410&gt;0),ROUND((L410-C410)*R410/(1-((1+R410)^-D410)),NbDeci),ROUND(L410/D410,NbDeci)),S409))</x:f>
       </x:c>
     </x:row>
@@ -22207,10 +22209,10 @@
         <x:f>SUM(M411:O411)</x:f>
       </x:c>
       <x:c r="Q411" s="0"/>
-      <x:c r="R411" s="71">
+      <x:c r="R411" s="75">
         <x:f>IF(B411&gt;0,IF(TauxActuariel,((B411+1)^(1/NbEchAn))-1,B411/NbEchAn),R410)</x:f>
       </x:c>
-      <x:c r="S411" s="70">
+      <x:c r="S411" s="74">
         <x:f>IF(E411&gt;0,E411,IF(D411&gt;0,IF(AND(EchFIXE,R411&gt;0),ROUND((L411-C411)*R411/(1-((1+R411)^-D411)),NbDeci),ROUND(L411/D411,NbDeci)),S410))</x:f>
       </x:c>
     </x:row>
@@ -22248,10 +22250,10 @@
         <x:f>SUM(M412:O412)</x:f>
       </x:c>
       <x:c r="Q412" s="0"/>
-      <x:c r="R412" s="71">
+      <x:c r="R412" s="75">
         <x:f>IF(B412&gt;0,IF(TauxActuariel,((B412+1)^(1/NbEchAn))-1,B412/NbEchAn),R411)</x:f>
       </x:c>
-      <x:c r="S412" s="70">
+      <x:c r="S412" s="74">
         <x:f>IF(E412&gt;0,E412,IF(D412&gt;0,IF(AND(EchFIXE,R412&gt;0),ROUND((L412-C412)*R412/(1-((1+R412)^-D412)),NbDeci),ROUND(L412/D412,NbDeci)),S411))</x:f>
       </x:c>
     </x:row>
@@ -22289,10 +22291,10 @@
         <x:f>SUM(M413:O413)</x:f>
       </x:c>
       <x:c r="Q413" s="0"/>
-      <x:c r="R413" s="71">
+      <x:c r="R413" s="75">
         <x:f>IF(B413&gt;0,IF(TauxActuariel,((B413+1)^(1/NbEchAn))-1,B413/NbEchAn),R412)</x:f>
       </x:c>
-      <x:c r="S413" s="70">
+      <x:c r="S413" s="74">
         <x:f>IF(E413&gt;0,E413,IF(D413&gt;0,IF(AND(EchFIXE,R413&gt;0),ROUND((L413-C413)*R413/(1-((1+R413)^-D413)),NbDeci),ROUND(L413/D413,NbDeci)),S412))</x:f>
       </x:c>
     </x:row>
@@ -22330,10 +22332,10 @@
         <x:f>SUM(M414:O414)</x:f>
       </x:c>
       <x:c r="Q414" s="0"/>
-      <x:c r="R414" s="71">
+      <x:c r="R414" s="75">
         <x:f>IF(B414&gt;0,IF(TauxActuariel,((B414+1)^(1/NbEchAn))-1,B414/NbEchAn),R413)</x:f>
       </x:c>
-      <x:c r="S414" s="70">
+      <x:c r="S414" s="74">
         <x:f>IF(E414&gt;0,E414,IF(D414&gt;0,IF(AND(EchFIXE,R414&gt;0),ROUND((L414-C414)*R414/(1-((1+R414)^-D414)),NbDeci),ROUND(L414/D414,NbDeci)),S413))</x:f>
       </x:c>
     </x:row>
@@ -22371,10 +22373,10 @@
         <x:f>SUM(M415:O415)</x:f>
       </x:c>
       <x:c r="Q415" s="0"/>
-      <x:c r="R415" s="71">
+      <x:c r="R415" s="75">
         <x:f>IF(B415&gt;0,IF(TauxActuariel,((B415+1)^(1/NbEchAn))-1,B415/NbEchAn),R414)</x:f>
       </x:c>
-      <x:c r="S415" s="70">
+      <x:c r="S415" s="74">
         <x:f>IF(E415&gt;0,E415,IF(D415&gt;0,IF(AND(EchFIXE,R415&gt;0),ROUND((L415-C415)*R415/(1-((1+R415)^-D415)),NbDeci),ROUND(L415/D415,NbDeci)),S414))</x:f>
       </x:c>
     </x:row>
@@ -22412,10 +22414,10 @@
         <x:f>SUM(M416:O416)</x:f>
       </x:c>
       <x:c r="Q416" s="0"/>
-      <x:c r="R416" s="71">
+      <x:c r="R416" s="75">
         <x:f>IF(B416&gt;0,IF(TauxActuariel,((B416+1)^(1/NbEchAn))-1,B416/NbEchAn),R415)</x:f>
       </x:c>
-      <x:c r="S416" s="70">
+      <x:c r="S416" s="74">
         <x:f>IF(E416&gt;0,E416,IF(D416&gt;0,IF(AND(EchFIXE,R416&gt;0),ROUND((L416-C416)*R416/(1-((1+R416)^-D416)),NbDeci),ROUND(L416/D416,NbDeci)),S415))</x:f>
       </x:c>
     </x:row>
@@ -22453,10 +22455,10 @@
         <x:f>SUM(M417:O417)</x:f>
       </x:c>
       <x:c r="Q417" s="0"/>
-      <x:c r="R417" s="71">
+      <x:c r="R417" s="75">
         <x:f>IF(B417&gt;0,IF(TauxActuariel,((B417+1)^(1/NbEchAn))-1,B417/NbEchAn),R416)</x:f>
       </x:c>
-      <x:c r="S417" s="70">
+      <x:c r="S417" s="74">
         <x:f>IF(E417&gt;0,E417,IF(D417&gt;0,IF(AND(EchFIXE,R417&gt;0),ROUND((L417-C417)*R417/(1-((1+R417)^-D417)),NbDeci),ROUND(L417/D417,NbDeci)),S416))</x:f>
       </x:c>
     </x:row>
@@ -22494,10 +22496,10 @@
         <x:f>SUM(M418:O418)</x:f>
       </x:c>
       <x:c r="Q418" s="0"/>
-      <x:c r="R418" s="71">
+      <x:c r="R418" s="75">
         <x:f>IF(B418&gt;0,IF(TauxActuariel,((B418+1)^(1/NbEchAn))-1,B418/NbEchAn),R417)</x:f>
       </x:c>
-      <x:c r="S418" s="70">
+      <x:c r="S418" s="74">
         <x:f>IF(E418&gt;0,E418,IF(D418&gt;0,IF(AND(EchFIXE,R418&gt;0),ROUND((L418-C418)*R418/(1-((1+R418)^-D418)),NbDeci),ROUND(L418/D418,NbDeci)),S417))</x:f>
       </x:c>
     </x:row>
@@ -22535,10 +22537,10 @@
         <x:f>SUM(M419:O419)</x:f>
       </x:c>
       <x:c r="Q419" s="0"/>
-      <x:c r="R419" s="71">
+      <x:c r="R419" s="75">
         <x:f>IF(B419&gt;0,IF(TauxActuariel,((B419+1)^(1/NbEchAn))-1,B419/NbEchAn),R418)</x:f>
       </x:c>
-      <x:c r="S419" s="70">
+      <x:c r="S419" s="74">
         <x:f>IF(E419&gt;0,E419,IF(D419&gt;0,IF(AND(EchFIXE,R419&gt;0),ROUND((L419-C419)*R419/(1-((1+R419)^-D419)),NbDeci),ROUND(L419/D419,NbDeci)),S418))</x:f>
       </x:c>
     </x:row>
@@ -22576,10 +22578,10 @@
         <x:f>SUM(M420:O420)</x:f>
       </x:c>
       <x:c r="Q420" s="0"/>
-      <x:c r="R420" s="71">
+      <x:c r="R420" s="75">
         <x:f>IF(B420&gt;0,IF(TauxActuariel,((B420+1)^(1/NbEchAn))-1,B420/NbEchAn),R419)</x:f>
       </x:c>
-      <x:c r="S420" s="70">
+      <x:c r="S420" s="74">
         <x:f>IF(E420&gt;0,E420,IF(D420&gt;0,IF(AND(EchFIXE,R420&gt;0),ROUND((L420-C420)*R420/(1-((1+R420)^-D420)),NbDeci),ROUND(L420/D420,NbDeci)),S419))</x:f>
       </x:c>
     </x:row>
@@ -22617,10 +22619,10 @@
         <x:f>SUM(M421:O421)</x:f>
       </x:c>
       <x:c r="Q421" s="0"/>
-      <x:c r="R421" s="71">
+      <x:c r="R421" s="75">
         <x:f>IF(B421&gt;0,IF(TauxActuariel,((B421+1)^(1/NbEchAn))-1,B421/NbEchAn),R420)</x:f>
       </x:c>
-      <x:c r="S421" s="70">
+      <x:c r="S421" s="74">
         <x:f>IF(E421&gt;0,E421,IF(D421&gt;0,IF(AND(EchFIXE,R421&gt;0),ROUND((L421-C421)*R421/(1-((1+R421)^-D421)),NbDeci),ROUND(L421/D421,NbDeci)),S420))</x:f>
       </x:c>
     </x:row>
@@ -22658,10 +22660,10 @@
         <x:f>SUM(M422:O422)</x:f>
       </x:c>
       <x:c r="Q422" s="0"/>
-      <x:c r="R422" s="71">
+      <x:c r="R422" s="75">
         <x:f>IF(B422&gt;0,IF(TauxActuariel,((B422+1)^(1/NbEchAn))-1,B422/NbEchAn),R421)</x:f>
       </x:c>
-      <x:c r="S422" s="70">
+      <x:c r="S422" s="74">
         <x:f>IF(E422&gt;0,E422,IF(D422&gt;0,IF(AND(EchFIXE,R422&gt;0),ROUND((L422-C422)*R422/(1-((1+R422)^-D422)),NbDeci),ROUND(L422/D422,NbDeci)),S421))</x:f>
       </x:c>
     </x:row>
@@ -22699,10 +22701,10 @@
         <x:f>SUM(M423:O423)</x:f>
       </x:c>
       <x:c r="Q423" s="0"/>
-      <x:c r="R423" s="71">
+      <x:c r="R423" s="75">
         <x:f>IF(B423&gt;0,IF(TauxActuariel,((B423+1)^(1/NbEchAn))-1,B423/NbEchAn),R422)</x:f>
       </x:c>
-      <x:c r="S423" s="70">
+      <x:c r="S423" s="74">
         <x:f>IF(E423&gt;0,E423,IF(D423&gt;0,IF(AND(EchFIXE,R423&gt;0),ROUND((L423-C423)*R423/(1-((1+R423)^-D423)),NbDeci),ROUND(L423/D423,NbDeci)),S422))</x:f>
       </x:c>
     </x:row>
@@ -22740,10 +22742,10 @@
         <x:f>SUM(M424:O424)</x:f>
       </x:c>
       <x:c r="Q424" s="0"/>
-      <x:c r="R424" s="71">
+      <x:c r="R424" s="75">
         <x:f>IF(B424&gt;0,IF(TauxActuariel,((B424+1)^(1/NbEchAn))-1,B424/NbEchAn),R423)</x:f>
       </x:c>
-      <x:c r="S424" s="70">
+      <x:c r="S424" s="74">
         <x:f>IF(E424&gt;0,E424,IF(D424&gt;0,IF(AND(EchFIXE,R424&gt;0),ROUND((L424-C424)*R424/(1-((1+R424)^-D424)),NbDeci),ROUND(L424/D424,NbDeci)),S423))</x:f>
       </x:c>
     </x:row>
@@ -22781,10 +22783,10 @@
         <x:f>SUM(M425:O425)</x:f>
       </x:c>
       <x:c r="Q425" s="0"/>
-      <x:c r="R425" s="71">
+      <x:c r="R425" s="75">
         <x:f>IF(B425&gt;0,IF(TauxActuariel,((B425+1)^(1/NbEchAn))-1,B425/NbEchAn),R424)</x:f>
       </x:c>
-      <x:c r="S425" s="70">
+      <x:c r="S425" s="74">
         <x:f>IF(E425&gt;0,E425,IF(D425&gt;0,IF(AND(EchFIXE,R425&gt;0),ROUND((L425-C425)*R425/(1-((1+R425)^-D425)),NbDeci),ROUND(L425/D425,NbDeci)),S424))</x:f>
       </x:c>
     </x:row>
@@ -22822,10 +22824,10 @@
         <x:f>SUM(M426:O426)</x:f>
       </x:c>
       <x:c r="Q426" s="0"/>
-      <x:c r="R426" s="71">
+      <x:c r="R426" s="75">
         <x:f>IF(B426&gt;0,IF(TauxActuariel,((B426+1)^(1/NbEchAn))-1,B426/NbEchAn),R425)</x:f>
       </x:c>
-      <x:c r="S426" s="70">
+      <x:c r="S426" s="74">
         <x:f>IF(E426&gt;0,E426,IF(D426&gt;0,IF(AND(EchFIXE,R426&gt;0),ROUND((L426-C426)*R426/(1-((1+R426)^-D426)),NbDeci),ROUND(L426/D426,NbDeci)),S425))</x:f>
       </x:c>
     </x:row>
@@ -22863,10 +22865,10 @@
         <x:f>SUM(M427:O427)</x:f>
       </x:c>
       <x:c r="Q427" s="0"/>
-      <x:c r="R427" s="71">
+      <x:c r="R427" s="75">
         <x:f>IF(B427&gt;0,IF(TauxActuariel,((B427+1)^(1/NbEchAn))-1,B427/NbEchAn),R426)</x:f>
       </x:c>
-      <x:c r="S427" s="70">
+      <x:c r="S427" s="74">
         <x:f>IF(E427&gt;0,E427,IF(D427&gt;0,IF(AND(EchFIXE,R427&gt;0),ROUND((L427-C427)*R427/(1-((1+R427)^-D427)),NbDeci),ROUND(L427/D427,NbDeci)),S426))</x:f>
       </x:c>
     </x:row>
@@ -22904,10 +22906,10 @@
         <x:f>SUM(M428:O428)</x:f>
       </x:c>
       <x:c r="Q428" s="0"/>
-      <x:c r="R428" s="71">
+      <x:c r="R428" s="75">
         <x:f>IF(B428&gt;0,IF(TauxActuariel,((B428+1)^(1/NbEchAn))-1,B428/NbEchAn),R427)</x:f>
       </x:c>
-      <x:c r="S428" s="70">
+      <x:c r="S428" s="74">
         <x:f>IF(E428&gt;0,E428,IF(D428&gt;0,IF(AND(EchFIXE,R428&gt;0),ROUND((L428-C428)*R428/(1-((1+R428)^-D428)),NbDeci),ROUND(L428/D428,NbDeci)),S427))</x:f>
       </x:c>
     </x:row>
@@ -22945,10 +22947,10 @@
         <x:f>SUM(M429:O429)</x:f>
       </x:c>
       <x:c r="Q429" s="0"/>
-      <x:c r="R429" s="71">
+      <x:c r="R429" s="75">
         <x:f>IF(B429&gt;0,IF(TauxActuariel,((B429+1)^(1/NbEchAn))-1,B429/NbEchAn),R428)</x:f>
       </x:c>
-      <x:c r="S429" s="70">
+      <x:c r="S429" s="74">
         <x:f>IF(E429&gt;0,E429,IF(D429&gt;0,IF(AND(EchFIXE,R429&gt;0),ROUND((L429-C429)*R429/(1-((1+R429)^-D429)),NbDeci),ROUND(L429/D429,NbDeci)),S428))</x:f>
       </x:c>
     </x:row>
@@ -22986,10 +22988,10 @@
         <x:f>SUM(M430:O430)</x:f>
       </x:c>
       <x:c r="Q430" s="0"/>
-      <x:c r="R430" s="71">
+      <x:c r="R430" s="75">
         <x:f>IF(B430&gt;0,IF(TauxActuariel,((B430+1)^(1/NbEchAn))-1,B430/NbEchAn),R429)</x:f>
       </x:c>
-      <x:c r="S430" s="70">
+      <x:c r="S430" s="74">
         <x:f>IF(E430&gt;0,E430,IF(D430&gt;0,IF(AND(EchFIXE,R430&gt;0),ROUND((L430-C430)*R430/(1-((1+R430)^-D430)),NbDeci),ROUND(L430/D430,NbDeci)),S429))</x:f>
       </x:c>
     </x:row>
@@ -23027,10 +23029,10 @@
         <x:f>SUM(M431:O431)</x:f>
       </x:c>
       <x:c r="Q431" s="0"/>
-      <x:c r="R431" s="71">
+      <x:c r="R431" s="75">
         <x:f>IF(B431&gt;0,IF(TauxActuariel,((B431+1)^(1/NbEchAn))-1,B431/NbEchAn),R430)</x:f>
       </x:c>
-      <x:c r="S431" s="70">
+      <x:c r="S431" s="74">
         <x:f>IF(E431&gt;0,E431,IF(D431&gt;0,IF(AND(EchFIXE,R431&gt;0),ROUND((L431-C431)*R431/(1-((1+R431)^-D431)),NbDeci),ROUND(L431/D431,NbDeci)),S430))</x:f>
       </x:c>
     </x:row>
@@ -23068,10 +23070,10 @@
         <x:f>SUM(M432:O432)</x:f>
       </x:c>
       <x:c r="Q432" s="0"/>
-      <x:c r="R432" s="71">
+      <x:c r="R432" s="75">
         <x:f>IF(B432&gt;0,IF(TauxActuariel,((B432+1)^(1/NbEchAn))-1,B432/NbEchAn),R431)</x:f>
       </x:c>
-      <x:c r="S432" s="70">
+      <x:c r="S432" s="74">
         <x:f>IF(E432&gt;0,E432,IF(D432&gt;0,IF(AND(EchFIXE,R432&gt;0),ROUND((L432-C432)*R432/(1-((1+R432)^-D432)),NbDeci),ROUND(L432/D432,NbDeci)),S431))</x:f>
       </x:c>
     </x:row>
@@ -23109,10 +23111,10 @@
         <x:f>SUM(M433:O433)</x:f>
       </x:c>
       <x:c r="Q433" s="0"/>
-      <x:c r="R433" s="71">
+      <x:c r="R433" s="75">
         <x:f>IF(B433&gt;0,IF(TauxActuariel,((B433+1)^(1/NbEchAn))-1,B433/NbEchAn),R432)</x:f>
       </x:c>
-      <x:c r="S433" s="70">
+      <x:c r="S433" s="74">
         <x:f>IF(E433&gt;0,E433,IF(D433&gt;0,IF(AND(EchFIXE,R433&gt;0),ROUND((L433-C433)*R433/(1-((1+R433)^-D433)),NbDeci),ROUND(L433/D433,NbDeci)),S432))</x:f>
       </x:c>
     </x:row>
@@ -23150,10 +23152,10 @@
         <x:f>SUM(M434:O434)</x:f>
       </x:c>
       <x:c r="Q434" s="0"/>
-      <x:c r="R434" s="71">
+      <x:c r="R434" s="75">
         <x:f>IF(B434&gt;0,IF(TauxActuariel,((B434+1)^(1/NbEchAn))-1,B434/NbEchAn),R433)</x:f>
       </x:c>
-      <x:c r="S434" s="70">
+      <x:c r="S434" s="74">
         <x:f>IF(E434&gt;0,E434,IF(D434&gt;0,IF(AND(EchFIXE,R434&gt;0),ROUND((L434-C434)*R434/(1-((1+R434)^-D434)),NbDeci),ROUND(L434/D434,NbDeci)),S433))</x:f>
       </x:c>
     </x:row>
@@ -23191,10 +23193,10 @@
         <x:f>SUM(M435:O435)</x:f>
       </x:c>
       <x:c r="Q435" s="0"/>
-      <x:c r="R435" s="71">
+      <x:c r="R435" s="75">
         <x:f>IF(B435&gt;0,IF(TauxActuariel,((B435+1)^(1/NbEchAn))-1,B435/NbEchAn),R434)</x:f>
       </x:c>
-      <x:c r="S435" s="70">
+      <x:c r="S435" s="74">
         <x:f>IF(E435&gt;0,E435,IF(D435&gt;0,IF(AND(EchFIXE,R435&gt;0),ROUND((L435-C435)*R435/(1-((1+R435)^-D435)),NbDeci),ROUND(L435/D435,NbDeci)),S434))</x:f>
       </x:c>
     </x:row>
@@ -23232,10 +23234,10 @@
         <x:f>SUM(M436:O436)</x:f>
       </x:c>
       <x:c r="Q436" s="0"/>
-      <x:c r="R436" s="71">
+      <x:c r="R436" s="75">
         <x:f>IF(B436&gt;0,IF(TauxActuariel,((B436+1)^(1/NbEchAn))-1,B436/NbEchAn),R435)</x:f>
       </x:c>
-      <x:c r="S436" s="70">
+      <x:c r="S436" s="74">
         <x:f>IF(E436&gt;0,E436,IF(D436&gt;0,IF(AND(EchFIXE,R436&gt;0),ROUND((L436-C436)*R436/(1-((1+R436)^-D436)),NbDeci),ROUND(L436/D436,NbDeci)),S435))</x:f>
       </x:c>
     </x:row>
@@ -23273,10 +23275,10 @@
         <x:f>SUM(M437:O437)</x:f>
       </x:c>
       <x:c r="Q437" s="0"/>
-      <x:c r="R437" s="71">
+      <x:c r="R437" s="75">
         <x:f>IF(B437&gt;0,IF(TauxActuariel,((B437+1)^(1/NbEchAn))-1,B437/NbEchAn),R436)</x:f>
       </x:c>
-      <x:c r="S437" s="70">
+      <x:c r="S437" s="74">
         <x:f>IF(E437&gt;0,E437,IF(D437&gt;0,IF(AND(EchFIXE,R437&gt;0),ROUND((L437-C437)*R437/(1-((1+R437)^-D437)),NbDeci),ROUND(L437/D437,NbDeci)),S436))</x:f>
       </x:c>
     </x:row>
@@ -23314,10 +23316,10 @@
         <x:f>SUM(M438:O438)</x:f>
       </x:c>
       <x:c r="Q438" s="0"/>
-      <x:c r="R438" s="71">
+      <x:c r="R438" s="75">
         <x:f>IF(B438&gt;0,IF(TauxActuariel,((B438+1)^(1/NbEchAn))-1,B438/NbEchAn),R437)</x:f>
       </x:c>
-      <x:c r="S438" s="70">
+      <x:c r="S438" s="74">
         <x:f>IF(E438&gt;0,E438,IF(D438&gt;0,IF(AND(EchFIXE,R438&gt;0),ROUND((L438-C438)*R438/(1-((1+R438)^-D438)),NbDeci),ROUND(L438/D438,NbDeci)),S437))</x:f>
       </x:c>
     </x:row>
@@ -23355,10 +23357,10 @@
         <x:f>SUM(M439:O439)</x:f>
       </x:c>
       <x:c r="Q439" s="0"/>
-      <x:c r="R439" s="71">
+      <x:c r="R439" s="75">
         <x:f>IF(B439&gt;0,IF(TauxActuariel,((B439+1)^(1/NbEchAn))-1,B439/NbEchAn),R438)</x:f>
       </x:c>
-      <x:c r="S439" s="70">
+      <x:c r="S439" s="74">
         <x:f>IF(E439&gt;0,E439,IF(D439&gt;0,IF(AND(EchFIXE,R439&gt;0),ROUND((L439-C439)*R439/(1-((1+R439)^-D439)),NbDeci),ROUND(L439/D439,NbDeci)),S438))</x:f>
       </x:c>
     </x:row>
@@ -23396,10 +23398,10 @@
         <x:f>SUM(M440:O440)</x:f>
       </x:c>
       <x:c r="Q440" s="0"/>
-      <x:c r="R440" s="71">
+      <x:c r="R440" s="75">
         <x:f>IF(B440&gt;0,IF(TauxActuariel,((B440+1)^(1/NbEchAn))-1,B440/NbEchAn),R439)</x:f>
       </x:c>
-      <x:c r="S440" s="70">
+      <x:c r="S440" s="74">
         <x:f>IF(E440&gt;0,E440,IF(D440&gt;0,IF(AND(EchFIXE,R440&gt;0),ROUND((L440-C440)*R440/(1-((1+R440)^-D440)),NbDeci),ROUND(L440/D440,NbDeci)),S439))</x:f>
       </x:c>
     </x:row>
@@ -23437,10 +23439,10 @@
         <x:f>SUM(M441:O441)</x:f>
       </x:c>
       <x:c r="Q441" s="0"/>
-      <x:c r="R441" s="71">
+      <x:c r="R441" s="75">
         <x:f>IF(B441&gt;0,IF(TauxActuariel,((B441+1)^(1/NbEchAn))-1,B441/NbEchAn),R440)</x:f>
       </x:c>
-      <x:c r="S441" s="70">
+      <x:c r="S441" s="74">
         <x:f>IF(E441&gt;0,E441,IF(D441&gt;0,IF(AND(EchFIXE,R441&gt;0),ROUND((L441-C441)*R441/(1-((1+R441)^-D441)),NbDeci),ROUND(L441/D441,NbDeci)),S440))</x:f>
       </x:c>
     </x:row>
@@ -23478,10 +23480,10 @@
         <x:f>SUM(M442:O442)</x:f>
       </x:c>
       <x:c r="Q442" s="0"/>
-      <x:c r="R442" s="71">
+      <x:c r="R442" s="75">
         <x:f>IF(B442&gt;0,IF(TauxActuariel,((B442+1)^(1/NbEchAn))-1,B442/NbEchAn),R441)</x:f>
       </x:c>
-      <x:c r="S442" s="70">
+      <x:c r="S442" s="74">
         <x:f>IF(E442&gt;0,E442,IF(D442&gt;0,IF(AND(EchFIXE,R442&gt;0),ROUND((L442-C442)*R442/(1-((1+R442)^-D442)),NbDeci),ROUND(L442/D442,NbDeci)),S441))</x:f>
       </x:c>
     </x:row>
@@ -23519,10 +23521,10 @@
         <x:f>SUM(M443:O443)</x:f>
       </x:c>
       <x:c r="Q443" s="0"/>
-      <x:c r="R443" s="71">
+      <x:c r="R443" s="75">
         <x:f>IF(B443&gt;0,IF(TauxActuariel,((B443+1)^(1/NbEchAn))-1,B443/NbEchAn),R442)</x:f>
       </x:c>
-      <x:c r="S443" s="70">
+      <x:c r="S443" s="74">
         <x:f>IF(E443&gt;0,E443,IF(D443&gt;0,IF(AND(EchFIXE,R443&gt;0),ROUND((L443-C443)*R443/(1-((1+R443)^-D443)),NbDeci),ROUND(L443/D443,NbDeci)),S442))</x:f>
       </x:c>
     </x:row>
@@ -23560,10 +23562,10 @@
         <x:f>SUM(M444:O444)</x:f>
       </x:c>
       <x:c r="Q444" s="0"/>
-      <x:c r="R444" s="71">
+      <x:c r="R444" s="75">
         <x:f>IF(B444&gt;0,IF(TauxActuariel,((B444+1)^(1/NbEchAn))-1,B444/NbEchAn),R443)</x:f>
       </x:c>
-      <x:c r="S444" s="70">
+      <x:c r="S444" s="74">
         <x:f>IF(E444&gt;0,E444,IF(D444&gt;0,IF(AND(EchFIXE,R444&gt;0),ROUND((L444-C444)*R444/(1-((1+R444)^-D444)),NbDeci),ROUND(L444/D444,NbDeci)),S443))</x:f>
       </x:c>
     </x:row>
@@ -23601,10 +23603,10 @@
         <x:f>SUM(M445:O445)</x:f>
       </x:c>
       <x:c r="Q445" s="0"/>
-      <x:c r="R445" s="71">
+      <x:c r="R445" s="75">
         <x:f>IF(B445&gt;0,IF(TauxActuariel,((B445+1)^(1/NbEchAn))-1,B445/NbEchAn),R444)</x:f>
       </x:c>
-      <x:c r="S445" s="70">
+      <x:c r="S445" s="74">
         <x:f>IF(E445&gt;0,E445,IF(D445&gt;0,IF(AND(EchFIXE,R445&gt;0),ROUND((L445-C445)*R445/(1-((1+R445)^-D445)),NbDeci),ROUND(L445/D445,NbDeci)),S444))</x:f>
       </x:c>
     </x:row>
@@ -23642,10 +23644,10 @@
         <x:f>SUM(M446:O446)</x:f>
       </x:c>
       <x:c r="Q446" s="0"/>
-      <x:c r="R446" s="71">
+      <x:c r="R446" s="75">
         <x:f>IF(B446&gt;0,IF(TauxActuariel,((B446+1)^(1/NbEchAn))-1,B446/NbEchAn),R445)</x:f>
       </x:c>
-      <x:c r="S446" s="70">
+      <x:c r="S446" s="74">
         <x:f>IF(E446&gt;0,E446,IF(D446&gt;0,IF(AND(EchFIXE,R446&gt;0),ROUND((L446-C446)*R446/(1-((1+R446)^-D446)),NbDeci),ROUND(L446/D446,NbDeci)),S445))</x:f>
       </x:c>
     </x:row>
@@ -23683,10 +23685,10 @@
         <x:f>SUM(M447:O447)</x:f>
       </x:c>
       <x:c r="Q447" s="0"/>
-      <x:c r="R447" s="71">
+      <x:c r="R447" s="75">
         <x:f>IF(B447&gt;0,IF(TauxActuariel,((B447+1)^(1/NbEchAn))-1,B447/NbEchAn),R446)</x:f>
       </x:c>
-      <x:c r="S447" s="70">
+      <x:c r="S447" s="74">
         <x:f>IF(E447&gt;0,E447,IF(D447&gt;0,IF(AND(EchFIXE,R447&gt;0),ROUND((L447-C447)*R447/(1-((1+R447)^-D447)),NbDeci),ROUND(L447/D447,NbDeci)),S446))</x:f>
       </x:c>
     </x:row>
@@ -23946,12 +23948,12 @@
     <x:col min="1" max="1" width="4.710938" style="0" customWidth="1"/>
     <x:col min="2" max="7" width="12.710938" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="11.425781" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.710938" style="50" hidden="1" customWidth="1"/>
+    <x:col min="9" max="9" width="11.710938" style="54" hidden="1" customWidth="1"/>
     <x:col min="10" max="256" width="11.425781" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:256" x14ac:dyDescent="0.2">
-      <x:c r="I1" s="50" t="s">
+      <x:c r="I1" s="54" t="s">
         <x:v>61</x:v>
       </x:c>
     </x:row>
@@ -23964,7 +23966,7 @@
       <x:c r="E2" s="358"/>
       <x:c r="F2" s="359"/>
       <x:c r="G2" s="360"/>
-      <x:c r="I2" s="50" t="s">
+      <x:c r="I2" s="54" t="s">
         <x:v>63</x:v>
       </x:c>
     </x:row>
@@ -23979,12 +23981,12 @@
       <x:c r="E3" s="362"/>
       <x:c r="F3" s="362"/>
       <x:c r="G3" s="364"/>
-      <x:c r="I3" s="50" t="s">
+      <x:c r="I3" s="54" t="s">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:256" x14ac:dyDescent="0.2">
-      <x:c r="I4" s="50" t="s">
+      <x:c r="I4" s="54" t="s">
         <x:v>66</x:v>
       </x:c>
     </x:row>
